--- a/outputs/VIC_mlf.xlsx
+++ b/outputs/VIC_mlf.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MLF Table" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Biggest Movers" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="MLF Table" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Biggest Movers" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -900,12 +900,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>KIATAWF1</t>
+          <t>DIAPURWF1</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Kiata Wind Farm</t>
+          <t>Diapur Wind Farm</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -914,22 +914,14 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>31.05</v>
+        <v>8</v>
       </c>
       <c r="E7" s="5" t="inlineStr"/>
       <c r="F7" s="5" t="inlineStr"/>
-      <c r="G7" s="5" t="n">
-        <v>1.0357</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>0.9911</v>
-      </c>
-      <c r="I7" s="5" t="n">
-        <v>0.9066</v>
-      </c>
-      <c r="J7" s="5" t="n">
-        <v>0.8974</v>
-      </c>
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr"/>
       <c r="K7" s="5" t="n">
         <v>0.9005</v>
       </c>
@@ -963,12 +955,12 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>DIAPURWF1</t>
+          <t>KIATAWF1</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Diapur Wind Farm</t>
+          <t>Kiata Wind Farm</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -977,14 +969,22 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>8</v>
+        <v>31.05</v>
       </c>
       <c r="E8" s="5" t="inlineStr"/>
       <c r="F8" s="5" t="inlineStr"/>
-      <c r="G8" s="5" t="inlineStr"/>
-      <c r="H8" s="5" t="inlineStr"/>
-      <c r="I8" s="5" t="inlineStr"/>
-      <c r="J8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="n">
+        <v>1.0357</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>0.9911</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>0.9066</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>0.8974</v>
+      </c>
       <c r="K8" s="5" t="n">
         <v>0.9005</v>
       </c>
@@ -1193,12 +1193,12 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>YATSF1</t>
+          <t>KARSF1</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Yatpool Solar Farm</t>
+          <t>Karadoc Solar Farm</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -1207,13 +1207,17 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="E12" s="5" t="inlineStr"/>
       <c r="F12" s="5" t="inlineStr"/>
       <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="n">
+        <v>0.9472</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>0.8097</v>
+      </c>
       <c r="J12" s="5" t="n">
         <v>0.8045</v>
       </c>
@@ -1250,12 +1254,12 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>KARSF1</t>
+          <t>YATSF1</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Karadoc Solar Farm</t>
+          <t>Yatpool Solar Farm</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -1264,17 +1268,13 @@
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="E13" s="5" t="inlineStr"/>
       <c r="F13" s="5" t="inlineStr"/>
       <c r="G13" s="5" t="inlineStr"/>
-      <c r="H13" s="5" t="n">
-        <v>0.9472</v>
-      </c>
-      <c r="I13" s="5" t="n">
-        <v>0.8097</v>
-      </c>
+      <c r="H13" s="5" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr"/>
       <c r="J13" s="5" t="n">
         <v>0.8045</v>
       </c>
@@ -1311,12 +1311,12 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>BANN1</t>
+          <t>WEMENSF1</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Bannerton Solar Park</t>
+          <t>Wemen Solar Farm</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="E14" s="5" t="inlineStr"/>
       <c r="F14" s="5" t="inlineStr"/>
@@ -1372,12 +1372,12 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>WEMENSF1</t>
+          <t>BANN1</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Wemen Solar Farm</t>
+          <t>Bannerton Solar Park</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -1386,7 +1386,7 @@
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="E15" s="5" t="inlineStr"/>
       <c r="F15" s="5" t="inlineStr"/>
@@ -1433,12 +1433,12 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>NUMURSF1</t>
+          <t>GIRGSF</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Numurkah Solar Farm</t>
+          <t>Girgarre Solar Farm</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -1447,29 +1447,17 @@
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>112</v>
+        <v>93.31</v>
       </c>
       <c r="E16" s="5" t="inlineStr"/>
       <c r="F16" s="5" t="inlineStr"/>
       <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="n">
-        <v>0.982</v>
-      </c>
-      <c r="I16" s="5" t="n">
-        <v>0.9896</v>
-      </c>
-      <c r="J16" s="5" t="n">
-        <v>0.9945000000000001</v>
-      </c>
-      <c r="K16" s="5" t="n">
-        <v>0.9963</v>
-      </c>
-      <c r="L16" s="5" t="n">
-        <v>0.9715</v>
-      </c>
-      <c r="M16" s="5" t="n">
-        <v>0.9738</v>
-      </c>
+      <c r="H16" s="5" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr"/>
+      <c r="L16" s="5" t="inlineStr"/>
+      <c r="M16" s="5" t="inlineStr"/>
       <c r="N16" s="5" t="n">
         <v>0.9477</v>
       </c>
@@ -1494,12 +1482,12 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>WUNUSF1</t>
+          <t>NUMURSF1</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Wunghnu Solar Farm</t>
+          <t>Numurkah Solar Farm</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -1508,17 +1496,29 @@
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>93.5</v>
+        <v>112</v>
       </c>
       <c r="E17" s="5" t="inlineStr"/>
       <c r="F17" s="5" t="inlineStr"/>
       <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
-      <c r="L17" s="5" t="inlineStr"/>
-      <c r="M17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>0.9896</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>0.9945000000000001</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>0.9963</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>0.9715</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>0.9738</v>
+      </c>
       <c r="N17" s="5" t="n">
         <v>0.9477</v>
       </c>
@@ -1543,12 +1543,12 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>LANCSF1</t>
+          <t>WUNUSF1</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Lancaster Solar Farm</t>
+          <t>Wunghnu Solar Farm</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -1557,7 +1557,7 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>94</v>
+        <v>93.5</v>
       </c>
       <c r="E18" s="5" t="inlineStr"/>
       <c r="F18" s="5" t="inlineStr"/>
@@ -1568,10 +1568,12 @@
       <c r="K18" s="5" t="inlineStr"/>
       <c r="L18" s="5" t="inlineStr"/>
       <c r="M18" s="5" t="inlineStr"/>
-      <c r="N18" s="5" t="inlineStr"/>
+      <c r="N18" s="5" t="n">
+        <v>0.9477</v>
+      </c>
       <c r="O18" s="5" t="inlineStr"/>
       <c r="P18" s="5" t="n">
-        <v>0.9441000000000001</v>
+        <v>0.9463</v>
       </c>
       <c r="Q18" s="5" t="inlineStr"/>
       <c r="R18" s="5" t="n">
@@ -1579,10 +1581,10 @@
       </c>
       <c r="S18" s="5" t="inlineStr"/>
       <c r="T18" s="5" t="n">
-        <v>-0.0231</v>
+        <v>-0.0253</v>
       </c>
       <c r="U18" s="6" t="n">
-        <v>-2.45</v>
+        <v>-2.67</v>
       </c>
       <c r="V18" s="5" t="inlineStr"/>
       <c r="W18" s="6" t="inlineStr"/>
@@ -1590,12 +1592,12 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>GIRGSF</t>
+          <t>LANCSF1</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Girgarre Solar Farm</t>
+          <t>Lancaster Solar Farm</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -1604,7 +1606,7 @@
         </is>
       </c>
       <c r="D19" s="4" t="n">
-        <v>93.31</v>
+        <v>94</v>
       </c>
       <c r="E19" s="5" t="inlineStr"/>
       <c r="F19" s="5" t="inlineStr"/>
@@ -1615,12 +1617,10 @@
       <c r="K19" s="5" t="inlineStr"/>
       <c r="L19" s="5" t="inlineStr"/>
       <c r="M19" s="5" t="inlineStr"/>
-      <c r="N19" s="5" t="n">
-        <v>0.9477</v>
-      </c>
+      <c r="N19" s="5" t="inlineStr"/>
       <c r="O19" s="5" t="inlineStr"/>
       <c r="P19" s="5" t="n">
-        <v>0.9463</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="Q19" s="5" t="inlineStr"/>
       <c r="R19" s="5" t="n">
@@ -1628,10 +1628,10 @@
       </c>
       <c r="S19" s="5" t="inlineStr"/>
       <c r="T19" s="5" t="n">
-        <v>-0.0253</v>
+        <v>-0.0231</v>
       </c>
       <c r="U19" s="6" t="n">
-        <v>-2.67</v>
+        <v>-2.45</v>
       </c>
       <c r="V19" s="5" t="inlineStr"/>
       <c r="W19" s="6" t="inlineStr"/>
@@ -1639,12 +1639,12 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>WINTSF1</t>
+          <t>GLRWNSF1</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Winton Solar Farm</t>
+          <t>Glenrowan West Solar Farm</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="E20" s="5" t="inlineStr"/>
       <c r="F20" s="5" t="inlineStr"/>
@@ -1696,12 +1696,12 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>GLRWNSF1</t>
+          <t>WINTSF1</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Glenrowan West Solar Farm</t>
+          <t>Winton Solar Farm</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="E21" s="5" t="inlineStr"/>
       <c r="F21" s="5" t="inlineStr"/>
@@ -2185,12 +2185,12 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>BRYB1WF1</t>
+          <t>BRYB2WF2</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Berrybank Wind Farm</t>
+          <t>Berrybank 2 Wind Farm</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -2199,19 +2199,15 @@
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>180.6</v>
+        <v>109</v>
       </c>
       <c r="E30" s="5" t="inlineStr"/>
       <c r="F30" s="5" t="inlineStr"/>
       <c r="G30" s="5" t="inlineStr"/>
       <c r="H30" s="5" t="inlineStr"/>
       <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="n">
-        <v>0.9482</v>
-      </c>
-      <c r="K30" s="5" t="n">
-        <v>0.9431</v>
-      </c>
+      <c r="J30" s="5" t="inlineStr"/>
+      <c r="K30" s="5" t="inlineStr"/>
       <c r="L30" s="5" t="n">
         <v>0.9496</v>
       </c>
@@ -2242,12 +2238,12 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>BRYB2WF2</t>
+          <t>BRYB1WF1</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Berrybank 2 Wind Farm</t>
+          <t>Berrybank Wind Farm</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -2256,15 +2252,19 @@
         </is>
       </c>
       <c r="D31" s="4" t="n">
-        <v>109</v>
+        <v>180.6</v>
       </c>
       <c r="E31" s="5" t="inlineStr"/>
       <c r="F31" s="5" t="inlineStr"/>
       <c r="G31" s="5" t="inlineStr"/>
       <c r="H31" s="5" t="inlineStr"/>
       <c r="I31" s="5" t="inlineStr"/>
-      <c r="J31" s="5" t="inlineStr"/>
-      <c r="K31" s="5" t="inlineStr"/>
+      <c r="J31" s="5" t="n">
+        <v>0.9482</v>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>0.9431</v>
+      </c>
       <c r="L31" s="5" t="n">
         <v>0.9496</v>
       </c>
@@ -2544,17 +2544,13 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Pine Lodge BESS</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>Battery</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="n">
-        <v>344.4</v>
-      </c>
+          <t>PLBESS1</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D36" s="3" t="inlineStr"/>
       <c r="E36" s="5" t="inlineStr"/>
       <c r="F36" s="5" t="inlineStr"/>
       <c r="G36" s="5" t="inlineStr"/>
@@ -2702,12 +2698,12 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>MERCER01</t>
+          <t>MOORAWF1</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Mt Mercer Wind Farm</t>
+          <t xml:space="preserve">Moorabool Wind Farm </t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -2716,23 +2712,13 @@
         </is>
       </c>
       <c r="D39" s="4" t="n">
-        <v>131.2</v>
-      </c>
-      <c r="E39" s="5" t="n">
-        <v>1.0033</v>
-      </c>
-      <c r="F39" s="5" t="n">
-        <v>1.0048</v>
-      </c>
-      <c r="G39" s="5" t="n">
-        <v>1.001</v>
-      </c>
-      <c r="H39" s="5" t="n">
-        <v>0.9909</v>
-      </c>
-      <c r="I39" s="5" t="n">
-        <v>0.965</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="E39" s="5" t="inlineStr"/>
+      <c r="F39" s="5" t="inlineStr"/>
+      <c r="G39" s="5" t="inlineStr"/>
+      <c r="H39" s="5" t="inlineStr"/>
+      <c r="I39" s="5" t="inlineStr"/>
       <c r="J39" s="5" t="n">
         <v>0.9500999999999999</v>
       </c>
@@ -2824,12 +2810,12 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>MOORAWF1</t>
+          <t>MERCER01</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moorabool Wind Farm </t>
+          <t>Mt Mercer Wind Farm</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -2838,13 +2824,23 @@
         </is>
       </c>
       <c r="D41" s="4" t="n">
-        <v>312</v>
-      </c>
-      <c r="E41" s="5" t="inlineStr"/>
-      <c r="F41" s="5" t="inlineStr"/>
-      <c r="G41" s="5" t="inlineStr"/>
-      <c r="H41" s="5" t="inlineStr"/>
-      <c r="I41" s="5" t="inlineStr"/>
+        <v>131.2</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>1.0033</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>1.0048</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>1.001</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>0.9909</v>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>0.965</v>
+      </c>
       <c r="J41" s="5" t="n">
         <v>0.9500999999999999</v>
       </c>
@@ -2881,7 +2877,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>MURAYNL2</t>
+          <t>MURAYNL3</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -2948,7 +2944,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>MURAYNL3</t>
+          <t>MURAYNL2</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -3015,7 +3011,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>MURRAY</t>
+          <t>MURAYNL1</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -3029,7 +3025,7 @@
         </is>
       </c>
       <c r="D44" s="4" t="n">
-        <v>1500</v>
+        <v>25</v>
       </c>
       <c r="E44" s="5" t="n">
         <v>0.9885</v>
@@ -3082,7 +3078,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>MURAYNL1</t>
+          <t>MURRAY</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -3096,7 +3092,7 @@
         </is>
       </c>
       <c r="D45" s="4" t="n">
-        <v>25</v>
+        <v>1500</v>
       </c>
       <c r="E45" s="5" t="n">
         <v>0.9885</v>
@@ -3283,12 +3279,12 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>YWNL1</t>
+          <t>YWPS4</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>YALLOURN 'W' POWER STATION</t>
+          <t>Yallourn 'W' Power Station</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -3297,7 +3293,7 @@
         </is>
       </c>
       <c r="D48" s="4" t="n">
-        <v>25</v>
+        <v>380</v>
       </c>
       <c r="E48" s="5" t="n">
         <v>0.9563</v>
@@ -3417,12 +3413,12 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>YWPS4</t>
+          <t>YWNL1</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Yallourn 'W' Power Station</t>
+          <t>YALLOURN 'W' POWER STATION</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -3431,7 +3427,7 @@
         </is>
       </c>
       <c r="D50" s="4" t="n">
-        <v>380</v>
+        <v>25</v>
       </c>
       <c r="E50" s="5" t="n">
         <v>0.9563</v>
@@ -3484,12 +3480,12 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>BAPS</t>
+          <t>DARTM1</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Banimboola Power Station</t>
+          <t>Dartmouth Power Station</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -3498,7 +3494,7 @@
         </is>
       </c>
       <c r="D51" s="4" t="n">
-        <v>12.85</v>
+        <v>185</v>
       </c>
       <c r="E51" s="5" t="n">
         <v>1.0004</v>
@@ -3551,12 +3547,12 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>DARTM1</t>
+          <t>BAPS</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Dartmouth Power Station</t>
+          <t>Banimboola Power Station</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -3565,7 +3561,7 @@
         </is>
       </c>
       <c r="D52" s="4" t="n">
-        <v>185</v>
+        <v>12.85</v>
       </c>
       <c r="E52" s="5" t="n">
         <v>1.0004</v>
@@ -3807,12 +3803,12 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>YSWF1</t>
+          <t>HEPWIND1</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Yaloak South Wind Farm</t>
+          <t>Hepburn Community Wind Farm</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -3821,10 +3817,14 @@
         </is>
       </c>
       <c r="D56" s="4" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="E56" s="5" t="inlineStr"/>
-      <c r="F56" s="5" t="inlineStr"/>
+        <v>4.1</v>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>1.0207</v>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>1.0209</v>
+      </c>
       <c r="G56" s="5" t="n">
         <v>1.016</v>
       </c>
@@ -3870,12 +3870,12 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>HEPWIND1</t>
+          <t>MAROOWF1</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Hepburn Community Wind Farm</t>
+          <t>Maroona Wind Farm</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -3884,14 +3884,10 @@
         </is>
       </c>
       <c r="D57" s="4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="E57" s="5" t="n">
-        <v>1.0207</v>
-      </c>
-      <c r="F57" s="5" t="n">
-        <v>1.0209</v>
-      </c>
+        <v>6.8</v>
+      </c>
+      <c r="E57" s="5" t="inlineStr"/>
+      <c r="F57" s="5" t="inlineStr"/>
       <c r="G57" s="5" t="n">
         <v>1.016</v>
       </c>
@@ -3937,12 +3933,12 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>MAROOWF1</t>
+          <t>YSWF1</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Maroona Wind Farm</t>
+          <t>Yaloak South Wind Farm</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -3951,7 +3947,7 @@
         </is>
       </c>
       <c r="D58" s="4" t="n">
-        <v>6.8</v>
+        <v>28.7</v>
       </c>
       <c r="E58" s="5" t="inlineStr"/>
       <c r="F58" s="5" t="inlineStr"/>
@@ -4000,7 +3996,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>MURR1-2</t>
+          <t>MURR1-4</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -4063,7 +4059,7 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>MURR1-1</t>
+          <t>MURR1-3</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -4126,7 +4122,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>MURR1-4</t>
+          <t>MURR1-2</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -4189,17 +4185,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>MURR2-1</t>
+          <t>MURR1-10</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>MURRAY2</t>
+          <t>MURRAY1</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr"/>
       <c r="D62" s="4" t="n">
-        <v>138</v>
+        <v>95</v>
       </c>
       <c r="E62" s="5" t="n">
         <v>0.98</v>
@@ -4252,7 +4248,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>MURR1-9</t>
+          <t>MURR1-1</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -4315,7 +4311,7 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>MURR1-10</t>
+          <t>MURR1-7</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -4378,7 +4374,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>MURR1-8</t>
+          <t>MURR1-6</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -4441,7 +4437,7 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>MURR1-3</t>
+          <t>MURR1-5</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -4504,7 +4500,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>MURR1-6</t>
+          <t>MURR1-8</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -4567,17 +4563,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>MURR1-5</t>
+          <t>MURR2-2</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>MURRAY1</t>
+          <t>MURRAY2</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr"/>
       <c r="D68" s="4" t="n">
-        <v>95</v>
+        <v>138</v>
       </c>
       <c r="E68" s="5" t="n">
         <v>0.98</v>
@@ -4630,7 +4626,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>MURR2-2</t>
+          <t>MURR2-1</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -4693,17 +4689,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>MURR2-3</t>
+          <t>MURR1-9</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>MURRAY2</t>
+          <t>MURRAY1</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr"/>
       <c r="D70" s="4" t="n">
-        <v>138</v>
+        <v>95</v>
       </c>
       <c r="E70" s="5" t="n">
         <v>0.98</v>
@@ -4756,7 +4752,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>MURR2-4</t>
+          <t>MURR2-3</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -4819,17 +4815,17 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>MURR1-7</t>
+          <t>MURR2-4</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>MURRAY1</t>
+          <t>MURRAY2</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr"/>
       <c r="D72" s="4" t="n">
-        <v>95</v>
+        <v>138</v>
       </c>
       <c r="E72" s="5" t="n">
         <v>0.98</v>
@@ -4941,7 +4937,7 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>GPWFEST3</t>
+          <t>GPWFEST2</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -4955,7 +4951,7 @@
         </is>
       </c>
       <c r="D74" s="4" t="n">
-        <v>248</v>
+        <v>260.4</v>
       </c>
       <c r="E74" s="5" t="inlineStr"/>
       <c r="F74" s="5" t="inlineStr"/>
@@ -4990,7 +4986,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>GPWFEST2</t>
+          <t>GPWFEST1</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -5004,7 +5000,7 @@
         </is>
       </c>
       <c r="D75" s="4" t="n">
-        <v>260.4</v>
+        <v>248</v>
       </c>
       <c r="E75" s="5" t="inlineStr"/>
       <c r="F75" s="5" t="inlineStr"/>
@@ -5039,7 +5035,7 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>GPWFEST1</t>
+          <t>GPWFEST3</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -5093,17 +5089,13 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Wooreen Battery Energy Storage System</t>
-        </is>
-      </c>
-      <c r="C77" s="3" t="inlineStr">
-        <is>
-          <t>Battery</t>
-        </is>
-      </c>
-      <c r="D77" s="4" t="n">
-        <v>491</v>
-      </c>
+          <t>WOOREEN</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D77" s="3" t="inlineStr"/>
       <c r="E77" s="5" t="inlineStr"/>
       <c r="F77" s="5" t="inlineStr"/>
       <c r="G77" s="5" t="inlineStr"/>
@@ -5182,55 +5174,35 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>JLA04</t>
+          <t>GPWFWST2</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>Jeeralang "A" Power Station</t>
+          <t>Golden Plains Wind Farm West</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D79" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="E79" s="5" t="n">
-        <v>0.9667</v>
-      </c>
-      <c r="F79" s="5" t="n">
-        <v>0.9641</v>
-      </c>
-      <c r="G79" s="5" t="n">
-        <v>0.983</v>
-      </c>
-      <c r="H79" s="5" t="n">
-        <v>0.9782999999999999</v>
-      </c>
-      <c r="I79" s="5" t="n">
-        <v>0.9731</v>
-      </c>
-      <c r="J79" s="5" t="n">
-        <v>0.9734</v>
-      </c>
-      <c r="K79" s="5" t="n">
-        <v>0.9755</v>
-      </c>
-      <c r="L79" s="5" t="n">
-        <v>0.9727</v>
-      </c>
-      <c r="M79" s="5" t="n">
-        <v>0.9764</v>
-      </c>
-      <c r="N79" s="5" t="n">
-        <v>0.9789</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="E79" s="5" t="inlineStr"/>
+      <c r="F79" s="5" t="inlineStr"/>
+      <c r="G79" s="5" t="inlineStr"/>
+      <c r="H79" s="5" t="inlineStr"/>
+      <c r="I79" s="5" t="inlineStr"/>
+      <c r="J79" s="5" t="inlineStr"/>
+      <c r="K79" s="5" t="inlineStr"/>
+      <c r="L79" s="5" t="inlineStr"/>
+      <c r="M79" s="5" t="inlineStr"/>
+      <c r="N79" s="5" t="inlineStr"/>
       <c r="O79" s="5" t="inlineStr"/>
       <c r="P79" s="5" t="n">
-        <v>0.9768</v>
+        <v>0.9837</v>
       </c>
       <c r="Q79" s="5" t="inlineStr"/>
       <c r="R79" s="5" t="n">
@@ -5238,10 +5210,10 @@
       </c>
       <c r="S79" s="5" t="inlineStr"/>
       <c r="T79" s="5" t="n">
-        <v>0.0055</v>
+        <v>-0.0014</v>
       </c>
       <c r="U79" s="6" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.14</v>
       </c>
       <c r="V79" s="5" t="inlineStr"/>
       <c r="W79" s="6" t="inlineStr"/>
@@ -5249,55 +5221,35 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>JLA03</t>
+          <t>GPWFWST1</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Jeeralang "A" Power Station</t>
+          <t>Golden Plains Wind Farm West</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D80" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="E80" s="5" t="n">
-        <v>0.9667</v>
-      </c>
-      <c r="F80" s="5" t="n">
-        <v>0.9641</v>
-      </c>
-      <c r="G80" s="5" t="n">
-        <v>0.983</v>
-      </c>
-      <c r="H80" s="5" t="n">
-        <v>0.9782999999999999</v>
-      </c>
-      <c r="I80" s="5" t="n">
-        <v>0.9731</v>
-      </c>
-      <c r="J80" s="5" t="n">
-        <v>0.9734</v>
-      </c>
-      <c r="K80" s="5" t="n">
-        <v>0.9755</v>
-      </c>
-      <c r="L80" s="5" t="n">
-        <v>0.9727</v>
-      </c>
-      <c r="M80" s="5" t="n">
-        <v>0.9764</v>
-      </c>
-      <c r="N80" s="5" t="n">
-        <v>0.9789</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="E80" s="5" t="inlineStr"/>
+      <c r="F80" s="5" t="inlineStr"/>
+      <c r="G80" s="5" t="inlineStr"/>
+      <c r="H80" s="5" t="inlineStr"/>
+      <c r="I80" s="5" t="inlineStr"/>
+      <c r="J80" s="5" t="inlineStr"/>
+      <c r="K80" s="5" t="inlineStr"/>
+      <c r="L80" s="5" t="inlineStr"/>
+      <c r="M80" s="5" t="inlineStr"/>
+      <c r="N80" s="5" t="inlineStr"/>
       <c r="O80" s="5" t="inlineStr"/>
       <c r="P80" s="5" t="n">
-        <v>0.9768</v>
+        <v>0.9837</v>
       </c>
       <c r="Q80" s="5" t="inlineStr"/>
       <c r="R80" s="5" t="n">
@@ -5305,10 +5257,10 @@
       </c>
       <c r="S80" s="5" t="inlineStr"/>
       <c r="T80" s="5" t="n">
-        <v>0.0055</v>
+        <v>-0.0014</v>
       </c>
       <c r="U80" s="6" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.14</v>
       </c>
       <c r="V80" s="5" t="inlineStr"/>
       <c r="W80" s="6" t="inlineStr"/>
@@ -5383,7 +5335,7 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>JLA02</t>
+          <t>JLA04</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -5450,12 +5402,12 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>JLB01</t>
+          <t>JLA03</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Jeeralang "B" Power Station</t>
+          <t>Jeeralang "A" Power Station</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -5464,7 +5416,7 @@
         </is>
       </c>
       <c r="D83" s="4" t="n">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E83" s="5" t="n">
         <v>0.9667</v>
@@ -5517,12 +5469,12 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>JLB02</t>
+          <t>JLA02</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Jeeralang "B" Power Station</t>
+          <t>Jeeralang "A" Power Station</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -5531,7 +5483,7 @@
         </is>
       </c>
       <c r="D84" s="4" t="n">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E84" s="5" t="n">
         <v>0.9667</v>
@@ -5651,35 +5603,55 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>GPWFWST1</t>
+          <t>JLB02</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Golden Plains Wind Farm West</t>
+          <t>Jeeralang "B" Power Station</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D86" s="4" t="n">
-        <v>266</v>
-      </c>
-      <c r="E86" s="5" t="inlineStr"/>
-      <c r="F86" s="5" t="inlineStr"/>
-      <c r="G86" s="5" t="inlineStr"/>
-      <c r="H86" s="5" t="inlineStr"/>
-      <c r="I86" s="5" t="inlineStr"/>
-      <c r="J86" s="5" t="inlineStr"/>
-      <c r="K86" s="5" t="inlineStr"/>
-      <c r="L86" s="5" t="inlineStr"/>
-      <c r="M86" s="5" t="inlineStr"/>
-      <c r="N86" s="5" t="inlineStr"/>
+        <v>76</v>
+      </c>
+      <c r="E86" s="5" t="n">
+        <v>0.9667</v>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>0.9641</v>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>0.983</v>
+      </c>
+      <c r="H86" s="5" t="n">
+        <v>0.9782999999999999</v>
+      </c>
+      <c r="I86" s="5" t="n">
+        <v>0.9731</v>
+      </c>
+      <c r="J86" s="5" t="n">
+        <v>0.9734</v>
+      </c>
+      <c r="K86" s="5" t="n">
+        <v>0.9755</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>0.9727</v>
+      </c>
+      <c r="M86" s="5" t="n">
+        <v>0.9764</v>
+      </c>
+      <c r="N86" s="5" t="n">
+        <v>0.9789</v>
+      </c>
       <c r="O86" s="5" t="inlineStr"/>
       <c r="P86" s="5" t="n">
-        <v>0.9837</v>
+        <v>0.9768</v>
       </c>
       <c r="Q86" s="5" t="inlineStr"/>
       <c r="R86" s="5" t="n">
@@ -5687,10 +5659,10 @@
       </c>
       <c r="S86" s="5" t="inlineStr"/>
       <c r="T86" s="5" t="n">
-        <v>-0.0014</v>
+        <v>0.0055</v>
       </c>
       <c r="U86" s="6" t="n">
-        <v>-0.14</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="V86" s="5" t="inlineStr"/>
       <c r="W86" s="6" t="inlineStr"/>
@@ -5698,35 +5670,55 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>GPWFWST2</t>
+          <t>JLB01</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>Golden Plains Wind Farm West</t>
+          <t>Jeeralang "B" Power Station</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D87" s="4" t="n">
-        <v>310</v>
-      </c>
-      <c r="E87" s="5" t="inlineStr"/>
-      <c r="F87" s="5" t="inlineStr"/>
-      <c r="G87" s="5" t="inlineStr"/>
-      <c r="H87" s="5" t="inlineStr"/>
-      <c r="I87" s="5" t="inlineStr"/>
-      <c r="J87" s="5" t="inlineStr"/>
-      <c r="K87" s="5" t="inlineStr"/>
-      <c r="L87" s="5" t="inlineStr"/>
-      <c r="M87" s="5" t="inlineStr"/>
-      <c r="N87" s="5" t="inlineStr"/>
+        <v>76</v>
+      </c>
+      <c r="E87" s="5" t="n">
+        <v>0.9667</v>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>0.9641</v>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>0.983</v>
+      </c>
+      <c r="H87" s="5" t="n">
+        <v>0.9782999999999999</v>
+      </c>
+      <c r="I87" s="5" t="n">
+        <v>0.9731</v>
+      </c>
+      <c r="J87" s="5" t="n">
+        <v>0.9734</v>
+      </c>
+      <c r="K87" s="5" t="n">
+        <v>0.9755</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>0.9727</v>
+      </c>
+      <c r="M87" s="5" t="n">
+        <v>0.9764</v>
+      </c>
+      <c r="N87" s="5" t="n">
+        <v>0.9789</v>
+      </c>
       <c r="O87" s="5" t="inlineStr"/>
       <c r="P87" s="5" t="n">
-        <v>0.9837</v>
+        <v>0.9768</v>
       </c>
       <c r="Q87" s="5" t="inlineStr"/>
       <c r="R87" s="5" t="n">
@@ -5734,10 +5726,10 @@
       </c>
       <c r="S87" s="5" t="inlineStr"/>
       <c r="T87" s="5" t="n">
-        <v>-0.0014</v>
+        <v>0.0055</v>
       </c>
       <c r="U87" s="6" t="n">
-        <v>-0.14</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="V87" s="5" t="inlineStr"/>
       <c r="W87" s="6" t="inlineStr"/>
@@ -5812,12 +5804,12 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>STOCKYD1</t>
+          <t>DUNDWF3</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>Stockyard Hill Wind Farm</t>
+          <t>Dundonnell Wind Farm</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -5826,25 +5818,29 @@
         </is>
       </c>
       <c r="D89" s="4" t="n">
-        <v>531</v>
+        <v>121</v>
       </c>
       <c r="E89" s="5" t="inlineStr"/>
       <c r="F89" s="5" t="inlineStr"/>
       <c r="G89" s="5" t="inlineStr"/>
       <c r="H89" s="5" t="inlineStr"/>
-      <c r="I89" s="5" t="inlineStr"/>
-      <c r="J89" s="5" t="inlineStr"/>
+      <c r="I89" s="5" t="n">
+        <v>0.9812</v>
+      </c>
+      <c r="J89" s="5" t="n">
+        <v>0.979</v>
+      </c>
       <c r="K89" s="5" t="n">
-        <v>0.9782</v>
+        <v>0.9789</v>
       </c>
       <c r="L89" s="5" t="n">
-        <v>0.9799</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="M89" s="5" t="n">
-        <v>0.9869</v>
+        <v>0.987</v>
       </c>
       <c r="N89" s="5" t="n">
-        <v>0.9812</v>
+        <v>0.981</v>
       </c>
       <c r="O89" s="5" t="inlineStr"/>
       <c r="P89" s="5" t="n">
@@ -5867,7 +5863,7 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>DUNDWF3</t>
+          <t>DUNDWF2</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -5881,7 +5877,7 @@
         </is>
       </c>
       <c r="D90" s="4" t="n">
-        <v>121</v>
+        <v>46</v>
       </c>
       <c r="E90" s="5" t="inlineStr"/>
       <c r="F90" s="5" t="inlineStr"/>
@@ -5926,7 +5922,7 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>DUNDWF2</t>
+          <t>DUNDWF1</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -5940,7 +5936,7 @@
         </is>
       </c>
       <c r="D91" s="4" t="n">
-        <v>46</v>
+        <v>168</v>
       </c>
       <c r="E91" s="5" t="inlineStr"/>
       <c r="F91" s="5" t="inlineStr"/>
@@ -5985,12 +5981,12 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>DUNDWF1</t>
+          <t>STOCKYD1</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>Dundonnell Wind Farm</t>
+          <t>Stockyard Hill Wind Farm</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
@@ -5999,29 +5995,25 @@
         </is>
       </c>
       <c r="D92" s="4" t="n">
-        <v>168</v>
+        <v>531</v>
       </c>
       <c r="E92" s="5" t="inlineStr"/>
       <c r="F92" s="5" t="inlineStr"/>
       <c r="G92" s="5" t="inlineStr"/>
       <c r="H92" s="5" t="inlineStr"/>
-      <c r="I92" s="5" t="n">
+      <c r="I92" s="5" t="inlineStr"/>
+      <c r="J92" s="5" t="inlineStr"/>
+      <c r="K92" s="5" t="n">
+        <v>0.9782</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>0.9799</v>
+      </c>
+      <c r="M92" s="5" t="n">
+        <v>0.9869</v>
+      </c>
+      <c r="N92" s="5" t="n">
         <v>0.9812</v>
-      </c>
-      <c r="J92" s="5" t="n">
-        <v>0.979</v>
-      </c>
-      <c r="K92" s="5" t="n">
-        <v>0.9789</v>
-      </c>
-      <c r="L92" s="5" t="n">
-        <v>0.9824000000000001</v>
-      </c>
-      <c r="M92" s="5" t="n">
-        <v>0.987</v>
-      </c>
-      <c r="N92" s="5" t="n">
-        <v>0.981</v>
       </c>
       <c r="O92" s="5" t="inlineStr"/>
       <c r="P92" s="5" t="n">
@@ -6093,12 +6085,12 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>LYNL1</t>
+          <t>VPGS6</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>LOY YANG A POWER STATION</t>
+          <t>Valley Power Peaking Facility</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -6107,7 +6099,7 @@
         </is>
       </c>
       <c r="D94" s="4" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E94" s="5" t="n">
         <v>0.9742</v>
@@ -6160,12 +6152,12 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>LYA4</t>
+          <t>VPGS5</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>Loy Yang A Power Station</t>
+          <t>Valley Power Peaking Facility</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -6174,7 +6166,7 @@
         </is>
       </c>
       <c r="D95" s="4" t="n">
-        <v>560</v>
+        <v>50</v>
       </c>
       <c r="E95" s="5" t="n">
         <v>0.9742</v>
@@ -6227,7 +6219,7 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>VPGS6</t>
+          <t>VPGS4</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -6294,61 +6286,69 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>HBESS1</t>
+          <t>VPGS3</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>Hazelwood Battery Energy Storage System</t>
+          <t>Valley Power Peaking Facility</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D97" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="E97" s="5" t="inlineStr"/>
-      <c r="F97" s="5" t="inlineStr"/>
-      <c r="G97" s="5" t="inlineStr"/>
-      <c r="H97" s="5" t="inlineStr"/>
-      <c r="I97" s="5" t="inlineStr"/>
-      <c r="J97" s="5" t="inlineStr"/>
-      <c r="K97" s="5" t="inlineStr"/>
-      <c r="L97" s="5" t="inlineStr"/>
-      <c r="M97" s="5" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="E97" s="5" t="n">
+        <v>0.9742</v>
+      </c>
+      <c r="F97" s="5" t="n">
+        <v>0.9723000000000001</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>0.9801</v>
+      </c>
+      <c r="H97" s="5" t="n">
+        <v>0.9798</v>
+      </c>
+      <c r="I97" s="5" t="n">
+        <v>0.9754</v>
+      </c>
+      <c r="J97" s="5" t="n">
+        <v>0.976</v>
+      </c>
+      <c r="K97" s="5" t="n">
+        <v>0.9759</v>
+      </c>
+      <c r="L97" s="5" t="n">
+        <v>0.9782999999999999</v>
+      </c>
+      <c r="M97" s="5" t="n">
+        <v>0.9782</v>
+      </c>
       <c r="N97" s="5" t="n">
-        <v>0.9804</v>
-      </c>
-      <c r="O97" s="5" t="n">
-        <v>0.9864000000000001</v>
-      </c>
+        <v>0.9809</v>
+      </c>
+      <c r="O97" s="5" t="inlineStr"/>
       <c r="P97" s="5" t="n">
-        <v>0.9802</v>
-      </c>
-      <c r="Q97" s="5" t="n">
-        <v>0.9873</v>
-      </c>
+        <v>0.9815</v>
+      </c>
+      <c r="Q97" s="5" t="inlineStr"/>
       <c r="R97" s="5" t="n">
         <v>0.9834000000000001</v>
       </c>
-      <c r="S97" s="5" t="n">
-        <v>0.9873</v>
-      </c>
+      <c r="S97" s="5" t="inlineStr"/>
       <c r="T97" s="5" t="n">
-        <v>0.0032</v>
+        <v>0.0019</v>
       </c>
       <c r="U97" s="6" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="V97" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W97" s="6" t="n">
-        <v>0</v>
-      </c>
+        <v>0.19</v>
+      </c>
+      <c r="V97" s="5" t="inlineStr"/>
+      <c r="W97" s="6" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
@@ -6487,79 +6487,71 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>LYA3</t>
+          <t>HBESS1</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>Loy Yang A Power Station</t>
+          <t>Hazelwood Battery Energy Storage System</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D100" s="4" t="n">
-        <v>560</v>
-      </c>
-      <c r="E100" s="5" t="n">
-        <v>0.9742</v>
-      </c>
-      <c r="F100" s="5" t="n">
-        <v>0.9723000000000001</v>
-      </c>
-      <c r="G100" s="5" t="n">
-        <v>0.9801</v>
-      </c>
-      <c r="H100" s="5" t="n">
-        <v>0.9798</v>
-      </c>
-      <c r="I100" s="5" t="n">
-        <v>0.9754</v>
-      </c>
-      <c r="J100" s="5" t="n">
-        <v>0.976</v>
-      </c>
-      <c r="K100" s="5" t="n">
-        <v>0.9759</v>
-      </c>
-      <c r="L100" s="5" t="n">
-        <v>0.9782999999999999</v>
-      </c>
-      <c r="M100" s="5" t="n">
-        <v>0.9782</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="E100" s="5" t="inlineStr"/>
+      <c r="F100" s="5" t="inlineStr"/>
+      <c r="G100" s="5" t="inlineStr"/>
+      <c r="H100" s="5" t="inlineStr"/>
+      <c r="I100" s="5" t="inlineStr"/>
+      <c r="J100" s="5" t="inlineStr"/>
+      <c r="K100" s="5" t="inlineStr"/>
+      <c r="L100" s="5" t="inlineStr"/>
+      <c r="M100" s="5" t="inlineStr"/>
       <c r="N100" s="5" t="n">
-        <v>0.9809</v>
-      </c>
-      <c r="O100" s="5" t="inlineStr"/>
+        <v>0.9804</v>
+      </c>
+      <c r="O100" s="5" t="n">
+        <v>0.9864000000000001</v>
+      </c>
       <c r="P100" s="5" t="n">
-        <v>0.9815</v>
-      </c>
-      <c r="Q100" s="5" t="inlineStr"/>
+        <v>0.9802</v>
+      </c>
+      <c r="Q100" s="5" t="n">
+        <v>0.9873</v>
+      </c>
       <c r="R100" s="5" t="n">
         <v>0.9834000000000001</v>
       </c>
-      <c r="S100" s="5" t="inlineStr"/>
+      <c r="S100" s="5" t="n">
+        <v>0.9873</v>
+      </c>
       <c r="T100" s="5" t="n">
-        <v>0.0019</v>
+        <v>0.0032</v>
       </c>
       <c r="U100" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="V100" s="5" t="inlineStr"/>
-      <c r="W100" s="6" t="inlineStr"/>
+        <v>0.33</v>
+      </c>
+      <c r="V100" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W100" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>VPGS3</t>
+          <t>LYNL1</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>Valley Power Peaking Facility</t>
+          <t>LOY YANG A POWER STATION</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
@@ -6568,7 +6560,7 @@
         </is>
       </c>
       <c r="D101" s="4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E101" s="5" t="n">
         <v>0.9742</v>
@@ -6621,7 +6613,7 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>LYA2</t>
+          <t>LYA4</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -6635,7 +6627,7 @@
         </is>
       </c>
       <c r="D102" s="4" t="n">
-        <v>530</v>
+        <v>560</v>
       </c>
       <c r="E102" s="5" t="n">
         <v>0.9742</v>
@@ -6688,7 +6680,7 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>LYA1</t>
+          <t>LYA3</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -6755,12 +6747,12 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>LOYYB1</t>
+          <t>LYA2</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>Loy Yang B Power Station</t>
+          <t>Loy Yang A Power Station</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
@@ -6769,7 +6761,7 @@
         </is>
       </c>
       <c r="D104" s="4" t="n">
-        <v>500</v>
+        <v>530</v>
       </c>
       <c r="E104" s="5" t="n">
         <v>0.9742</v>
@@ -6822,12 +6814,12 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>VPGS5</t>
+          <t>LYA1</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>Valley Power Peaking Facility</t>
+          <t>Loy Yang A Power Station</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
@@ -6836,7 +6828,7 @@
         </is>
       </c>
       <c r="D105" s="4" t="n">
-        <v>50</v>
+        <v>560</v>
       </c>
       <c r="E105" s="5" t="n">
         <v>0.9742</v>
@@ -6889,12 +6881,12 @@
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>VPGS4</t>
+          <t>LOYYB2</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>Valley Power Peaking Facility</t>
+          <t>Loy Yang B Power Station</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
@@ -6903,7 +6895,7 @@
         </is>
       </c>
       <c r="D106" s="4" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="E106" s="5" t="n">
         <v>0.9742</v>
@@ -6956,7 +6948,7 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>LOYYB2</t>
+          <t>LOYYB1</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -7031,9 +7023,13 @@
           <t>Basslink HVDC Link</t>
         </is>
       </c>
-      <c r="C108" s="3" t="inlineStr"/>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
       <c r="D108" s="4" t="n">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="E108" s="5" t="n">
         <v>0.9828</v>
@@ -7220,12 +7216,12 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>WKIEWA2</t>
+          <t>WKIEWA1</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>WEST KIEWA POWER STATION</t>
+          <t>West Kiewa Power Station</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
@@ -7287,7 +7283,7 @@
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>WKIEWA1</t>
+          <t>WKIEWA2</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -7301,7 +7297,7 @@
         </is>
       </c>
       <c r="D112" s="4" t="n">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="E112" s="5" t="n">
         <v>1.0247</v>
@@ -7535,74 +7531,62 @@
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>BDL02</t>
+          <t>MLB01</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>Bairnsdale Power Station</t>
+          <t>Mortlake Battery Energy Storage System</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D116" s="4" t="n">
-        <v>46</v>
-      </c>
-      <c r="E116" s="5" t="n">
-        <v>0.9771</v>
-      </c>
-      <c r="F116" s="5" t="n">
-        <v>0.9745</v>
-      </c>
-      <c r="G116" s="5" t="n">
-        <v>0.9863</v>
-      </c>
-      <c r="H116" s="5" t="n">
-        <v>0.9866</v>
-      </c>
-      <c r="I116" s="5" t="n">
-        <v>0.9871</v>
-      </c>
-      <c r="J116" s="5" t="n">
-        <v>0.9899</v>
-      </c>
-      <c r="K116" s="5" t="n">
-        <v>0.9874000000000001</v>
-      </c>
-      <c r="L116" s="5" t="n">
-        <v>0.9913</v>
-      </c>
-      <c r="M116" s="5" t="n">
-        <v>0.9804</v>
-      </c>
-      <c r="N116" s="5" t="n">
-        <v>0.9816</v>
-      </c>
+        <v>440</v>
+      </c>
+      <c r="E116" s="5" t="inlineStr"/>
+      <c r="F116" s="5" t="inlineStr"/>
+      <c r="G116" s="5" t="inlineStr"/>
+      <c r="H116" s="5" t="inlineStr"/>
+      <c r="I116" s="5" t="inlineStr"/>
+      <c r="J116" s="5" t="inlineStr"/>
+      <c r="K116" s="5" t="inlineStr"/>
+      <c r="L116" s="5" t="inlineStr"/>
+      <c r="M116" s="5" t="inlineStr"/>
+      <c r="N116" s="5" t="inlineStr"/>
       <c r="O116" s="5" t="inlineStr"/>
       <c r="P116" s="5" t="n">
-        <v>0.9816</v>
-      </c>
-      <c r="Q116" s="5" t="inlineStr"/>
+        <v>0.9945000000000001</v>
+      </c>
+      <c r="Q116" s="5" t="n">
+        <v>0.9945000000000001</v>
+      </c>
       <c r="R116" s="5" t="n">
         <v>0.9893</v>
       </c>
-      <c r="S116" s="5" t="inlineStr"/>
+      <c r="S116" s="5" t="n">
+        <v>0.994</v>
+      </c>
       <c r="T116" s="5" t="n">
-        <v>0.0077</v>
+        <v>-0.0052</v>
       </c>
       <c r="U116" s="6" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="V116" s="5" t="inlineStr"/>
-      <c r="W116" s="6" t="inlineStr"/>
+        <v>-0.52</v>
+      </c>
+      <c r="V116" s="5" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="W116" s="6" t="n">
+        <v>-0.05</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>BDL01</t>
+          <t>BDL02</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -7669,57 +7653,69 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>MLB01</t>
+          <t>BDL01</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>Mortlake Battery Energy Storage System</t>
+          <t>Bairnsdale Power Station</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D118" s="4" t="n">
-        <v>440</v>
-      </c>
-      <c r="E118" s="5" t="inlineStr"/>
-      <c r="F118" s="5" t="inlineStr"/>
-      <c r="G118" s="5" t="inlineStr"/>
-      <c r="H118" s="5" t="inlineStr"/>
-      <c r="I118" s="5" t="inlineStr"/>
-      <c r="J118" s="5" t="inlineStr"/>
-      <c r="K118" s="5" t="inlineStr"/>
-      <c r="L118" s="5" t="inlineStr"/>
-      <c r="M118" s="5" t="inlineStr"/>
-      <c r="N118" s="5" t="inlineStr"/>
+        <v>46</v>
+      </c>
+      <c r="E118" s="5" t="n">
+        <v>0.9771</v>
+      </c>
+      <c r="F118" s="5" t="n">
+        <v>0.9745</v>
+      </c>
+      <c r="G118" s="5" t="n">
+        <v>0.9863</v>
+      </c>
+      <c r="H118" s="5" t="n">
+        <v>0.9866</v>
+      </c>
+      <c r="I118" s="5" t="n">
+        <v>0.9871</v>
+      </c>
+      <c r="J118" s="5" t="n">
+        <v>0.9899</v>
+      </c>
+      <c r="K118" s="5" t="n">
+        <v>0.9874000000000001</v>
+      </c>
+      <c r="L118" s="5" t="n">
+        <v>0.9913</v>
+      </c>
+      <c r="M118" s="5" t="n">
+        <v>0.9804</v>
+      </c>
+      <c r="N118" s="5" t="n">
+        <v>0.9816</v>
+      </c>
       <c r="O118" s="5" t="inlineStr"/>
       <c r="P118" s="5" t="n">
-        <v>0.9945000000000001</v>
-      </c>
-      <c r="Q118" s="5" t="n">
-        <v>0.9945000000000001</v>
-      </c>
+        <v>0.9816</v>
+      </c>
+      <c r="Q118" s="5" t="inlineStr"/>
       <c r="R118" s="5" t="n">
         <v>0.9893</v>
       </c>
-      <c r="S118" s="5" t="n">
-        <v>0.994</v>
-      </c>
+      <c r="S118" s="5" t="inlineStr"/>
       <c r="T118" s="5" t="n">
-        <v>-0.0052</v>
+        <v>0.0077</v>
       </c>
       <c r="U118" s="6" t="n">
-        <v>-0.52</v>
-      </c>
-      <c r="V118" s="5" t="n">
-        <v>-0.0005</v>
-      </c>
-      <c r="W118" s="6" t="n">
-        <v>-0.05</v>
-      </c>
+        <v>0.78</v>
+      </c>
+      <c r="V118" s="5" t="inlineStr"/>
+      <c r="W118" s="6" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
@@ -7779,12 +7775,12 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>MREHA1</t>
+          <t>MREHA2</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>Melbourne Renewable Energy Hub Connection A1</t>
+          <t>Melbourne Renewable Energy Hub Connection A2</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
@@ -7838,12 +7834,12 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>MREHA2</t>
+          <t>MREHA1</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>Melbourne Renewable Energy Hub Connection A2</t>
+          <t>Melbourne Renewable Energy Hub Connection A1</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
@@ -7952,21 +7948,21 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>TOORAWF</t>
+          <t>GLENMAG1</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>Toora Wind Farm</t>
+          <t>Glenmaggie Hydro Power Station</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="D123" s="4" t="n">
-        <v>21</v>
+        <v>3.8</v>
       </c>
       <c r="E123" s="5" t="n">
         <v>0.9799</v>
@@ -8019,21 +8015,21 @@
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>TGNSS1</t>
+          <t>WONWP</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>Traralgon Network Support Station</t>
+          <t>Wonthaggi Wind Farm</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D124" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E124" s="5" t="n">
         <v>0.9799</v>
@@ -8086,138 +8082,138 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>LONGFORD</t>
+          <t>PIBESS1</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>Longford Plant</t>
+          <t>Phillip Island BESS</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D125" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="E125" s="5" t="n">
-        <v>0.9799</v>
-      </c>
-      <c r="F125" s="5" t="n">
-        <v>0.9759</v>
-      </c>
-      <c r="G125" s="5" t="n">
-        <v>0.9886</v>
-      </c>
-      <c r="H125" s="5" t="n">
-        <v>0.9879</v>
-      </c>
-      <c r="I125" s="5" t="n">
-        <v>0.9938</v>
-      </c>
-      <c r="J125" s="5" t="n">
-        <v>0.9955000000000001</v>
-      </c>
-      <c r="K125" s="5" t="n">
-        <v>0.9936</v>
-      </c>
-      <c r="L125" s="5" t="n">
-        <v>0.9977</v>
-      </c>
-      <c r="M125" s="5" t="n">
-        <v>0.9825</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="E125" s="5" t="inlineStr"/>
+      <c r="F125" s="5" t="inlineStr"/>
+      <c r="G125" s="5" t="inlineStr"/>
+      <c r="H125" s="5" t="inlineStr"/>
+      <c r="I125" s="5" t="inlineStr"/>
+      <c r="J125" s="5" t="inlineStr"/>
+      <c r="K125" s="5" t="inlineStr"/>
+      <c r="L125" s="5" t="inlineStr"/>
+      <c r="M125" s="5" t="inlineStr"/>
       <c r="N125" s="5" t="n">
         <v>0.9848</v>
       </c>
-      <c r="O125" s="5" t="inlineStr"/>
+      <c r="O125" s="5" t="n">
+        <v>0.9848</v>
+      </c>
       <c r="P125" s="5" t="n">
         <v>0.9862</v>
       </c>
-      <c r="Q125" s="5" t="inlineStr"/>
+      <c r="Q125" s="5" t="n">
+        <v>0.9862</v>
+      </c>
       <c r="R125" s="5" t="n">
         <v>0.992</v>
       </c>
-      <c r="S125" s="5" t="inlineStr"/>
+      <c r="S125" s="5" t="n">
+        <v>0.992</v>
+      </c>
       <c r="T125" s="5" t="n">
         <v>0.0058</v>
       </c>
       <c r="U125" s="6" t="n">
         <v>0.59</v>
       </c>
-      <c r="V125" s="5" t="inlineStr"/>
-      <c r="W125" s="6" t="inlineStr"/>
+      <c r="V125" s="5" t="n">
+        <v>0.0058</v>
+      </c>
+      <c r="W125" s="6" t="n">
+        <v>0.59</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>PIBESS1</t>
+          <t>TGNSS1</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>Phillip Island BESS</t>
+          <t>Traralgon Network Support Station</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D126" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="E126" s="5" t="inlineStr"/>
-      <c r="F126" s="5" t="inlineStr"/>
-      <c r="G126" s="5" t="inlineStr"/>
-      <c r="H126" s="5" t="inlineStr"/>
-      <c r="I126" s="5" t="inlineStr"/>
-      <c r="J126" s="5" t="inlineStr"/>
-      <c r="K126" s="5" t="inlineStr"/>
-      <c r="L126" s="5" t="inlineStr"/>
-      <c r="M126" s="5" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="E126" s="5" t="n">
+        <v>0.9799</v>
+      </c>
+      <c r="F126" s="5" t="n">
+        <v>0.9759</v>
+      </c>
+      <c r="G126" s="5" t="n">
+        <v>0.9886</v>
+      </c>
+      <c r="H126" s="5" t="n">
+        <v>0.9879</v>
+      </c>
+      <c r="I126" s="5" t="n">
+        <v>0.9938</v>
+      </c>
+      <c r="J126" s="5" t="n">
+        <v>0.9955000000000001</v>
+      </c>
+      <c r="K126" s="5" t="n">
+        <v>0.9936</v>
+      </c>
+      <c r="L126" s="5" t="n">
+        <v>0.9977</v>
+      </c>
+      <c r="M126" s="5" t="n">
+        <v>0.9825</v>
+      </c>
       <c r="N126" s="5" t="n">
         <v>0.9848</v>
       </c>
-      <c r="O126" s="5" t="n">
-        <v>0.9848</v>
-      </c>
+      <c r="O126" s="5" t="inlineStr"/>
       <c r="P126" s="5" t="n">
         <v>0.9862</v>
       </c>
-      <c r="Q126" s="5" t="n">
-        <v>0.9862</v>
-      </c>
+      <c r="Q126" s="5" t="inlineStr"/>
       <c r="R126" s="5" t="n">
         <v>0.992</v>
       </c>
-      <c r="S126" s="5" t="n">
-        <v>0.992</v>
-      </c>
+      <c r="S126" s="5" t="inlineStr"/>
       <c r="T126" s="5" t="n">
         <v>0.0058</v>
       </c>
       <c r="U126" s="6" t="n">
         <v>0.59</v>
       </c>
-      <c r="V126" s="5" t="n">
-        <v>0.0058</v>
-      </c>
-      <c r="W126" s="6" t="n">
-        <v>0.59</v>
-      </c>
+      <c r="V126" s="5" t="inlineStr"/>
+      <c r="W126" s="6" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>BALDHWF1</t>
+          <t>TOORAWF</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>Bald Hills Wind Farm</t>
+          <t>Toora Wind Farm</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
@@ -8226,7 +8222,7 @@
         </is>
       </c>
       <c r="D127" s="4" t="n">
-        <v>106.6</v>
+        <v>21</v>
       </c>
       <c r="E127" s="5" t="n">
         <v>0.9799</v>
@@ -8279,12 +8275,12 @@
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>WONWP</t>
+          <t>BALDHWF1</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>Wonthaggi Wind Farm</t>
+          <t>Bald Hills Wind Farm</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
@@ -8293,7 +8289,7 @@
         </is>
       </c>
       <c r="D128" s="4" t="n">
-        <v>12</v>
+        <v>106.6</v>
       </c>
       <c r="E128" s="5" t="n">
         <v>0.9799</v>
@@ -8346,21 +8342,21 @@
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>GLENMAG1</t>
+          <t>LONGFORD</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>Glenmaggie Hydro Power Station</t>
+          <t>LONGFORD PLANT</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>Hydro</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D129" s="4" t="n">
-        <v>3.8</v>
+        <v>44</v>
       </c>
       <c r="E129" s="5" t="n">
         <v>0.9799</v>
@@ -8539,12 +8535,12 @@
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>YAMBUKWF</t>
+          <t>FSWF1</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>Yambuk Wind Farm</t>
+          <t>Ferguson South Wind Farm</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
@@ -8553,23 +8549,13 @@
         </is>
       </c>
       <c r="D132" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="E132" s="5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="F132" s="5" t="n">
-        <v>1.0339</v>
-      </c>
-      <c r="G132" s="5" t="n">
-        <v>1.0322</v>
-      </c>
-      <c r="H132" s="5" t="n">
-        <v>1.0149</v>
-      </c>
-      <c r="I132" s="5" t="n">
-        <v>1.0019</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="E132" s="5" t="inlineStr"/>
+      <c r="F132" s="5" t="inlineStr"/>
+      <c r="G132" s="5" t="inlineStr"/>
+      <c r="H132" s="5" t="inlineStr"/>
+      <c r="I132" s="5" t="inlineStr"/>
       <c r="J132" s="5" t="n">
         <v>1.0079</v>
       </c>
@@ -8606,12 +8592,12 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>OAKLAND1</t>
+          <t>CODRNGTON</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>Oaklands Hill Wind Farm</t>
+          <t>Codrington Wind Farm</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
@@ -8620,7 +8606,7 @@
         </is>
       </c>
       <c r="D133" s="4" t="n">
-        <v>67</v>
+        <v>18.2</v>
       </c>
       <c r="E133" s="5" t="n">
         <v>1.03</v>
@@ -8673,12 +8659,12 @@
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>FSWF1</t>
+          <t>OAKLAND1</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>Ferguson South Wind Farm</t>
+          <t>Oaklands Hill Wind Farm</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
@@ -8687,13 +8673,23 @@
         </is>
       </c>
       <c r="D134" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="E134" s="5" t="inlineStr"/>
-      <c r="F134" s="5" t="inlineStr"/>
-      <c r="G134" s="5" t="inlineStr"/>
-      <c r="H134" s="5" t="inlineStr"/>
-      <c r="I134" s="5" t="inlineStr"/>
+        <v>67</v>
+      </c>
+      <c r="E134" s="5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="F134" s="5" t="n">
+        <v>1.0339</v>
+      </c>
+      <c r="G134" s="5" t="n">
+        <v>1.0322</v>
+      </c>
+      <c r="H134" s="5" t="n">
+        <v>1.0149</v>
+      </c>
+      <c r="I134" s="5" t="n">
+        <v>1.0019</v>
+      </c>
       <c r="J134" s="5" t="n">
         <v>1.0079</v>
       </c>
@@ -8730,12 +8726,12 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>CODRNGTON</t>
+          <t>MLWF1</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>Codrington Wind Farm</t>
+          <t>Mortons Lane Wind Farm</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
@@ -8744,7 +8740,7 @@
         </is>
       </c>
       <c r="D135" s="4" t="n">
-        <v>18.2</v>
+        <v>20</v>
       </c>
       <c r="E135" s="5" t="n">
         <v>1.03</v>
@@ -8797,12 +8793,12 @@
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>MLWF1</t>
+          <t>YAMBUKWF</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>Mortons Lane Wind Farm</t>
+          <t>Yambuk Wind Farm</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
@@ -8811,7 +8807,7 @@
         </is>
       </c>
       <c r="D136" s="4" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E136" s="5" t="n">
         <v>1.03</v>
@@ -9598,30 +9594,30 @@
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>WOLLERT1</t>
+          <t>RUBICON</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>Wollert Renewable Energy Facility</t>
+          <t>Rubicon Mountain Streams Station</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>Other Renewable</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="D149" s="4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E149" s="5" t="n">
-        <v>0.9987</v>
+        <v>1</v>
       </c>
       <c r="F149" s="5" t="n">
-        <v>0.9985000000000001</v>
+        <v>1</v>
       </c>
       <c r="G149" s="5" t="n">
-        <v>0.998</v>
+        <v>1</v>
       </c>
       <c r="H149" s="5" t="n">
         <v>0.9979</v>
@@ -9665,12 +9661,12 @@
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>RUBICON</t>
+          <t>EILDON3</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>Rubicon Mountain Streams Station</t>
+          <t>Eildon Power Station</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
@@ -9679,16 +9675,16 @@
         </is>
       </c>
       <c r="D150" s="4" t="n">
-        <v>13</v>
+        <v>4.5</v>
       </c>
       <c r="E150" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F150" s="5" t="n">
-        <v>1</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="G150" s="5" t="n">
-        <v>1</v>
+        <v>0.998</v>
       </c>
       <c r="H150" s="5" t="n">
         <v>0.9979</v>
@@ -9732,24 +9728,24 @@
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>EILDON3</t>
+          <t>WOLLERT1</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>Eildon Power Station</t>
+          <t>Wollert Renewable Energy Facility</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>Hydro</t>
+          <t>Other Renewable</t>
         </is>
       </c>
       <c r="D151" s="4" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>1</v>
+        <v>0.9987</v>
       </c>
       <c r="F151" s="5" t="n">
         <v>0.9985000000000001</v>
@@ -10384,12 +10380,12 @@
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>SHEP1</t>
+          <t>TATURA01</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>Shepparton Wastewater Treatment Facility</t>
+          <t>Tatura Biomass Generator</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
@@ -10451,12 +10447,12 @@
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>TATURA01</t>
+          <t>SHEP1</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>Tatura Biomass Generator</t>
+          <t>Shepparton Wastewater Treatment Facility</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
@@ -10652,7 +10648,7 @@
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
         <is>
-          <t>MOR1</t>
+          <t>MOR3</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
@@ -10665,7 +10661,7 @@
       </c>
       <c r="D165" s="3" t="inlineStr"/>
       <c r="E165" s="5" t="n">
-        <v>0.9704</v>
+        <v>0.9732</v>
       </c>
       <c r="F165" s="5" t="inlineStr"/>
       <c r="G165" s="5" t="inlineStr"/>
@@ -10726,7 +10722,7 @@
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
         <is>
-          <t>MOR3</t>
+          <t>MOR1</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
@@ -10739,7 +10735,7 @@
       </c>
       <c r="D167" s="3" t="inlineStr"/>
       <c r="E167" s="5" t="n">
-        <v>0.9732</v>
+        <v>0.9704</v>
       </c>
       <c r="F167" s="5" t="inlineStr"/>
       <c r="G167" s="5" t="inlineStr"/>
@@ -10845,7 +10841,7 @@
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>HWPNL1</t>
+          <t>HWPS6</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -10859,7 +10855,7 @@
         </is>
       </c>
       <c r="D170" s="4" t="n">
-        <v>25</v>
+        <v>200</v>
       </c>
       <c r="E170" s="5" t="n">
         <v>0.9723000000000001</v>
@@ -10888,7 +10884,7 @@
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>HWPS1</t>
+          <t>HWPS7</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -10902,7 +10898,7 @@
         </is>
       </c>
       <c r="D171" s="4" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="E171" s="5" t="n">
         <v>0.9723000000000001</v>
@@ -10931,7 +10927,7 @@
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>HWPS2</t>
+          <t>HWPS8</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -10945,7 +10941,7 @@
         </is>
       </c>
       <c r="D172" s="4" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="E172" s="5" t="n">
         <v>0.9723000000000001</v>
@@ -10974,7 +10970,7 @@
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>HWPS3</t>
+          <t>HWPS4</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -11017,7 +11013,7 @@
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>HWPS4</t>
+          <t>HWPS5</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -11060,7 +11056,7 @@
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>HWPS5</t>
+          <t>HWPS3</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
@@ -11103,7 +11099,7 @@
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>HWPS6</t>
+          <t>HWPS2</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -11117,7 +11113,7 @@
         </is>
       </c>
       <c r="D176" s="4" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="E176" s="5" t="n">
         <v>0.9723000000000001</v>
@@ -11146,7 +11142,7 @@
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
         <is>
-          <t>HWPS7</t>
+          <t>HWPS1</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
@@ -11160,7 +11156,7 @@
         </is>
       </c>
       <c r="D177" s="4" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="E177" s="5" t="n">
         <v>0.9723000000000001</v>
@@ -11189,7 +11185,7 @@
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>HWPS8</t>
+          <t>HWPNL1</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -11203,7 +11199,7 @@
         </is>
       </c>
       <c r="D178" s="4" t="n">
-        <v>200</v>
+        <v>25</v>
       </c>
       <c r="E178" s="5" t="n">
         <v>0.9723000000000001</v>
@@ -11232,12 +11228,12 @@
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
         <is>
-          <t>MORNW</t>
+          <t>WYNDW</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>Mornington Waste Disposal Facility</t>
+          <t>Wyndham Waste Disposal Facility</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
@@ -11249,13 +11245,13 @@
         <v>1</v>
       </c>
       <c r="E179" s="5" t="n">
-        <v>0.9923999999999999</v>
+        <v>1.0032</v>
       </c>
       <c r="F179" s="5" t="n">
-        <v>0.9925</v>
+        <v>1.0068</v>
       </c>
       <c r="G179" s="5" t="n">
-        <v>0.9963</v>
+        <v>1.0084</v>
       </c>
       <c r="H179" s="5" t="inlineStr"/>
       <c r="I179" s="5" t="inlineStr"/>
@@ -11277,12 +11273,12 @@
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>WYNDW</t>
+          <t>MORNW</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>Wyndham Waste Disposal Facility</t>
+          <t>Mornington Waste Disposal Facility</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
@@ -11294,13 +11290,13 @@
         <v>1</v>
       </c>
       <c r="E180" s="5" t="n">
-        <v>1.0032</v>
+        <v>0.9923999999999999</v>
       </c>
       <c r="F180" s="5" t="n">
-        <v>1.0068</v>
+        <v>0.9925</v>
       </c>
       <c r="G180" s="5" t="n">
-        <v>1.0084</v>
+        <v>0.9963</v>
       </c>
       <c r="H180" s="5" t="inlineStr"/>
       <c r="I180" s="5" t="inlineStr"/>
@@ -11322,45 +11318,41 @@
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>CORIO1</t>
+          <t>BERWICK</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>Corio Landfill Gas Power Station</t>
-        </is>
-      </c>
-      <c r="C181" s="3" t="inlineStr">
-        <is>
-          <t>Other Renewable</t>
-        </is>
-      </c>
+          <t>Berwick Power Plant</t>
+        </is>
+      </c>
+      <c r="C181" s="3" t="inlineStr"/>
       <c r="D181" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E181" s="5" t="n">
-        <v>0.9987</v>
+        <v>0.9923</v>
       </c>
       <c r="F181" s="5" t="n">
-        <v>1.0048</v>
+        <v>0.9923</v>
       </c>
       <c r="G181" s="5" t="n">
-        <v>1.0055</v>
+        <v>0.9923</v>
       </c>
       <c r="H181" s="5" t="n">
-        <v>1.0002</v>
+        <v>0.9923</v>
       </c>
       <c r="I181" s="5" t="n">
-        <v>0.9908</v>
+        <v>0.9923</v>
       </c>
       <c r="J181" s="5" t="n">
-        <v>0.9913999999999999</v>
+        <v>0.9923</v>
       </c>
       <c r="K181" s="5" t="n">
-        <v>0.9918</v>
+        <v>0.9923</v>
       </c>
       <c r="L181" s="5" t="n">
-        <v>0.9933</v>
+        <v>0.9923</v>
       </c>
       <c r="M181" s="5" t="inlineStr"/>
       <c r="N181" s="5" t="inlineStr"/>
@@ -11377,41 +11369,45 @@
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>BERWICK</t>
+          <t>CORIO1</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>Berwick Power Plant</t>
-        </is>
-      </c>
-      <c r="C182" s="3" t="inlineStr"/>
+          <t>Corio Landfill Gas Power Station</t>
+        </is>
+      </c>
+      <c r="C182" s="3" t="inlineStr">
+        <is>
+          <t>Other Renewable</t>
+        </is>
+      </c>
       <c r="D182" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>0.9923</v>
+        <v>0.9987</v>
       </c>
       <c r="F182" s="5" t="n">
-        <v>0.9923</v>
+        <v>1.0048</v>
       </c>
       <c r="G182" s="5" t="n">
-        <v>0.9923</v>
+        <v>1.0055</v>
       </c>
       <c r="H182" s="5" t="n">
-        <v>0.9923</v>
+        <v>1.0002</v>
       </c>
       <c r="I182" s="5" t="n">
-        <v>0.9923</v>
+        <v>0.9908</v>
       </c>
       <c r="J182" s="5" t="n">
-        <v>0.9923</v>
+        <v>0.9913999999999999</v>
       </c>
       <c r="K182" s="5" t="n">
-        <v>0.9923</v>
+        <v>0.9918</v>
       </c>
       <c r="L182" s="5" t="n">
-        <v>0.9923</v>
+        <v>0.9933</v>
       </c>
       <c r="M182" s="5" t="inlineStr"/>
       <c r="N182" s="5" t="inlineStr"/>
@@ -11428,12 +11424,12 @@
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t>BROADMDW</t>
+          <t>SVALE1</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>Broadmeadows Landfill Gas Power Station</t>
+          <t>Springvale Landfill Gas Power Station</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
@@ -11445,31 +11441,31 @@
         <v>5</v>
       </c>
       <c r="E183" s="5" t="n">
-        <v>1</v>
+        <v>0.997</v>
       </c>
       <c r="F183" s="5" t="n">
-        <v>1</v>
+        <v>0.9972</v>
       </c>
       <c r="G183" s="5" t="n">
-        <v>1</v>
+        <v>0.9989</v>
       </c>
       <c r="H183" s="5" t="n">
-        <v>1</v>
+        <v>0.9986</v>
       </c>
       <c r="I183" s="5" t="n">
-        <v>1</v>
+        <v>0.9987</v>
       </c>
       <c r="J183" s="5" t="n">
-        <v>1</v>
+        <v>0.9984</v>
       </c>
       <c r="K183" s="5" t="n">
-        <v>1</v>
+        <v>0.9957</v>
       </c>
       <c r="L183" s="5" t="n">
-        <v>1</v>
+        <v>0.9972</v>
       </c>
       <c r="M183" s="5" t="n">
-        <v>1</v>
+        <v>1.0001</v>
       </c>
       <c r="N183" s="5" t="inlineStr"/>
       <c r="O183" s="5" t="inlineStr"/>
@@ -11485,12 +11481,12 @@
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>SVALE1</t>
+          <t>BROADMDW</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>Springvale Landfill Gas Power Station</t>
+          <t>Broadmeadows Landfill Gas Power Station</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
@@ -11502,31 +11498,31 @@
         <v>5</v>
       </c>
       <c r="E184" s="5" t="n">
-        <v>0.997</v>
+        <v>1</v>
       </c>
       <c r="F184" s="5" t="n">
-        <v>0.9972</v>
+        <v>1</v>
       </c>
       <c r="G184" s="5" t="n">
-        <v>0.9989</v>
+        <v>1</v>
       </c>
       <c r="H184" s="5" t="n">
-        <v>0.9986</v>
+        <v>1</v>
       </c>
       <c r="I184" s="5" t="n">
-        <v>0.9987</v>
+        <v>1</v>
       </c>
       <c r="J184" s="5" t="n">
-        <v>0.9984</v>
+        <v>1</v>
       </c>
       <c r="K184" s="5" t="n">
-        <v>0.9957</v>
+        <v>1</v>
       </c>
       <c r="L184" s="5" t="n">
-        <v>0.9972</v>
+        <v>1</v>
       </c>
       <c r="M184" s="5" t="n">
-        <v>1.0001</v>
+        <v>1</v>
       </c>
       <c r="N184" s="5" t="inlineStr"/>
       <c r="O184" s="5" t="inlineStr"/>
@@ -11542,12 +11538,12 @@
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
         <is>
-          <t>VBBG1</t>
+          <t>PIBESSG1</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>Victorian Big Battery</t>
+          <t>Phillip Island BESS</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
@@ -11556,7 +11552,7 @@
         </is>
       </c>
       <c r="D185" s="4" t="n">
-        <v>360</v>
+        <v>7</v>
       </c>
       <c r="E185" s="5" t="inlineStr"/>
       <c r="F185" s="5" t="inlineStr"/>
@@ -11564,17 +11560,15 @@
       <c r="H185" s="5" t="inlineStr"/>
       <c r="I185" s="5" t="inlineStr"/>
       <c r="J185" s="5" t="inlineStr"/>
-      <c r="K185" s="5" t="n">
-        <v>0.982</v>
-      </c>
+      <c r="K185" s="5" t="inlineStr"/>
       <c r="L185" s="5" t="n">
+        <v>0.9977</v>
+      </c>
+      <c r="M185" s="5" t="n">
+        <v>0.9825</v>
+      </c>
+      <c r="N185" s="5" t="n">
         <v>0.9848</v>
-      </c>
-      <c r="M185" s="5" t="n">
-        <v>0.9885</v>
-      </c>
-      <c r="N185" s="5" t="n">
-        <v>0.9879</v>
       </c>
       <c r="O185" s="5" t="inlineStr"/>
       <c r="P185" s="5" t="inlineStr"/>
@@ -11589,12 +11583,12 @@
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>HBESSG1</t>
+          <t>BULBESG1</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>Hazelwood Battery Energy Storage System</t>
+          <t>Bulgana Green Power Hub</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
@@ -11603,7 +11597,7 @@
         </is>
       </c>
       <c r="D186" s="4" t="n">
-        <v>200</v>
+        <v>24</v>
       </c>
       <c r="E186" s="5" t="inlineStr"/>
       <c r="F186" s="5" t="inlineStr"/>
@@ -11611,15 +11605,17 @@
       <c r="H186" s="5" t="inlineStr"/>
       <c r="I186" s="5" t="inlineStr"/>
       <c r="J186" s="5" t="inlineStr"/>
-      <c r="K186" s="5" t="inlineStr"/>
+      <c r="K186" s="5" t="n">
+        <v>0.8949</v>
+      </c>
       <c r="L186" s="5" t="n">
-        <v>0.9785</v>
+        <v>0.8839</v>
       </c>
       <c r="M186" s="5" t="n">
-        <v>0.9789</v>
+        <v>0.8821</v>
       </c>
       <c r="N186" s="5" t="n">
-        <v>0.9804</v>
+        <v>0.8733</v>
       </c>
       <c r="O186" s="5" t="inlineStr"/>
       <c r="P186" s="5" t="inlineStr"/>
@@ -11634,45 +11630,41 @@
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
         <is>
-          <t>GANNBG1</t>
+          <t>FNWF1</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>Gannawarra Energy Storage System</t>
+          <t>Ferguson North Wind Farm</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D187" s="4" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="E187" s="5" t="inlineStr"/>
       <c r="F187" s="5" t="inlineStr"/>
       <c r="G187" s="5" t="inlineStr"/>
-      <c r="H187" s="5" t="n">
-        <v>1.007</v>
-      </c>
-      <c r="I187" s="5" t="n">
-        <v>0.9643</v>
-      </c>
+      <c r="H187" s="5" t="inlineStr"/>
+      <c r="I187" s="5" t="inlineStr"/>
       <c r="J187" s="5" t="n">
-        <v>0.9792999999999999</v>
+        <v>1.0079</v>
       </c>
       <c r="K187" s="5" t="n">
-        <v>0.9772999999999999</v>
+        <v>1.0035</v>
       </c>
       <c r="L187" s="5" t="n">
-        <v>1.0026</v>
+        <v>0.9972</v>
       </c>
       <c r="M187" s="5" t="n">
-        <v>1.029</v>
+        <v>0.9933</v>
       </c>
       <c r="N187" s="5" t="n">
-        <v>1.0155</v>
+        <v>0.9993</v>
       </c>
       <c r="O187" s="5" t="inlineStr"/>
       <c r="P187" s="5" t="inlineStr"/>
@@ -11687,41 +11679,39 @@
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t>FNWF1</t>
+          <t>VBBG1</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>Ferguson North Wind Farm</t>
+          <t>Victorian Big Battery</t>
         </is>
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D188" s="4" t="n">
-        <v>4</v>
+        <v>360</v>
       </c>
       <c r="E188" s="5" t="inlineStr"/>
       <c r="F188" s="5" t="inlineStr"/>
       <c r="G188" s="5" t="inlineStr"/>
       <c r="H188" s="5" t="inlineStr"/>
       <c r="I188" s="5" t="inlineStr"/>
-      <c r="J188" s="5" t="n">
-        <v>1.0079</v>
-      </c>
+      <c r="J188" s="5" t="inlineStr"/>
       <c r="K188" s="5" t="n">
-        <v>1.0035</v>
+        <v>0.982</v>
       </c>
       <c r="L188" s="5" t="n">
-        <v>0.9972</v>
+        <v>0.9848</v>
       </c>
       <c r="M188" s="5" t="n">
-        <v>0.9933</v>
+        <v>0.9885</v>
       </c>
       <c r="N188" s="5" t="n">
-        <v>0.9993</v>
+        <v>0.9879</v>
       </c>
       <c r="O188" s="5" t="inlineStr"/>
       <c r="P188" s="5" t="inlineStr"/>
@@ -11736,12 +11726,12 @@
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
         <is>
-          <t>PIBESSG1</t>
+          <t>GANNBG1</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>Phillip Island BESS</t>
+          <t>Gannawarra Energy Storage System</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
@@ -11750,23 +11740,31 @@
         </is>
       </c>
       <c r="D189" s="4" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="E189" s="5" t="inlineStr"/>
       <c r="F189" s="5" t="inlineStr"/>
       <c r="G189" s="5" t="inlineStr"/>
-      <c r="H189" s="5" t="inlineStr"/>
-      <c r="I189" s="5" t="inlineStr"/>
-      <c r="J189" s="5" t="inlineStr"/>
-      <c r="K189" s="5" t="inlineStr"/>
+      <c r="H189" s="5" t="n">
+        <v>1.007</v>
+      </c>
+      <c r="I189" s="5" t="n">
+        <v>0.9643</v>
+      </c>
+      <c r="J189" s="5" t="n">
+        <v>0.9792999999999999</v>
+      </c>
+      <c r="K189" s="5" t="n">
+        <v>0.9772999999999999</v>
+      </c>
       <c r="L189" s="5" t="n">
-        <v>0.9977</v>
+        <v>1.0026</v>
       </c>
       <c r="M189" s="5" t="n">
-        <v>0.9825</v>
+        <v>1.029</v>
       </c>
       <c r="N189" s="5" t="n">
-        <v>0.9848</v>
+        <v>1.0155</v>
       </c>
       <c r="O189" s="5" t="inlineStr"/>
       <c r="P189" s="5" t="inlineStr"/>
@@ -11781,12 +11779,12 @@
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t>BULBESG1</t>
+          <t>HBESSG1</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>Bulgana Green Power Hub</t>
+          <t>Hazelwood Battery Energy Storage System</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
@@ -11795,7 +11793,7 @@
         </is>
       </c>
       <c r="D190" s="4" t="n">
-        <v>24</v>
+        <v>200</v>
       </c>
       <c r="E190" s="5" t="inlineStr"/>
       <c r="F190" s="5" t="inlineStr"/>
@@ -11803,17 +11801,15 @@
       <c r="H190" s="5" t="inlineStr"/>
       <c r="I190" s="5" t="inlineStr"/>
       <c r="J190" s="5" t="inlineStr"/>
-      <c r="K190" s="5" t="n">
-        <v>0.8949</v>
-      </c>
+      <c r="K190" s="5" t="inlineStr"/>
       <c r="L190" s="5" t="n">
-        <v>0.8839</v>
+        <v>0.9785</v>
       </c>
       <c r="M190" s="5" t="n">
-        <v>0.8821</v>
+        <v>0.9789</v>
       </c>
       <c r="N190" s="5" t="n">
-        <v>0.8733</v>
+        <v>0.9804</v>
       </c>
       <c r="O190" s="5" t="inlineStr"/>
       <c r="P190" s="5" t="inlineStr"/>
@@ -12299,23 +12295,15 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>KIATAWF1</t>
+          <t>DIAPURWF1</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr"/>
       <c r="C7" s="5" t="inlineStr"/>
-      <c r="D7" s="5" t="n">
-        <v>1.0357</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>0.9911</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>0.9066</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>0.8974</v>
-      </c>
+      <c r="D7" s="5" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr"/>
       <c r="H7" s="5" t="n">
         <v>0.9005</v>
       </c>
@@ -12341,15 +12329,23 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>DIAPURWF1</t>
+          <t>KIATAWF1</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr"/>
       <c r="C8" s="5" t="inlineStr"/>
-      <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="5" t="inlineStr"/>
-      <c r="F8" s="5" t="inlineStr"/>
-      <c r="G8" s="5" t="inlineStr"/>
+      <c r="D8" s="5" t="n">
+        <v>1.0357</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.9911</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>0.9066</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>0.8974</v>
+      </c>
       <c r="H8" s="5" t="n">
         <v>0.9005</v>
       </c>
@@ -12487,14 +12483,18 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>YATSF1</t>
+          <t>KARSF1</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr"/>
       <c r="C12" s="5" t="inlineStr"/>
       <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="n">
+        <v>0.9472</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0.8097</v>
+      </c>
       <c r="G12" s="5" t="n">
         <v>0.8045</v>
       </c>
@@ -12523,18 +12523,14 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>KARSF1</t>
+          <t>YATSF1</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr"/>
       <c r="C13" s="5" t="inlineStr"/>
       <c r="D13" s="5" t="inlineStr"/>
-      <c r="E13" s="5" t="n">
-        <v>0.9472</v>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>0.8097</v>
-      </c>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr"/>
       <c r="G13" s="5" t="n">
         <v>0.8045</v>
       </c>
@@ -12563,7 +12559,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>BANN1</t>
+          <t>WEMENSF1</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr"/>
@@ -12603,7 +12599,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>WEMENSF1</t>
+          <t>BANN1</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr"/>
@@ -12643,30 +12639,18 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>NUMURSF1</t>
+          <t>GIRGSF</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr"/>
       <c r="C16" s="5" t="inlineStr"/>
       <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="n">
-        <v>0.982</v>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>0.9896</v>
-      </c>
-      <c r="G16" s="5" t="n">
-        <v>0.9945000000000001</v>
-      </c>
-      <c r="H16" s="5" t="n">
-        <v>0.9963</v>
-      </c>
-      <c r="I16" s="5" t="n">
-        <v>0.9715</v>
-      </c>
-      <c r="J16" s="5" t="n">
-        <v>0.9738</v>
-      </c>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr"/>
       <c r="K16" s="5" t="n">
         <v>0.9477</v>
       </c>
@@ -12683,18 +12667,30 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>WUNUSF1</t>
+          <t>NUMURSF1</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr"/>
       <c r="C17" s="5" t="inlineStr"/>
       <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>0.9896</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0.9945000000000001</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>0.9963</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>0.9715</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>0.9738</v>
+      </c>
       <c r="K17" s="5" t="n">
         <v>0.9477</v>
       </c>
@@ -12711,7 +12707,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>LANCSF1</t>
+          <t>WUNUSF1</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr"/>
@@ -12723,10 +12719,12 @@
       <c r="H18" s="5" t="inlineStr"/>
       <c r="I18" s="5" t="inlineStr"/>
       <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="n">
+        <v>0.9477</v>
+      </c>
       <c r="L18" s="5" t="inlineStr"/>
       <c r="M18" s="5" t="n">
-        <v>0.9441000000000001</v>
+        <v>0.9463</v>
       </c>
       <c r="N18" s="5" t="inlineStr"/>
       <c r="O18" s="5" t="n">
@@ -12737,7 +12735,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>GIRGSF</t>
+          <t>LANCSF1</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr"/>
@@ -12749,12 +12747,10 @@
       <c r="H19" s="5" t="inlineStr"/>
       <c r="I19" s="5" t="inlineStr"/>
       <c r="J19" s="5" t="inlineStr"/>
-      <c r="K19" s="5" t="n">
-        <v>0.9477</v>
-      </c>
+      <c r="K19" s="5" t="inlineStr"/>
       <c r="L19" s="5" t="inlineStr"/>
       <c r="M19" s="5" t="n">
-        <v>0.9463</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="N19" s="5" t="inlineStr"/>
       <c r="O19" s="5" t="n">
@@ -12765,7 +12761,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>WINTSF1</t>
+          <t>GLRWNSF1</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr"/>
@@ -12801,7 +12797,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>GLRWNSF1</t>
+          <t>WINTSF1</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr"/>
@@ -13101,7 +13097,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>BRYB1WF1</t>
+          <t>BRYB2WF2</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr"/>
@@ -13109,12 +13105,8 @@
       <c r="D30" s="5" t="inlineStr"/>
       <c r="E30" s="5" t="inlineStr"/>
       <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="n">
-        <v>0.9482</v>
-      </c>
-      <c r="H30" s="5" t="n">
-        <v>0.9431</v>
-      </c>
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr"/>
       <c r="I30" s="5" t="n">
         <v>0.9496</v>
       </c>
@@ -13137,7 +13129,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>BRYB2WF2</t>
+          <t>BRYB1WF1</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr"/>
@@ -13145,8 +13137,12 @@
       <c r="D31" s="5" t="inlineStr"/>
       <c r="E31" s="5" t="inlineStr"/>
       <c r="F31" s="5" t="inlineStr"/>
-      <c r="G31" s="5" t="inlineStr"/>
-      <c r="H31" s="5" t="inlineStr"/>
+      <c r="G31" s="5" t="n">
+        <v>0.9482</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>0.9431</v>
+      </c>
       <c r="I31" s="5" t="n">
         <v>0.9496</v>
       </c>
@@ -13429,24 +13425,14 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>MERCER01</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="n">
-        <v>1.0033</v>
-      </c>
-      <c r="C39" s="5" t="n">
-        <v>1.0048</v>
-      </c>
-      <c r="D39" s="5" t="n">
-        <v>1.001</v>
-      </c>
-      <c r="E39" s="5" t="n">
-        <v>0.9909</v>
-      </c>
-      <c r="F39" s="5" t="n">
-        <v>0.965</v>
-      </c>
+          <t>MOORAWF1</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr"/>
+      <c r="C39" s="5" t="inlineStr"/>
+      <c r="D39" s="5" t="inlineStr"/>
+      <c r="E39" s="5" t="inlineStr"/>
+      <c r="F39" s="5" t="inlineStr"/>
       <c r="G39" s="5" t="n">
         <v>0.9500999999999999</v>
       </c>
@@ -13505,14 +13491,24 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>MOORAWF1</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="inlineStr"/>
-      <c r="C41" s="5" t="inlineStr"/>
-      <c r="D41" s="5" t="inlineStr"/>
-      <c r="E41" s="5" t="inlineStr"/>
-      <c r="F41" s="5" t="inlineStr"/>
+          <t>MERCER01</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>1.0033</v>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>1.0048</v>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>1.001</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>0.9909</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>0.965</v>
+      </c>
       <c r="G41" s="5" t="n">
         <v>0.9500999999999999</v>
       </c>
@@ -13541,7 +13537,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>MURAYNL2</t>
+          <t>MURAYNL3</t>
         </is>
       </c>
       <c r="B42" s="5" t="n">
@@ -13587,7 +13583,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>MURAYNL3</t>
+          <t>MURAYNL2</t>
         </is>
       </c>
       <c r="B43" s="5" t="n">
@@ -13633,7 +13629,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>MURRAY</t>
+          <t>MURAYNL1</t>
         </is>
       </c>
       <c r="B44" s="5" t="n">
@@ -13679,7 +13675,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>MURAYNL1</t>
+          <t>MURRAY</t>
         </is>
       </c>
       <c r="B45" s="5" t="n">
@@ -13817,7 +13813,7 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>YWNL1</t>
+          <t>YWPS4</t>
         </is>
       </c>
       <c r="B48" s="5" t="n">
@@ -13909,7 +13905,7 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>YWPS4</t>
+          <t>YWNL1</t>
         </is>
       </c>
       <c r="B50" s="5" t="n">
@@ -13955,7 +13951,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>BAPS</t>
+          <t>DARTM1</t>
         </is>
       </c>
       <c r="B51" s="5" t="n">
@@ -14001,7 +13997,7 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>DARTM1</t>
+          <t>BAPS</t>
         </is>
       </c>
       <c r="B52" s="5" t="n">
@@ -14169,11 +14165,15 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>YSWF1</t>
-        </is>
-      </c>
-      <c r="B56" s="5" t="inlineStr"/>
-      <c r="C56" s="5" t="inlineStr"/>
+          <t>HEPWIND1</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>1.0207</v>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>1.0209</v>
+      </c>
       <c r="D56" s="5" t="n">
         <v>1.016</v>
       </c>
@@ -14211,15 +14211,11 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>HEPWIND1</t>
-        </is>
-      </c>
-      <c r="B57" s="5" t="n">
-        <v>1.0207</v>
-      </c>
-      <c r="C57" s="5" t="n">
-        <v>1.0209</v>
-      </c>
+          <t>MAROOWF1</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr"/>
+      <c r="C57" s="5" t="inlineStr"/>
       <c r="D57" s="5" t="n">
         <v>1.016</v>
       </c>
@@ -14257,7 +14253,7 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>MAROOWF1</t>
+          <t>YSWF1</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr"/>
@@ -14299,7 +14295,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>MURR1-2</t>
+          <t>MURR1-4</t>
         </is>
       </c>
       <c r="B59" s="5" t="n">
@@ -14345,7 +14341,7 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>MURR1-1</t>
+          <t>MURR1-3</t>
         </is>
       </c>
       <c r="B60" s="5" t="n">
@@ -14391,7 +14387,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>MURR1-4</t>
+          <t>MURR1-2</t>
         </is>
       </c>
       <c r="B61" s="5" t="n">
@@ -14437,7 +14433,7 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>MURR2-1</t>
+          <t>MURR1-10</t>
         </is>
       </c>
       <c r="B62" s="5" t="n">
@@ -14483,7 +14479,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>MURR1-9</t>
+          <t>MURR1-1</t>
         </is>
       </c>
       <c r="B63" s="5" t="n">
@@ -14529,7 +14525,7 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>MURR1-10</t>
+          <t>MURR1-7</t>
         </is>
       </c>
       <c r="B64" s="5" t="n">
@@ -14575,7 +14571,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>MURR1-8</t>
+          <t>MURR1-6</t>
         </is>
       </c>
       <c r="B65" s="5" t="n">
@@ -14621,7 +14617,7 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>MURR1-3</t>
+          <t>MURR1-5</t>
         </is>
       </c>
       <c r="B66" s="5" t="n">
@@ -14667,7 +14663,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>MURR1-6</t>
+          <t>MURR1-8</t>
         </is>
       </c>
       <c r="B67" s="5" t="n">
@@ -14713,7 +14709,7 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>MURR1-5</t>
+          <t>MURR2-2</t>
         </is>
       </c>
       <c r="B68" s="5" t="n">
@@ -14759,7 +14755,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>MURR2-2</t>
+          <t>MURR2-1</t>
         </is>
       </c>
       <c r="B69" s="5" t="n">
@@ -14805,7 +14801,7 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>MURR2-3</t>
+          <t>MURR1-9</t>
         </is>
       </c>
       <c r="B70" s="5" t="n">
@@ -14851,7 +14847,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>MURR2-4</t>
+          <t>MURR2-3</t>
         </is>
       </c>
       <c r="B71" s="5" t="n">
@@ -14897,7 +14893,7 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>MURR1-7</t>
+          <t>MURR2-4</t>
         </is>
       </c>
       <c r="B72" s="5" t="n">
@@ -14977,7 +14973,7 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>GPWFEST3</t>
+          <t>GPWFEST2</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr"/>
@@ -15005,7 +15001,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>GPWFEST2</t>
+          <t>GPWFEST1</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr"/>
@@ -15033,7 +15029,7 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>GPWFEST1</t>
+          <t>GPWFEST3</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr"/>
@@ -15117,42 +15113,22 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>JLA04</t>
-        </is>
-      </c>
-      <c r="B79" s="5" t="n">
-        <v>0.9667</v>
-      </c>
-      <c r="C79" s="5" t="n">
-        <v>0.9641</v>
-      </c>
-      <c r="D79" s="5" t="n">
-        <v>0.983</v>
-      </c>
-      <c r="E79" s="5" t="n">
-        <v>0.9782999999999999</v>
-      </c>
-      <c r="F79" s="5" t="n">
-        <v>0.9731</v>
-      </c>
-      <c r="G79" s="5" t="n">
-        <v>0.9734</v>
-      </c>
-      <c r="H79" s="5" t="n">
-        <v>0.9755</v>
-      </c>
-      <c r="I79" s="5" t="n">
-        <v>0.9727</v>
-      </c>
-      <c r="J79" s="5" t="n">
-        <v>0.9764</v>
-      </c>
-      <c r="K79" s="5" t="n">
-        <v>0.9789</v>
-      </c>
+          <t>GPWFWST2</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr"/>
+      <c r="C79" s="5" t="inlineStr"/>
+      <c r="D79" s="5" t="inlineStr"/>
+      <c r="E79" s="5" t="inlineStr"/>
+      <c r="F79" s="5" t="inlineStr"/>
+      <c r="G79" s="5" t="inlineStr"/>
+      <c r="H79" s="5" t="inlineStr"/>
+      <c r="I79" s="5" t="inlineStr"/>
+      <c r="J79" s="5" t="inlineStr"/>
+      <c r="K79" s="5" t="inlineStr"/>
       <c r="L79" s="5" t="inlineStr"/>
       <c r="M79" s="5" t="n">
-        <v>0.9768</v>
+        <v>0.9837</v>
       </c>
       <c r="N79" s="5" t="inlineStr"/>
       <c r="O79" s="5" t="n">
@@ -15163,42 +15139,22 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>JLA03</t>
-        </is>
-      </c>
-      <c r="B80" s="5" t="n">
-        <v>0.9667</v>
-      </c>
-      <c r="C80" s="5" t="n">
-        <v>0.9641</v>
-      </c>
-      <c r="D80" s="5" t="n">
-        <v>0.983</v>
-      </c>
-      <c r="E80" s="5" t="n">
-        <v>0.9782999999999999</v>
-      </c>
-      <c r="F80" s="5" t="n">
-        <v>0.9731</v>
-      </c>
-      <c r="G80" s="5" t="n">
-        <v>0.9734</v>
-      </c>
-      <c r="H80" s="5" t="n">
-        <v>0.9755</v>
-      </c>
-      <c r="I80" s="5" t="n">
-        <v>0.9727</v>
-      </c>
-      <c r="J80" s="5" t="n">
-        <v>0.9764</v>
-      </c>
-      <c r="K80" s="5" t="n">
-        <v>0.9789</v>
-      </c>
+          <t>GPWFWST1</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr"/>
+      <c r="C80" s="5" t="inlineStr"/>
+      <c r="D80" s="5" t="inlineStr"/>
+      <c r="E80" s="5" t="inlineStr"/>
+      <c r="F80" s="5" t="inlineStr"/>
+      <c r="G80" s="5" t="inlineStr"/>
+      <c r="H80" s="5" t="inlineStr"/>
+      <c r="I80" s="5" t="inlineStr"/>
+      <c r="J80" s="5" t="inlineStr"/>
+      <c r="K80" s="5" t="inlineStr"/>
       <c r="L80" s="5" t="inlineStr"/>
       <c r="M80" s="5" t="n">
-        <v>0.9768</v>
+        <v>0.9837</v>
       </c>
       <c r="N80" s="5" t="inlineStr"/>
       <c r="O80" s="5" t="n">
@@ -15255,7 +15211,7 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>JLA02</t>
+          <t>JLA04</t>
         </is>
       </c>
       <c r="B82" s="5" t="n">
@@ -15301,7 +15257,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>JLB01</t>
+          <t>JLA03</t>
         </is>
       </c>
       <c r="B83" s="5" t="n">
@@ -15347,7 +15303,7 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>JLB02</t>
+          <t>JLA02</t>
         </is>
       </c>
       <c r="B84" s="5" t="n">
@@ -15439,22 +15395,42 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>GPWFWST1</t>
-        </is>
-      </c>
-      <c r="B86" s="5" t="inlineStr"/>
-      <c r="C86" s="5" t="inlineStr"/>
-      <c r="D86" s="5" t="inlineStr"/>
-      <c r="E86" s="5" t="inlineStr"/>
-      <c r="F86" s="5" t="inlineStr"/>
-      <c r="G86" s="5" t="inlineStr"/>
-      <c r="H86" s="5" t="inlineStr"/>
-      <c r="I86" s="5" t="inlineStr"/>
-      <c r="J86" s="5" t="inlineStr"/>
-      <c r="K86" s="5" t="inlineStr"/>
+          <t>JLB02</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="n">
+        <v>0.9667</v>
+      </c>
+      <c r="C86" s="5" t="n">
+        <v>0.9641</v>
+      </c>
+      <c r="D86" s="5" t="n">
+        <v>0.983</v>
+      </c>
+      <c r="E86" s="5" t="n">
+        <v>0.9782999999999999</v>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>0.9731</v>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>0.9734</v>
+      </c>
+      <c r="H86" s="5" t="n">
+        <v>0.9755</v>
+      </c>
+      <c r="I86" s="5" t="n">
+        <v>0.9727</v>
+      </c>
+      <c r="J86" s="5" t="n">
+        <v>0.9764</v>
+      </c>
+      <c r="K86" s="5" t="n">
+        <v>0.9789</v>
+      </c>
       <c r="L86" s="5" t="inlineStr"/>
       <c r="M86" s="5" t="n">
-        <v>0.9837</v>
+        <v>0.9768</v>
       </c>
       <c r="N86" s="5" t="inlineStr"/>
       <c r="O86" s="5" t="n">
@@ -15465,22 +15441,42 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>GPWFWST2</t>
-        </is>
-      </c>
-      <c r="B87" s="5" t="inlineStr"/>
-      <c r="C87" s="5" t="inlineStr"/>
-      <c r="D87" s="5" t="inlineStr"/>
-      <c r="E87" s="5" t="inlineStr"/>
-      <c r="F87" s="5" t="inlineStr"/>
-      <c r="G87" s="5" t="inlineStr"/>
-      <c r="H87" s="5" t="inlineStr"/>
-      <c r="I87" s="5" t="inlineStr"/>
-      <c r="J87" s="5" t="inlineStr"/>
-      <c r="K87" s="5" t="inlineStr"/>
+          <t>JLB01</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="n">
+        <v>0.9667</v>
+      </c>
+      <c r="C87" s="5" t="n">
+        <v>0.9641</v>
+      </c>
+      <c r="D87" s="5" t="n">
+        <v>0.983</v>
+      </c>
+      <c r="E87" s="5" t="n">
+        <v>0.9782999999999999</v>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>0.9731</v>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>0.9734</v>
+      </c>
+      <c r="H87" s="5" t="n">
+        <v>0.9755</v>
+      </c>
+      <c r="I87" s="5" t="n">
+        <v>0.9727</v>
+      </c>
+      <c r="J87" s="5" t="n">
+        <v>0.9764</v>
+      </c>
+      <c r="K87" s="5" t="n">
+        <v>0.9789</v>
+      </c>
       <c r="L87" s="5" t="inlineStr"/>
       <c r="M87" s="5" t="n">
-        <v>0.9837</v>
+        <v>0.9768</v>
       </c>
       <c r="N87" s="5" t="inlineStr"/>
       <c r="O87" s="5" t="n">
@@ -15537,26 +15533,30 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>STOCKYD1</t>
+          <t>DUNDWF3</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr"/>
       <c r="C89" s="5" t="inlineStr"/>
       <c r="D89" s="5" t="inlineStr"/>
       <c r="E89" s="5" t="inlineStr"/>
-      <c r="F89" s="5" t="inlineStr"/>
-      <c r="G89" s="5" t="inlineStr"/>
+      <c r="F89" s="5" t="n">
+        <v>0.9812</v>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>0.979</v>
+      </c>
       <c r="H89" s="5" t="n">
-        <v>0.9782</v>
+        <v>0.9789</v>
       </c>
       <c r="I89" s="5" t="n">
-        <v>0.9799</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="J89" s="5" t="n">
-        <v>0.9869</v>
+        <v>0.987</v>
       </c>
       <c r="K89" s="5" t="n">
-        <v>0.9812</v>
+        <v>0.981</v>
       </c>
       <c r="L89" s="5" t="inlineStr"/>
       <c r="M89" s="5" t="n">
@@ -15571,7 +15571,7 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>DUNDWF3</t>
+          <t>DUNDWF2</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr"/>
@@ -15609,7 +15609,7 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>DUNDWF2</t>
+          <t>DUNDWF1</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr"/>
@@ -15647,30 +15647,26 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>DUNDWF1</t>
+          <t>STOCKYD1</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr"/>
       <c r="C92" s="5" t="inlineStr"/>
       <c r="D92" s="5" t="inlineStr"/>
       <c r="E92" s="5" t="inlineStr"/>
-      <c r="F92" s="5" t="n">
+      <c r="F92" s="5" t="inlineStr"/>
+      <c r="G92" s="5" t="inlineStr"/>
+      <c r="H92" s="5" t="n">
+        <v>0.9782</v>
+      </c>
+      <c r="I92" s="5" t="n">
+        <v>0.9799</v>
+      </c>
+      <c r="J92" s="5" t="n">
+        <v>0.9869</v>
+      </c>
+      <c r="K92" s="5" t="n">
         <v>0.9812</v>
-      </c>
-      <c r="G92" s="5" t="n">
-        <v>0.979</v>
-      </c>
-      <c r="H92" s="5" t="n">
-        <v>0.9789</v>
-      </c>
-      <c r="I92" s="5" t="n">
-        <v>0.9824000000000001</v>
-      </c>
-      <c r="J92" s="5" t="n">
-        <v>0.987</v>
-      </c>
-      <c r="K92" s="5" t="n">
-        <v>0.981</v>
       </c>
       <c r="L92" s="5" t="inlineStr"/>
       <c r="M92" s="5" t="n">
@@ -15713,7 +15709,7 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>LYNL1</t>
+          <t>VPGS6</t>
         </is>
       </c>
       <c r="B94" s="5" t="n">
@@ -15759,7 +15755,7 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>LYA4</t>
+          <t>VPGS5</t>
         </is>
       </c>
       <c r="B95" s="5" t="n">
@@ -15805,7 +15801,7 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>VPGS6</t>
+          <t>VPGS4</t>
         </is>
       </c>
       <c r="B96" s="5" t="n">
@@ -15851,36 +15847,48 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>HBESS1</t>
-        </is>
-      </c>
-      <c r="B97" s="5" t="inlineStr"/>
-      <c r="C97" s="5" t="inlineStr"/>
-      <c r="D97" s="5" t="inlineStr"/>
-      <c r="E97" s="5" t="inlineStr"/>
-      <c r="F97" s="5" t="inlineStr"/>
-      <c r="G97" s="5" t="inlineStr"/>
-      <c r="H97" s="5" t="inlineStr"/>
-      <c r="I97" s="5" t="inlineStr"/>
-      <c r="J97" s="5" t="inlineStr"/>
+          <t>VPGS3</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="n">
+        <v>0.9742</v>
+      </c>
+      <c r="C97" s="5" t="n">
+        <v>0.9723000000000001</v>
+      </c>
+      <c r="D97" s="5" t="n">
+        <v>0.9801</v>
+      </c>
+      <c r="E97" s="5" t="n">
+        <v>0.9798</v>
+      </c>
+      <c r="F97" s="5" t="n">
+        <v>0.9754</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>0.976</v>
+      </c>
+      <c r="H97" s="5" t="n">
+        <v>0.9759</v>
+      </c>
+      <c r="I97" s="5" t="n">
+        <v>0.9782999999999999</v>
+      </c>
+      <c r="J97" s="5" t="n">
+        <v>0.9782</v>
+      </c>
       <c r="K97" s="5" t="n">
-        <v>0.9804</v>
-      </c>
-      <c r="L97" s="5" t="n">
-        <v>0.9864000000000001</v>
-      </c>
+        <v>0.9809</v>
+      </c>
+      <c r="L97" s="5" t="inlineStr"/>
       <c r="M97" s="5" t="n">
-        <v>0.9802</v>
-      </c>
-      <c r="N97" s="5" t="n">
-        <v>0.9873</v>
-      </c>
+        <v>0.9815</v>
+      </c>
+      <c r="N97" s="5" t="inlineStr"/>
       <c r="O97" s="5" t="n">
         <v>0.9834000000000001</v>
       </c>
-      <c r="P97" s="5" t="n">
-        <v>0.9873</v>
-      </c>
+      <c r="P97" s="5" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
@@ -15977,53 +15985,41 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>LYA3</t>
-        </is>
-      </c>
-      <c r="B100" s="5" t="n">
-        <v>0.9742</v>
-      </c>
-      <c r="C100" s="5" t="n">
-        <v>0.9723000000000001</v>
-      </c>
-      <c r="D100" s="5" t="n">
-        <v>0.9801</v>
-      </c>
-      <c r="E100" s="5" t="n">
-        <v>0.9798</v>
-      </c>
-      <c r="F100" s="5" t="n">
-        <v>0.9754</v>
-      </c>
-      <c r="G100" s="5" t="n">
-        <v>0.976</v>
-      </c>
-      <c r="H100" s="5" t="n">
-        <v>0.9759</v>
-      </c>
-      <c r="I100" s="5" t="n">
-        <v>0.9782999999999999</v>
-      </c>
-      <c r="J100" s="5" t="n">
-        <v>0.9782</v>
-      </c>
+          <t>HBESS1</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="inlineStr"/>
+      <c r="C100" s="5" t="inlineStr"/>
+      <c r="D100" s="5" t="inlineStr"/>
+      <c r="E100" s="5" t="inlineStr"/>
+      <c r="F100" s="5" t="inlineStr"/>
+      <c r="G100" s="5" t="inlineStr"/>
+      <c r="H100" s="5" t="inlineStr"/>
+      <c r="I100" s="5" t="inlineStr"/>
+      <c r="J100" s="5" t="inlineStr"/>
       <c r="K100" s="5" t="n">
-        <v>0.9809</v>
-      </c>
-      <c r="L100" s="5" t="inlineStr"/>
+        <v>0.9804</v>
+      </c>
+      <c r="L100" s="5" t="n">
+        <v>0.9864000000000001</v>
+      </c>
       <c r="M100" s="5" t="n">
-        <v>0.9815</v>
-      </c>
-      <c r="N100" s="5" t="inlineStr"/>
+        <v>0.9802</v>
+      </c>
+      <c r="N100" s="5" t="n">
+        <v>0.9873</v>
+      </c>
       <c r="O100" s="5" t="n">
         <v>0.9834000000000001</v>
       </c>
-      <c r="P100" s="5" t="inlineStr"/>
+      <c r="P100" s="5" t="n">
+        <v>0.9873</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>VPGS3</t>
+          <t>LYNL1</t>
         </is>
       </c>
       <c r="B101" s="5" t="n">
@@ -16069,7 +16065,7 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>LYA2</t>
+          <t>LYA4</t>
         </is>
       </c>
       <c r="B102" s="5" t="n">
@@ -16115,7 +16111,7 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>LYA1</t>
+          <t>LYA3</t>
         </is>
       </c>
       <c r="B103" s="5" t="n">
@@ -16161,7 +16157,7 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>LOYYB1</t>
+          <t>LYA2</t>
         </is>
       </c>
       <c r="B104" s="5" t="n">
@@ -16207,7 +16203,7 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>VPGS5</t>
+          <t>LYA1</t>
         </is>
       </c>
       <c r="B105" s="5" t="n">
@@ -16253,7 +16249,7 @@
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>VPGS4</t>
+          <t>LOYYB2</t>
         </is>
       </c>
       <c r="B106" s="5" t="n">
@@ -16299,7 +16295,7 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>LOYYB2</t>
+          <t>LOYYB1</t>
         </is>
       </c>
       <c r="B107" s="5" t="n">
@@ -16483,7 +16479,7 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>WKIEWA2</t>
+          <t>WKIEWA1</t>
         </is>
       </c>
       <c r="B111" s="5" t="n">
@@ -16529,7 +16525,7 @@
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>WKIEWA1</t>
+          <t>WKIEWA2</t>
         </is>
       </c>
       <c r="B112" s="5" t="n">
@@ -16685,53 +16681,37 @@
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>BDL02</t>
-        </is>
-      </c>
-      <c r="B116" s="5" t="n">
-        <v>0.9771</v>
-      </c>
-      <c r="C116" s="5" t="n">
-        <v>0.9745</v>
-      </c>
-      <c r="D116" s="5" t="n">
-        <v>0.9863</v>
-      </c>
-      <c r="E116" s="5" t="n">
-        <v>0.9866</v>
-      </c>
-      <c r="F116" s="5" t="n">
-        <v>0.9871</v>
-      </c>
-      <c r="G116" s="5" t="n">
-        <v>0.9899</v>
-      </c>
-      <c r="H116" s="5" t="n">
-        <v>0.9874000000000001</v>
-      </c>
-      <c r="I116" s="5" t="n">
-        <v>0.9913</v>
-      </c>
-      <c r="J116" s="5" t="n">
-        <v>0.9804</v>
-      </c>
-      <c r="K116" s="5" t="n">
-        <v>0.9816</v>
-      </c>
+          <t>MLB01</t>
+        </is>
+      </c>
+      <c r="B116" s="5" t="inlineStr"/>
+      <c r="C116" s="5" t="inlineStr"/>
+      <c r="D116" s="5" t="inlineStr"/>
+      <c r="E116" s="5" t="inlineStr"/>
+      <c r="F116" s="5" t="inlineStr"/>
+      <c r="G116" s="5" t="inlineStr"/>
+      <c r="H116" s="5" t="inlineStr"/>
+      <c r="I116" s="5" t="inlineStr"/>
+      <c r="J116" s="5" t="inlineStr"/>
+      <c r="K116" s="5" t="inlineStr"/>
       <c r="L116" s="5" t="inlineStr"/>
       <c r="M116" s="5" t="n">
-        <v>0.9816</v>
-      </c>
-      <c r="N116" s="5" t="inlineStr"/>
+        <v>0.9945000000000001</v>
+      </c>
+      <c r="N116" s="5" t="n">
+        <v>0.9945000000000001</v>
+      </c>
       <c r="O116" s="5" t="n">
         <v>0.9893</v>
       </c>
-      <c r="P116" s="5" t="inlineStr"/>
+      <c r="P116" s="5" t="n">
+        <v>0.994</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>BDL01</t>
+          <t>BDL02</t>
         </is>
       </c>
       <c r="B117" s="5" t="n">
@@ -16777,32 +16757,48 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>MLB01</t>
-        </is>
-      </c>
-      <c r="B118" s="5" t="inlineStr"/>
-      <c r="C118" s="5" t="inlineStr"/>
-      <c r="D118" s="5" t="inlineStr"/>
-      <c r="E118" s="5" t="inlineStr"/>
-      <c r="F118" s="5" t="inlineStr"/>
-      <c r="G118" s="5" t="inlineStr"/>
-      <c r="H118" s="5" t="inlineStr"/>
-      <c r="I118" s="5" t="inlineStr"/>
-      <c r="J118" s="5" t="inlineStr"/>
-      <c r="K118" s="5" t="inlineStr"/>
+          <t>BDL01</t>
+        </is>
+      </c>
+      <c r="B118" s="5" t="n">
+        <v>0.9771</v>
+      </c>
+      <c r="C118" s="5" t="n">
+        <v>0.9745</v>
+      </c>
+      <c r="D118" s="5" t="n">
+        <v>0.9863</v>
+      </c>
+      <c r="E118" s="5" t="n">
+        <v>0.9866</v>
+      </c>
+      <c r="F118" s="5" t="n">
+        <v>0.9871</v>
+      </c>
+      <c r="G118" s="5" t="n">
+        <v>0.9899</v>
+      </c>
+      <c r="H118" s="5" t="n">
+        <v>0.9874000000000001</v>
+      </c>
+      <c r="I118" s="5" t="n">
+        <v>0.9913</v>
+      </c>
+      <c r="J118" s="5" t="n">
+        <v>0.9804</v>
+      </c>
+      <c r="K118" s="5" t="n">
+        <v>0.9816</v>
+      </c>
       <c r="L118" s="5" t="inlineStr"/>
       <c r="M118" s="5" t="n">
-        <v>0.9945000000000001</v>
-      </c>
-      <c r="N118" s="5" t="n">
-        <v>0.9945000000000001</v>
-      </c>
+        <v>0.9816</v>
+      </c>
+      <c r="N118" s="5" t="inlineStr"/>
       <c r="O118" s="5" t="n">
         <v>0.9893</v>
       </c>
-      <c r="P118" s="5" t="n">
-        <v>0.994</v>
-      </c>
+      <c r="P118" s="5" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
@@ -16837,7 +16833,7 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>MREHA1</t>
+          <t>MREHA2</t>
         </is>
       </c>
       <c r="B120" s="5" t="inlineStr"/>
@@ -16871,7 +16867,7 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>MREHA2</t>
+          <t>MREHA1</t>
         </is>
       </c>
       <c r="B121" s="5" t="inlineStr"/>
@@ -16935,7 +16931,7 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>TOORAWF</t>
+          <t>GLENMAG1</t>
         </is>
       </c>
       <c r="B123" s="5" t="n">
@@ -16981,7 +16977,7 @@
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>TGNSS1</t>
+          <t>WONWP</t>
         </is>
       </c>
       <c r="B124" s="5" t="n">
@@ -17027,87 +17023,87 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>LONGFORD</t>
-        </is>
-      </c>
-      <c r="B125" s="5" t="n">
-        <v>0.9799</v>
-      </c>
-      <c r="C125" s="5" t="n">
-        <v>0.9759</v>
-      </c>
-      <c r="D125" s="5" t="n">
-        <v>0.9886</v>
-      </c>
-      <c r="E125" s="5" t="n">
-        <v>0.9879</v>
-      </c>
-      <c r="F125" s="5" t="n">
-        <v>0.9938</v>
-      </c>
-      <c r="G125" s="5" t="n">
-        <v>0.9955000000000001</v>
-      </c>
-      <c r="H125" s="5" t="n">
-        <v>0.9936</v>
-      </c>
-      <c r="I125" s="5" t="n">
-        <v>0.9977</v>
-      </c>
-      <c r="J125" s="5" t="n">
-        <v>0.9825</v>
-      </c>
+          <t>PIBESS1</t>
+        </is>
+      </c>
+      <c r="B125" s="5" t="inlineStr"/>
+      <c r="C125" s="5" t="inlineStr"/>
+      <c r="D125" s="5" t="inlineStr"/>
+      <c r="E125" s="5" t="inlineStr"/>
+      <c r="F125" s="5" t="inlineStr"/>
+      <c r="G125" s="5" t="inlineStr"/>
+      <c r="H125" s="5" t="inlineStr"/>
+      <c r="I125" s="5" t="inlineStr"/>
+      <c r="J125" s="5" t="inlineStr"/>
       <c r="K125" s="5" t="n">
         <v>0.9848</v>
       </c>
-      <c r="L125" s="5" t="inlineStr"/>
+      <c r="L125" s="5" t="n">
+        <v>0.9848</v>
+      </c>
       <c r="M125" s="5" t="n">
         <v>0.9862</v>
       </c>
-      <c r="N125" s="5" t="inlineStr"/>
+      <c r="N125" s="5" t="n">
+        <v>0.9862</v>
+      </c>
       <c r="O125" s="5" t="n">
         <v>0.992</v>
       </c>
-      <c r="P125" s="5" t="inlineStr"/>
+      <c r="P125" s="5" t="n">
+        <v>0.992</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>PIBESS1</t>
-        </is>
-      </c>
-      <c r="B126" s="5" t="inlineStr"/>
-      <c r="C126" s="5" t="inlineStr"/>
-      <c r="D126" s="5" t="inlineStr"/>
-      <c r="E126" s="5" t="inlineStr"/>
-      <c r="F126" s="5" t="inlineStr"/>
-      <c r="G126" s="5" t="inlineStr"/>
-      <c r="H126" s="5" t="inlineStr"/>
-      <c r="I126" s="5" t="inlineStr"/>
-      <c r="J126" s="5" t="inlineStr"/>
+          <t>TGNSS1</t>
+        </is>
+      </c>
+      <c r="B126" s="5" t="n">
+        <v>0.9799</v>
+      </c>
+      <c r="C126" s="5" t="n">
+        <v>0.9759</v>
+      </c>
+      <c r="D126" s="5" t="n">
+        <v>0.9886</v>
+      </c>
+      <c r="E126" s="5" t="n">
+        <v>0.9879</v>
+      </c>
+      <c r="F126" s="5" t="n">
+        <v>0.9938</v>
+      </c>
+      <c r="G126" s="5" t="n">
+        <v>0.9955000000000001</v>
+      </c>
+      <c r="H126" s="5" t="n">
+        <v>0.9936</v>
+      </c>
+      <c r="I126" s="5" t="n">
+        <v>0.9977</v>
+      </c>
+      <c r="J126" s="5" t="n">
+        <v>0.9825</v>
+      </c>
       <c r="K126" s="5" t="n">
         <v>0.9848</v>
       </c>
-      <c r="L126" s="5" t="n">
-        <v>0.9848</v>
-      </c>
+      <c r="L126" s="5" t="inlineStr"/>
       <c r="M126" s="5" t="n">
         <v>0.9862</v>
       </c>
-      <c r="N126" s="5" t="n">
-        <v>0.9862</v>
-      </c>
+      <c r="N126" s="5" t="inlineStr"/>
       <c r="O126" s="5" t="n">
         <v>0.992</v>
       </c>
-      <c r="P126" s="5" t="n">
-        <v>0.992</v>
-      </c>
+      <c r="P126" s="5" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>BALDHWF1</t>
+          <t>TOORAWF</t>
         </is>
       </c>
       <c r="B127" s="5" t="n">
@@ -17153,7 +17149,7 @@
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>WONWP</t>
+          <t>BALDHWF1</t>
         </is>
       </c>
       <c r="B128" s="5" t="n">
@@ -17199,7 +17195,7 @@
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>GLENMAG1</t>
+          <t>LONGFORD</t>
         </is>
       </c>
       <c r="B129" s="5" t="n">
@@ -17325,24 +17321,14 @@
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>YAMBUKWF</t>
-        </is>
-      </c>
-      <c r="B132" s="5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="C132" s="5" t="n">
-        <v>1.0339</v>
-      </c>
-      <c r="D132" s="5" t="n">
-        <v>1.0322</v>
-      </c>
-      <c r="E132" s="5" t="n">
-        <v>1.0149</v>
-      </c>
-      <c r="F132" s="5" t="n">
-        <v>1.0019</v>
-      </c>
+          <t>FSWF1</t>
+        </is>
+      </c>
+      <c r="B132" s="5" t="inlineStr"/>
+      <c r="C132" s="5" t="inlineStr"/>
+      <c r="D132" s="5" t="inlineStr"/>
+      <c r="E132" s="5" t="inlineStr"/>
+      <c r="F132" s="5" t="inlineStr"/>
       <c r="G132" s="5" t="n">
         <v>1.0079</v>
       </c>
@@ -17371,7 +17357,7 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>OAKLAND1</t>
+          <t>CODRNGTON</t>
         </is>
       </c>
       <c r="B133" s="5" t="n">
@@ -17417,14 +17403,24 @@
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>FSWF1</t>
-        </is>
-      </c>
-      <c r="B134" s="5" t="inlineStr"/>
-      <c r="C134" s="5" t="inlineStr"/>
-      <c r="D134" s="5" t="inlineStr"/>
-      <c r="E134" s="5" t="inlineStr"/>
-      <c r="F134" s="5" t="inlineStr"/>
+          <t>OAKLAND1</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="C134" s="5" t="n">
+        <v>1.0339</v>
+      </c>
+      <c r="D134" s="5" t="n">
+        <v>1.0322</v>
+      </c>
+      <c r="E134" s="5" t="n">
+        <v>1.0149</v>
+      </c>
+      <c r="F134" s="5" t="n">
+        <v>1.0019</v>
+      </c>
       <c r="G134" s="5" t="n">
         <v>1.0079</v>
       </c>
@@ -17453,7 +17449,7 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>CODRNGTON</t>
+          <t>MLWF1</t>
         </is>
       </c>
       <c r="B135" s="5" t="n">
@@ -17499,7 +17495,7 @@
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>MLWF1</t>
+          <t>YAMBUKWF</t>
         </is>
       </c>
       <c r="B136" s="5" t="n">
@@ -18035,17 +18031,17 @@
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>WOLLERT1</t>
+          <t>RUBICON</t>
         </is>
       </c>
       <c r="B149" s="5" t="n">
-        <v>0.9987</v>
+        <v>1</v>
       </c>
       <c r="C149" s="5" t="n">
-        <v>0.9985000000000001</v>
+        <v>1</v>
       </c>
       <c r="D149" s="5" t="n">
-        <v>0.998</v>
+        <v>1</v>
       </c>
       <c r="E149" s="5" t="n">
         <v>0.9979</v>
@@ -18081,17 +18077,17 @@
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>RUBICON</t>
+          <t>EILDON3</t>
         </is>
       </c>
       <c r="B150" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C150" s="5" t="n">
-        <v>1</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="D150" s="5" t="n">
-        <v>1</v>
+        <v>0.998</v>
       </c>
       <c r="E150" s="5" t="n">
         <v>0.9979</v>
@@ -18127,11 +18123,11 @@
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>EILDON3</t>
+          <t>WOLLERT1</t>
         </is>
       </c>
       <c r="B151" s="5" t="n">
-        <v>1</v>
+        <v>0.9987</v>
       </c>
       <c r="C151" s="5" t="n">
         <v>0.9985000000000001</v>
@@ -18569,7 +18565,7 @@
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>SHEP1</t>
+          <t>TATURA01</t>
         </is>
       </c>
       <c r="B161" s="5" t="n">
@@ -18615,7 +18611,7 @@
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>TATURA01</t>
+          <t>SHEP1</t>
         </is>
       </c>
       <c r="B162" s="5" t="n">
@@ -18753,11 +18749,11 @@
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
         <is>
-          <t>MOR1</t>
+          <t>MOR3</t>
         </is>
       </c>
       <c r="B165" s="5" t="n">
-        <v>0.9704</v>
+        <v>0.9732</v>
       </c>
       <c r="C165" s="5" t="inlineStr"/>
       <c r="D165" s="5" t="inlineStr"/>
@@ -18801,11 +18797,11 @@
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
         <is>
-          <t>MOR3</t>
+          <t>MOR1</t>
         </is>
       </c>
       <c r="B167" s="5" t="n">
-        <v>0.9732</v>
+        <v>0.9704</v>
       </c>
       <c r="C167" s="5" t="inlineStr"/>
       <c r="D167" s="5" t="inlineStr"/>
@@ -18873,7 +18869,7 @@
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>HWPNL1</t>
+          <t>HWPS6</t>
         </is>
       </c>
       <c r="B170" s="5" t="n">
@@ -18899,7 +18895,7 @@
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>HWPS1</t>
+          <t>HWPS7</t>
         </is>
       </c>
       <c r="B171" s="5" t="n">
@@ -18925,7 +18921,7 @@
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>HWPS2</t>
+          <t>HWPS8</t>
         </is>
       </c>
       <c r="B172" s="5" t="n">
@@ -18951,7 +18947,7 @@
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>HWPS3</t>
+          <t>HWPS4</t>
         </is>
       </c>
       <c r="B173" s="5" t="n">
@@ -18977,7 +18973,7 @@
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>HWPS4</t>
+          <t>HWPS5</t>
         </is>
       </c>
       <c r="B174" s="5" t="n">
@@ -19003,7 +18999,7 @@
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>HWPS5</t>
+          <t>HWPS3</t>
         </is>
       </c>
       <c r="B175" s="5" t="n">
@@ -19029,7 +19025,7 @@
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>HWPS6</t>
+          <t>HWPS2</t>
         </is>
       </c>
       <c r="B176" s="5" t="n">
@@ -19055,7 +19051,7 @@
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
         <is>
-          <t>HWPS7</t>
+          <t>HWPS1</t>
         </is>
       </c>
       <c r="B177" s="5" t="n">
@@ -19081,7 +19077,7 @@
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>HWPS8</t>
+          <t>HWPNL1</t>
         </is>
       </c>
       <c r="B178" s="5" t="n">
@@ -19107,17 +19103,17 @@
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
         <is>
-          <t>MORNW</t>
+          <t>WYNDW</t>
         </is>
       </c>
       <c r="B179" s="5" t="n">
-        <v>0.9923999999999999</v>
+        <v>1.0032</v>
       </c>
       <c r="C179" s="5" t="n">
-        <v>0.9925</v>
+        <v>1.0068</v>
       </c>
       <c r="D179" s="5" t="n">
-        <v>0.9963</v>
+        <v>1.0084</v>
       </c>
       <c r="E179" s="5" t="inlineStr"/>
       <c r="F179" s="5" t="inlineStr"/>
@@ -19135,17 +19131,17 @@
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>WYNDW</t>
+          <t>MORNW</t>
         </is>
       </c>
       <c r="B180" s="5" t="n">
-        <v>1.0032</v>
+        <v>0.9923999999999999</v>
       </c>
       <c r="C180" s="5" t="n">
-        <v>1.0068</v>
+        <v>0.9925</v>
       </c>
       <c r="D180" s="5" t="n">
-        <v>1.0084</v>
+        <v>0.9963</v>
       </c>
       <c r="E180" s="5" t="inlineStr"/>
       <c r="F180" s="5" t="inlineStr"/>
@@ -19163,32 +19159,32 @@
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>CORIO1</t>
+          <t>BERWICK</t>
         </is>
       </c>
       <c r="B181" s="5" t="n">
-        <v>0.9987</v>
+        <v>0.9923</v>
       </c>
       <c r="C181" s="5" t="n">
-        <v>1.0048</v>
+        <v>0.9923</v>
       </c>
       <c r="D181" s="5" t="n">
-        <v>1.0055</v>
+        <v>0.9923</v>
       </c>
       <c r="E181" s="5" t="n">
-        <v>1.0002</v>
+        <v>0.9923</v>
       </c>
       <c r="F181" s="5" t="n">
-        <v>0.9908</v>
+        <v>0.9923</v>
       </c>
       <c r="G181" s="5" t="n">
-        <v>0.9913999999999999</v>
+        <v>0.9923</v>
       </c>
       <c r="H181" s="5" t="n">
-        <v>0.9918</v>
+        <v>0.9923</v>
       </c>
       <c r="I181" s="5" t="n">
-        <v>0.9933</v>
+        <v>0.9923</v>
       </c>
       <c r="J181" s="5" t="inlineStr"/>
       <c r="K181" s="5" t="inlineStr"/>
@@ -19201,32 +19197,32 @@
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>BERWICK</t>
+          <t>CORIO1</t>
         </is>
       </c>
       <c r="B182" s="5" t="n">
-        <v>0.9923</v>
+        <v>0.9987</v>
       </c>
       <c r="C182" s="5" t="n">
-        <v>0.9923</v>
+        <v>1.0048</v>
       </c>
       <c r="D182" s="5" t="n">
-        <v>0.9923</v>
+        <v>1.0055</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>0.9923</v>
+        <v>1.0002</v>
       </c>
       <c r="F182" s="5" t="n">
-        <v>0.9923</v>
+        <v>0.9908</v>
       </c>
       <c r="G182" s="5" t="n">
-        <v>0.9923</v>
+        <v>0.9913999999999999</v>
       </c>
       <c r="H182" s="5" t="n">
-        <v>0.9923</v>
+        <v>0.9918</v>
       </c>
       <c r="I182" s="5" t="n">
-        <v>0.9923</v>
+        <v>0.9933</v>
       </c>
       <c r="J182" s="5" t="inlineStr"/>
       <c r="K182" s="5" t="inlineStr"/>
@@ -19239,35 +19235,35 @@
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t>BROADMDW</t>
+          <t>SVALE1</t>
         </is>
       </c>
       <c r="B183" s="5" t="n">
-        <v>1</v>
+        <v>0.997</v>
       </c>
       <c r="C183" s="5" t="n">
-        <v>1</v>
+        <v>0.9972</v>
       </c>
       <c r="D183" s="5" t="n">
-        <v>1</v>
+        <v>0.9989</v>
       </c>
       <c r="E183" s="5" t="n">
-        <v>1</v>
+        <v>0.9986</v>
       </c>
       <c r="F183" s="5" t="n">
-        <v>1</v>
+        <v>0.9987</v>
       </c>
       <c r="G183" s="5" t="n">
-        <v>1</v>
+        <v>0.9984</v>
       </c>
       <c r="H183" s="5" t="n">
-        <v>1</v>
+        <v>0.9957</v>
       </c>
       <c r="I183" s="5" t="n">
-        <v>1</v>
+        <v>0.9972</v>
       </c>
       <c r="J183" s="5" t="n">
-        <v>1</v>
+        <v>1.0001</v>
       </c>
       <c r="K183" s="5" t="inlineStr"/>
       <c r="L183" s="5" t="inlineStr"/>
@@ -19279,35 +19275,35 @@
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>SVALE1</t>
+          <t>BROADMDW</t>
         </is>
       </c>
       <c r="B184" s="5" t="n">
-        <v>0.997</v>
+        <v>1</v>
       </c>
       <c r="C184" s="5" t="n">
-        <v>0.9972</v>
+        <v>1</v>
       </c>
       <c r="D184" s="5" t="n">
-        <v>0.9989</v>
+        <v>1</v>
       </c>
       <c r="E184" s="5" t="n">
-        <v>0.9986</v>
+        <v>1</v>
       </c>
       <c r="F184" s="5" t="n">
-        <v>0.9987</v>
+        <v>1</v>
       </c>
       <c r="G184" s="5" t="n">
-        <v>0.9984</v>
+        <v>1</v>
       </c>
       <c r="H184" s="5" t="n">
-        <v>0.9957</v>
+        <v>1</v>
       </c>
       <c r="I184" s="5" t="n">
-        <v>0.9972</v>
+        <v>1</v>
       </c>
       <c r="J184" s="5" t="n">
-        <v>1.0001</v>
+        <v>1</v>
       </c>
       <c r="K184" s="5" t="inlineStr"/>
       <c r="L184" s="5" t="inlineStr"/>
@@ -19319,7 +19315,7 @@
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
         <is>
-          <t>VBBG1</t>
+          <t>PIBESSG1</t>
         </is>
       </c>
       <c r="B185" s="5" t="inlineStr"/>
@@ -19328,17 +19324,15 @@
       <c r="E185" s="5" t="inlineStr"/>
       <c r="F185" s="5" t="inlineStr"/>
       <c r="G185" s="5" t="inlineStr"/>
-      <c r="H185" s="5" t="n">
-        <v>0.982</v>
-      </c>
+      <c r="H185" s="5" t="inlineStr"/>
       <c r="I185" s="5" t="n">
+        <v>0.9977</v>
+      </c>
+      <c r="J185" s="5" t="n">
+        <v>0.9825</v>
+      </c>
+      <c r="K185" s="5" t="n">
         <v>0.9848</v>
-      </c>
-      <c r="J185" s="5" t="n">
-        <v>0.9885</v>
-      </c>
-      <c r="K185" s="5" t="n">
-        <v>0.9879</v>
       </c>
       <c r="L185" s="5" t="inlineStr"/>
       <c r="M185" s="5" t="inlineStr"/>
@@ -19349,7 +19343,7 @@
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>HBESSG1</t>
+          <t>BULBESG1</t>
         </is>
       </c>
       <c r="B186" s="5" t="inlineStr"/>
@@ -19358,15 +19352,17 @@
       <c r="E186" s="5" t="inlineStr"/>
       <c r="F186" s="5" t="inlineStr"/>
       <c r="G186" s="5" t="inlineStr"/>
-      <c r="H186" s="5" t="inlineStr"/>
+      <c r="H186" s="5" t="n">
+        <v>0.8949</v>
+      </c>
       <c r="I186" s="5" t="n">
-        <v>0.9785</v>
+        <v>0.8839</v>
       </c>
       <c r="J186" s="5" t="n">
-        <v>0.9789</v>
+        <v>0.8821</v>
       </c>
       <c r="K186" s="5" t="n">
-        <v>0.9804</v>
+        <v>0.8733</v>
       </c>
       <c r="L186" s="5" t="inlineStr"/>
       <c r="M186" s="5" t="inlineStr"/>
@@ -19377,32 +19373,28 @@
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
         <is>
-          <t>GANNBG1</t>
+          <t>FNWF1</t>
         </is>
       </c>
       <c r="B187" s="5" t="inlineStr"/>
       <c r="C187" s="5" t="inlineStr"/>
       <c r="D187" s="5" t="inlineStr"/>
-      <c r="E187" s="5" t="n">
-        <v>1.007</v>
-      </c>
-      <c r="F187" s="5" t="n">
-        <v>0.9643</v>
-      </c>
+      <c r="E187" s="5" t="inlineStr"/>
+      <c r="F187" s="5" t="inlineStr"/>
       <c r="G187" s="5" t="n">
-        <v>0.9792999999999999</v>
+        <v>1.0079</v>
       </c>
       <c r="H187" s="5" t="n">
-        <v>0.9772999999999999</v>
+        <v>1.0035</v>
       </c>
       <c r="I187" s="5" t="n">
-        <v>1.0026</v>
+        <v>0.9972</v>
       </c>
       <c r="J187" s="5" t="n">
-        <v>1.029</v>
+        <v>0.9933</v>
       </c>
       <c r="K187" s="5" t="n">
-        <v>1.0155</v>
+        <v>0.9993</v>
       </c>
       <c r="L187" s="5" t="inlineStr"/>
       <c r="M187" s="5" t="inlineStr"/>
@@ -19413,7 +19405,7 @@
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t>FNWF1</t>
+          <t>VBBG1</t>
         </is>
       </c>
       <c r="B188" s="5" t="inlineStr"/>
@@ -19421,20 +19413,18 @@
       <c r="D188" s="5" t="inlineStr"/>
       <c r="E188" s="5" t="inlineStr"/>
       <c r="F188" s="5" t="inlineStr"/>
-      <c r="G188" s="5" t="n">
-        <v>1.0079</v>
-      </c>
+      <c r="G188" s="5" t="inlineStr"/>
       <c r="H188" s="5" t="n">
-        <v>1.0035</v>
+        <v>0.982</v>
       </c>
       <c r="I188" s="5" t="n">
-        <v>0.9972</v>
+        <v>0.9848</v>
       </c>
       <c r="J188" s="5" t="n">
-        <v>0.9933</v>
+        <v>0.9885</v>
       </c>
       <c r="K188" s="5" t="n">
-        <v>0.9993</v>
+        <v>0.9879</v>
       </c>
       <c r="L188" s="5" t="inlineStr"/>
       <c r="M188" s="5" t="inlineStr"/>
@@ -19445,24 +19435,32 @@
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
         <is>
-          <t>PIBESSG1</t>
+          <t>GANNBG1</t>
         </is>
       </c>
       <c r="B189" s="5" t="inlineStr"/>
       <c r="C189" s="5" t="inlineStr"/>
       <c r="D189" s="5" t="inlineStr"/>
-      <c r="E189" s="5" t="inlineStr"/>
-      <c r="F189" s="5" t="inlineStr"/>
-      <c r="G189" s="5" t="inlineStr"/>
-      <c r="H189" s="5" t="inlineStr"/>
+      <c r="E189" s="5" t="n">
+        <v>1.007</v>
+      </c>
+      <c r="F189" s="5" t="n">
+        <v>0.9643</v>
+      </c>
+      <c r="G189" s="5" t="n">
+        <v>0.9792999999999999</v>
+      </c>
+      <c r="H189" s="5" t="n">
+        <v>0.9772999999999999</v>
+      </c>
       <c r="I189" s="5" t="n">
-        <v>0.9977</v>
+        <v>1.0026</v>
       </c>
       <c r="J189" s="5" t="n">
-        <v>0.9825</v>
+        <v>1.029</v>
       </c>
       <c r="K189" s="5" t="n">
-        <v>0.9848</v>
+        <v>1.0155</v>
       </c>
       <c r="L189" s="5" t="inlineStr"/>
       <c r="M189" s="5" t="inlineStr"/>
@@ -19473,7 +19471,7 @@
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t>BULBESG1</t>
+          <t>HBESSG1</t>
         </is>
       </c>
       <c r="B190" s="5" t="inlineStr"/>
@@ -19482,17 +19480,15 @@
       <c r="E190" s="5" t="inlineStr"/>
       <c r="F190" s="5" t="inlineStr"/>
       <c r="G190" s="5" t="inlineStr"/>
-      <c r="H190" s="5" t="n">
-        <v>0.8949</v>
-      </c>
+      <c r="H190" s="5" t="inlineStr"/>
       <c r="I190" s="5" t="n">
-        <v>0.8839</v>
+        <v>0.9785</v>
       </c>
       <c r="J190" s="5" t="n">
-        <v>0.8821</v>
+        <v>0.9789</v>
       </c>
       <c r="K190" s="5" t="n">
-        <v>0.8733</v>
+        <v>0.9804</v>
       </c>
       <c r="L190" s="5" t="inlineStr"/>
       <c r="M190" s="5" t="inlineStr"/>
@@ -19932,7 +19928,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>MURRAY</t>
+          <t>MURAYNL3</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -19961,7 +19957,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>MURAYNL1</t>
+          <t>MURAYNL2</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -19990,7 +19986,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>MURAYNL3</t>
+          <t>MURAYNL1</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -20019,7 +20015,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>MURAYNL2</t>
+          <t>MURRAY</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -20048,12 +20044,12 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>NUMURSF1</t>
+          <t>GIRGSF</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Numurkah Solar Farm</t>
+          <t>Girgarre Solar Farm</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -20077,12 +20073,12 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>WUNUSF1</t>
+          <t>NUMURSF1</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Wunghnu Solar Farm</t>
+          <t>Numurkah Solar Farm</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -20106,12 +20102,12 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>GIRGSF</t>
+          <t>WUNUSF1</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Girgarre Solar Farm</t>
+          <t>Wunghnu Solar Farm</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -20251,12 +20247,12 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>WINTSF1</t>
+          <t>GLRWNSF1</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Winton Solar Farm</t>
+          <t>Glenrowan West Solar Farm</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -20280,12 +20276,12 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>GLRWNSF1</t>
+          <t>WINTSF1</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Glenrowan West Solar Farm</t>
+          <t>Winton Solar Farm</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -20367,12 +20363,12 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>WKIEWA2</t>
+          <t>WKIEWA1</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>WEST KIEWA POWER STATION</t>
+          <t>West Kiewa Power Station</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -20396,7 +20392,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>WKIEWA1</t>
+          <t>WKIEWA2</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -20425,17 +20421,17 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>YWNGAHYD</t>
+          <t>TATURA01</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Yarrawonga Hydro Power Station</t>
+          <t>Tatura Biomass Generator</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Hydro</t>
+          <t>Other Renewable</t>
         </is>
       </c>
       <c r="D22" s="5" t="n">
@@ -20498,12 +20494,12 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>YATSF1</t>
+          <t>KARSF1</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Yatpool Solar Farm</t>
+          <t>Karadoc Solar Farm</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -20527,12 +20523,12 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>KARSF1</t>
+          <t>YATSF1</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Karadoc Solar Farm</t>
+          <t>Yatpool Solar Farm</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -20556,12 +20552,12 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>BANN1</t>
+          <t>WEMENSF1</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Bannerton Solar Park</t>
+          <t>Wemen Solar Farm</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -20585,12 +20581,12 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>WEMENSF1</t>
+          <t>BANN1</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Wemen Solar Farm</t>
+          <t>Bannerton Solar Park</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -20730,17 +20726,17 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>WONWP</t>
+          <t>GLENMAG1</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Wonthaggi Wind Farm</t>
+          <t>Glenmaggie Hydro Power Station</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
@@ -20759,17 +20755,17 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>PIBESS1</t>
+          <t>WONWP</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Phillip Island BESS</t>
+          <t>Wonthaggi Wind Farm</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D36" s="5" t="n">
@@ -20788,17 +20784,17 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>BALDHWF1</t>
+          <t>PIBESS1</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Bald Hills Wind Farm</t>
+          <t>Phillip Island BESS</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D37" s="5" t="n">
@@ -20817,17 +20813,17 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>GLENMAG1</t>
+          <t>TGNSS1</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Glenmaggie Hydro Power Station</t>
+          <t>Traralgon Network Support Station</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Hydro</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D38" s="5" t="n">
@@ -20846,17 +20842,17 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>LONGFORD</t>
+          <t>TOORAWF</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Longford Plant</t>
+          <t>Toora Wind Farm</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
@@ -20875,17 +20871,17 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TGNSS1</t>
+          <t>BALDHWF1</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Traralgon Network Support Station</t>
+          <t>Bald Hills Wind Farm</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D40" s="5" t="n">
@@ -20904,17 +20900,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>TOORAWF</t>
+          <t>LONGFORD</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Toora Wind Farm</t>
+          <t>LONGFORD PLANT</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">
@@ -20933,12 +20929,12 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>JLB03</t>
+          <t>JLA01</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Jeeralang "B" Power Station</t>
+          <t>Jeeralang "A" Power Station</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -20962,12 +20958,12 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>JLB02</t>
+          <t>JLA04</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Jeeralang "B" Power Station</t>
+          <t>Jeeralang "A" Power Station</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -20991,12 +20987,12 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>JLB01</t>
+          <t>JLA03</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Jeeralang "B" Power Station</t>
+          <t>Jeeralang "A" Power Station</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -21049,12 +21045,12 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>JLA03</t>
+          <t>JLB03</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Jeeralang "A" Power Station</t>
+          <t>Jeeralang "B" Power Station</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">

--- a/outputs/VIC_mlf.xlsx
+++ b/outputs/VIC_mlf.xlsx
@@ -2544,13 +2544,17 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>PLBESS1</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="n">
-        <v/>
-      </c>
-      <c r="D36" s="3" t="inlineStr"/>
+          <t>Pine Lodge BESS</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>344.4</v>
+      </c>
       <c r="E36" s="5" t="inlineStr"/>
       <c r="F36" s="5" t="inlineStr"/>
       <c r="G36" s="5" t="inlineStr"/>
@@ -5089,13 +5093,17 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>WOOREEN</t>
-        </is>
-      </c>
-      <c r="C77" s="3" t="n">
-        <v/>
-      </c>
-      <c r="D77" s="3" t="inlineStr"/>
+          <t>Wooreen Battery Energy Storage System</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="n">
+        <v>491</v>
+      </c>
       <c r="E77" s="5" t="inlineStr"/>
       <c r="F77" s="5" t="inlineStr"/>
       <c r="G77" s="5" t="inlineStr"/>
@@ -7023,13 +7031,9 @@
           <t>Basslink HVDC Link</t>
         </is>
       </c>
-      <c r="C108" s="3" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
+      <c r="C108" s="3" t="inlineStr"/>
       <c r="D108" s="4" t="n">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="E108" s="5" t="n">
         <v>0.9828</v>
@@ -7230,7 +7234,7 @@
         </is>
       </c>
       <c r="D111" s="4" t="n">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="E111" s="5" t="n">
         <v>1.0247</v>
@@ -7288,7 +7292,7 @@
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>West Kiewa Power Station</t>
+          <t>WEST KIEWA POWER STATION</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
@@ -8347,7 +8351,7 @@
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>LONGFORD PLANT</t>
+          <t>Longford Plant</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
@@ -8356,7 +8360,7 @@
         </is>
       </c>
       <c r="D129" s="4" t="n">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="E129" s="5" t="n">
         <v>0.9799</v>
@@ -20397,7 +20401,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>West Kiewa Power Station</t>
+          <t>WEST KIEWA POWER STATION</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -20905,7 +20909,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>LONGFORD PLANT</t>
+          <t>Longford Plant</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">

--- a/outputs/VIC_mlf.xlsx
+++ b/outputs/VIC_mlf.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MLF Table" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Biggest Movers" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="MLF Table" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Biggest Movers" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -906,12 +906,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>KIATAWF1</t>
+          <t>DIAPURWF1</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Kiata Wind Farm</t>
+          <t>Diapur Wind Farm</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -920,22 +920,14 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>31.05</v>
+        <v>8</v>
       </c>
       <c r="E7" s="5" t="inlineStr"/>
       <c r="F7" s="5" t="inlineStr"/>
-      <c r="G7" s="5" t="n">
-        <v>1.0357</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>0.9911</v>
-      </c>
-      <c r="I7" s="5" t="n">
-        <v>0.9066</v>
-      </c>
-      <c r="J7" s="5" t="n">
-        <v>0.8974</v>
-      </c>
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr"/>
       <c r="K7" s="5" t="n">
         <v>0.9005</v>
       </c>
@@ -969,12 +961,12 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>DIAPURWF1</t>
+          <t>KIATAWF1</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Diapur Wind Farm</t>
+          <t>Kiata Wind Farm</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -983,14 +975,22 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>8</v>
+        <v>31.05</v>
       </c>
       <c r="E8" s="5" t="inlineStr"/>
       <c r="F8" s="5" t="inlineStr"/>
-      <c r="G8" s="5" t="inlineStr"/>
-      <c r="H8" s="5" t="inlineStr"/>
-      <c r="I8" s="5" t="inlineStr"/>
-      <c r="J8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="n">
+        <v>1.0357</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>0.9911</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>0.9066</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>0.8974</v>
+      </c>
       <c r="K8" s="5" t="n">
         <v>0.9005</v>
       </c>
@@ -1199,12 +1199,12 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>YATSF1</t>
+          <t>KARSF1</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Yatpool Solar Farm</t>
+          <t>Karadoc Solar Farm</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -1213,13 +1213,17 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="E12" s="5" t="inlineStr"/>
       <c r="F12" s="5" t="inlineStr"/>
       <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="n">
+        <v>0.9472</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>0.8097</v>
+      </c>
       <c r="J12" s="5" t="n">
         <v>0.8045</v>
       </c>
@@ -1256,12 +1260,12 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>KARSF1</t>
+          <t>YATSF1</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Karadoc Solar Farm</t>
+          <t>Yatpool Solar Farm</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -1270,17 +1274,13 @@
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="E13" s="5" t="inlineStr"/>
       <c r="F13" s="5" t="inlineStr"/>
       <c r="G13" s="5" t="inlineStr"/>
-      <c r="H13" s="5" t="n">
-        <v>0.9472</v>
-      </c>
-      <c r="I13" s="5" t="n">
-        <v>0.8097</v>
-      </c>
+      <c r="H13" s="5" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr"/>
       <c r="J13" s="5" t="n">
         <v>0.8045</v>
       </c>
@@ -1317,12 +1317,12 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>BANN1</t>
+          <t>WEMENSF1</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Bannerton Solar Park</t>
+          <t>Wemen Solar Farm</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="E14" s="5" t="inlineStr"/>
       <c r="F14" s="5" t="inlineStr"/>
@@ -1378,12 +1378,12 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>WEMENSF1</t>
+          <t>BANN1</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Wemen Solar Farm</t>
+          <t>Bannerton Solar Park</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -1392,7 +1392,7 @@
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="E15" s="5" t="inlineStr"/>
       <c r="F15" s="5" t="inlineStr"/>
@@ -1439,12 +1439,12 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>NUMURSF1</t>
+          <t>GIRGSF</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Numurkah Solar Farm</t>
+          <t>Girgarre Solar Farm</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -1453,29 +1453,17 @@
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>112</v>
+        <v>93.31</v>
       </c>
       <c r="E16" s="5" t="inlineStr"/>
       <c r="F16" s="5" t="inlineStr"/>
       <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="n">
-        <v>0.982</v>
-      </c>
-      <c r="I16" s="5" t="n">
-        <v>0.9896</v>
-      </c>
-      <c r="J16" s="5" t="n">
-        <v>0.9945000000000001</v>
-      </c>
-      <c r="K16" s="5" t="n">
-        <v>0.9963</v>
-      </c>
-      <c r="L16" s="5" t="n">
-        <v>0.9715</v>
-      </c>
-      <c r="M16" s="5" t="n">
-        <v>0.9738</v>
-      </c>
+      <c r="H16" s="5" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr"/>
+      <c r="L16" s="5" t="inlineStr"/>
+      <c r="M16" s="5" t="inlineStr"/>
       <c r="N16" s="5" t="n">
         <v>0.9477</v>
       </c>
@@ -1500,12 +1488,12 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>WUNUSF1</t>
+          <t>NUMURSF1</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Wunghnu Solar Farm</t>
+          <t>Numurkah Solar Farm</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -1514,17 +1502,29 @@
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>93.5</v>
+        <v>112</v>
       </c>
       <c r="E17" s="5" t="inlineStr"/>
       <c r="F17" s="5" t="inlineStr"/>
       <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
-      <c r="L17" s="5" t="inlineStr"/>
-      <c r="M17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>0.9896</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>0.9945000000000001</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>0.9963</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>0.9715</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>0.9738</v>
+      </c>
       <c r="N17" s="5" t="n">
         <v>0.9477</v>
       </c>
@@ -1549,12 +1549,12 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>LANCSF1</t>
+          <t>WUNUSF1</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Lancaster Solar Farm</t>
+          <t>Wunghnu Solar Farm</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -1563,7 +1563,7 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>94</v>
+        <v>93.5</v>
       </c>
       <c r="E18" s="5" t="inlineStr"/>
       <c r="F18" s="5" t="inlineStr"/>
@@ -1574,10 +1574,12 @@
       <c r="K18" s="5" t="inlineStr"/>
       <c r="L18" s="5" t="inlineStr"/>
       <c r="M18" s="5" t="inlineStr"/>
-      <c r="N18" s="5" t="inlineStr"/>
+      <c r="N18" s="5" t="n">
+        <v>0.9477</v>
+      </c>
       <c r="O18" s="5" t="inlineStr"/>
       <c r="P18" s="5" t="n">
-        <v>0.9441000000000001</v>
+        <v>0.9463</v>
       </c>
       <c r="Q18" s="5" t="inlineStr"/>
       <c r="R18" s="5" t="n">
@@ -1585,10 +1587,10 @@
       </c>
       <c r="S18" s="5" t="inlineStr"/>
       <c r="T18" s="5" t="n">
-        <v>-0.0231</v>
+        <v>-0.0253</v>
       </c>
       <c r="U18" s="6" t="n">
-        <v>-2.45</v>
+        <v>-2.67</v>
       </c>
       <c r="V18" s="5" t="inlineStr"/>
       <c r="W18" s="6" t="inlineStr"/>
@@ -1596,12 +1598,12 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>GIRGSF</t>
+          <t>LANCSF1</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Girgarre Solar Farm</t>
+          <t>Lancaster Solar Farm</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -1610,7 +1612,7 @@
         </is>
       </c>
       <c r="D19" s="4" t="n">
-        <v>93.31</v>
+        <v>94</v>
       </c>
       <c r="E19" s="5" t="inlineStr"/>
       <c r="F19" s="5" t="inlineStr"/>
@@ -1621,12 +1623,10 @@
       <c r="K19" s="5" t="inlineStr"/>
       <c r="L19" s="5" t="inlineStr"/>
       <c r="M19" s="5" t="inlineStr"/>
-      <c r="N19" s="5" t="n">
-        <v>0.9477</v>
-      </c>
+      <c r="N19" s="5" t="inlineStr"/>
       <c r="O19" s="5" t="inlineStr"/>
       <c r="P19" s="5" t="n">
-        <v>0.9463</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="Q19" s="5" t="inlineStr"/>
       <c r="R19" s="5" t="n">
@@ -1634,10 +1634,10 @@
       </c>
       <c r="S19" s="5" t="inlineStr"/>
       <c r="T19" s="5" t="n">
-        <v>-0.0253</v>
+        <v>-0.0231</v>
       </c>
       <c r="U19" s="6" t="n">
-        <v>-2.67</v>
+        <v>-2.45</v>
       </c>
       <c r="V19" s="5" t="inlineStr"/>
       <c r="W19" s="6" t="inlineStr"/>
@@ -1645,12 +1645,12 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>WINTSF1</t>
+          <t>GLRWNSF1</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Winton Solar Farm</t>
+          <t>Glenrowan West Solar Farm</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="E20" s="5" t="inlineStr"/>
       <c r="F20" s="5" t="inlineStr"/>
@@ -1702,12 +1702,12 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>GLRWNSF1</t>
+          <t>WINTSF1</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Glenrowan West Solar Farm</t>
+          <t>Winton Solar Farm</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -1716,7 +1716,7 @@
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="E21" s="5" t="inlineStr"/>
       <c r="F21" s="5" t="inlineStr"/>
@@ -2191,12 +2191,12 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>BRYB1WF1</t>
+          <t>BRYB2WF2</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Berrybank Wind Farm</t>
+          <t>Berrybank 2 Wind Farm</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -2205,19 +2205,15 @@
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>180.6</v>
+        <v>109</v>
       </c>
       <c r="E30" s="5" t="inlineStr"/>
       <c r="F30" s="5" t="inlineStr"/>
       <c r="G30" s="5" t="inlineStr"/>
       <c r="H30" s="5" t="inlineStr"/>
       <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="n">
-        <v>0.9482</v>
-      </c>
-      <c r="K30" s="5" t="n">
-        <v>0.9431</v>
-      </c>
+      <c r="J30" s="5" t="inlineStr"/>
+      <c r="K30" s="5" t="inlineStr"/>
       <c r="L30" s="5" t="n">
         <v>0.9496</v>
       </c>
@@ -2248,12 +2244,12 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>BRYB2WF2</t>
+          <t>BRYB1WF1</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Berrybank 2 Wind Farm</t>
+          <t>Berrybank Wind Farm</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -2262,15 +2258,19 @@
         </is>
       </c>
       <c r="D31" s="4" t="n">
-        <v>109</v>
+        <v>180.6</v>
       </c>
       <c r="E31" s="5" t="inlineStr"/>
       <c r="F31" s="5" t="inlineStr"/>
       <c r="G31" s="5" t="inlineStr"/>
       <c r="H31" s="5" t="inlineStr"/>
       <c r="I31" s="5" t="inlineStr"/>
-      <c r="J31" s="5" t="inlineStr"/>
-      <c r="K31" s="5" t="inlineStr"/>
+      <c r="J31" s="5" t="n">
+        <v>0.9482</v>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>0.9431</v>
+      </c>
       <c r="L31" s="5" t="n">
         <v>0.9496</v>
       </c>
@@ -2708,12 +2708,12 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>MERCER01</t>
+          <t>MOORAWF1</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Mt Mercer Wind Farm</t>
+          <t xml:space="preserve">Moorabool Wind Farm </t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -2722,23 +2722,13 @@
         </is>
       </c>
       <c r="D39" s="4" t="n">
-        <v>131.2</v>
-      </c>
-      <c r="E39" s="5" t="n">
-        <v>1.0033</v>
-      </c>
-      <c r="F39" s="5" t="n">
-        <v>1.0048</v>
-      </c>
-      <c r="G39" s="5" t="n">
-        <v>1.001</v>
-      </c>
-      <c r="H39" s="5" t="n">
-        <v>0.9909</v>
-      </c>
-      <c r="I39" s="5" t="n">
-        <v>0.965</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="E39" s="5" t="inlineStr"/>
+      <c r="F39" s="5" t="inlineStr"/>
+      <c r="G39" s="5" t="inlineStr"/>
+      <c r="H39" s="5" t="inlineStr"/>
+      <c r="I39" s="5" t="inlineStr"/>
       <c r="J39" s="5" t="n">
         <v>0.9500999999999999</v>
       </c>
@@ -2830,12 +2820,12 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>MOORAWF1</t>
+          <t>MERCER01</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moorabool Wind Farm </t>
+          <t>Mt Mercer Wind Farm</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -2844,13 +2834,23 @@
         </is>
       </c>
       <c r="D41" s="4" t="n">
-        <v>312</v>
-      </c>
-      <c r="E41" s="5" t="inlineStr"/>
-      <c r="F41" s="5" t="inlineStr"/>
-      <c r="G41" s="5" t="inlineStr"/>
-      <c r="H41" s="5" t="inlineStr"/>
-      <c r="I41" s="5" t="inlineStr"/>
+        <v>131.2</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>1.0033</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>1.0048</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>1.001</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>0.9909</v>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>0.965</v>
+      </c>
       <c r="J41" s="5" t="n">
         <v>0.9500999999999999</v>
       </c>
@@ -2887,7 +2887,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>MURAYNL2</t>
+          <t>MURAYNL3</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -2954,7 +2954,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>MURAYNL3</t>
+          <t>MURAYNL2</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -3289,12 +3289,12 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>YWNL1</t>
+          <t>YWPS4</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>YALLOURN 'W' POWER STATION</t>
+          <t>Yallourn 'W' Power Station</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -3303,7 +3303,7 @@
         </is>
       </c>
       <c r="D48" s="4" t="n">
-        <v>25</v>
+        <v>380</v>
       </c>
       <c r="E48" s="5" t="n">
         <v>0.9563</v>
@@ -3423,12 +3423,12 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>YWPS4</t>
+          <t>YWNL1</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Yallourn 'W' Power Station</t>
+          <t>YALLOURN 'W' POWER STATION</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -3437,7 +3437,7 @@
         </is>
       </c>
       <c r="D50" s="4" t="n">
-        <v>380</v>
+        <v>25</v>
       </c>
       <c r="E50" s="5" t="n">
         <v>0.9563</v>
@@ -3490,12 +3490,12 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>BAPS</t>
+          <t>DARTM1</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Banimboola Power Station</t>
+          <t>Dartmouth Power Station</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -3504,7 +3504,7 @@
         </is>
       </c>
       <c r="D51" s="4" t="n">
-        <v>12.85</v>
+        <v>185</v>
       </c>
       <c r="E51" s="5" t="n">
         <v>1.0004</v>
@@ -3557,12 +3557,12 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>DARTM1</t>
+          <t>BAPS</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Dartmouth Power Station</t>
+          <t>Banimboola Power Station</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -3571,7 +3571,7 @@
         </is>
       </c>
       <c r="D52" s="4" t="n">
-        <v>185</v>
+        <v>12.85</v>
       </c>
       <c r="E52" s="5" t="n">
         <v>1.0004</v>
@@ -3746,12 +3746,12 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>MAROOWF1</t>
+          <t>CHALLHWF</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Maroona Wind Farm</t>
+          <t>Challicum Hills Wind Farm</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -3760,18 +3760,22 @@
         </is>
       </c>
       <c r="D55" s="4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="E55" s="5" t="inlineStr"/>
-      <c r="F55" s="5" t="inlineStr"/>
+        <v>52.5</v>
+      </c>
+      <c r="E55" s="5" t="n">
+        <v>1.0988</v>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>1.0988</v>
+      </c>
       <c r="G55" s="5" t="n">
-        <v>1.016</v>
+        <v>1.0988</v>
       </c>
       <c r="H55" s="5" t="n">
-        <v>1.0016</v>
+        <v>0.9957</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>0.9716</v>
+        <v>0.9193</v>
       </c>
       <c r="J55" s="5" t="n">
         <v>0.9711</v>
@@ -3876,12 +3880,12 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>CHALLHWF</t>
+          <t>MAROOWF1</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Challicum Hills Wind Farm</t>
+          <t>Maroona Wind Farm</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -3890,22 +3894,18 @@
         </is>
       </c>
       <c r="D57" s="4" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="E57" s="5" t="n">
-        <v>1.0988</v>
-      </c>
-      <c r="F57" s="5" t="n">
-        <v>1.0988</v>
-      </c>
+        <v>6.8</v>
+      </c>
+      <c r="E57" s="5" t="inlineStr"/>
+      <c r="F57" s="5" t="inlineStr"/>
       <c r="G57" s="5" t="n">
-        <v>1.0988</v>
+        <v>1.016</v>
       </c>
       <c r="H57" s="5" t="n">
-        <v>0.9957</v>
+        <v>1.0016</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>0.9193</v>
+        <v>0.9716</v>
       </c>
       <c r="J57" s="5" t="n">
         <v>0.9711</v>
@@ -4006,7 +4006,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>MURR1-8</t>
+          <t>MURR1-4</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -4014,7 +4014,9 @@
           <t>MURRAY1</t>
         </is>
       </c>
-      <c r="C59" s="3" t="n"/>
+      <c r="C59" s="3" t="n">
+        <v/>
+      </c>
       <c r="D59" s="4" t="n">
         <v>95</v>
       </c>
@@ -4069,17 +4071,19 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>MURR2-1</t>
+          <t>MURR1-3</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>MURRAY2</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="n"/>
+          <t>MURRAY1</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v/>
+      </c>
       <c r="D60" s="4" t="n">
-        <v>138</v>
+        <v>95</v>
       </c>
       <c r="E60" s="5" t="n">
         <v>0.98</v>
@@ -4132,7 +4136,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>MURR1-10</t>
+          <t>MURR1-2</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -4140,7 +4144,9 @@
           <t>MURRAY1</t>
         </is>
       </c>
-      <c r="C61" s="3" t="n"/>
+      <c r="C61" s="3" t="n">
+        <v/>
+      </c>
       <c r="D61" s="4" t="n">
         <v>95</v>
       </c>
@@ -4195,7 +4201,7 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>MURR1-1</t>
+          <t>MURR1-10</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -4203,7 +4209,9 @@
           <t>MURRAY1</t>
         </is>
       </c>
-      <c r="C62" s="3" t="n"/>
+      <c r="C62" s="3" t="n">
+        <v/>
+      </c>
       <c r="D62" s="4" t="n">
         <v>95</v>
       </c>
@@ -4258,7 +4266,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>MURR1-2</t>
+          <t>MURR1-1</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -4266,7 +4274,9 @@
           <t>MURRAY1</t>
         </is>
       </c>
-      <c r="C63" s="3" t="n"/>
+      <c r="C63" s="3" t="n">
+        <v/>
+      </c>
       <c r="D63" s="4" t="n">
         <v>95</v>
       </c>
@@ -4321,7 +4331,7 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>MURR1-9</t>
+          <t>MURR1-7</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -4329,7 +4339,9 @@
           <t>MURRAY1</t>
         </is>
       </c>
-      <c r="C64" s="3" t="n"/>
+      <c r="C64" s="3" t="n">
+        <v/>
+      </c>
       <c r="D64" s="4" t="n">
         <v>95</v>
       </c>
@@ -4384,7 +4396,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>MURR1-7</t>
+          <t>MURR1-6</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -4392,7 +4404,9 @@
           <t>MURRAY1</t>
         </is>
       </c>
-      <c r="C65" s="3" t="n"/>
+      <c r="C65" s="3" t="n">
+        <v/>
+      </c>
       <c r="D65" s="4" t="n">
         <v>95</v>
       </c>
@@ -4455,7 +4469,9 @@
           <t>MURRAY1</t>
         </is>
       </c>
-      <c r="C66" s="3" t="n"/>
+      <c r="C66" s="3" t="n">
+        <v/>
+      </c>
       <c r="D66" s="4" t="n">
         <v>95</v>
       </c>
@@ -4510,7 +4526,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>MURR1-4</t>
+          <t>MURR1-8</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -4518,7 +4534,9 @@
           <t>MURRAY1</t>
         </is>
       </c>
-      <c r="C67" s="3" t="n"/>
+      <c r="C67" s="3" t="n">
+        <v/>
+      </c>
       <c r="D67" s="4" t="n">
         <v>95</v>
       </c>
@@ -4573,17 +4591,19 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>MURR1-3</t>
+          <t>MURR2-2</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>MURRAY1</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="n"/>
+          <t>MURRAY2</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v/>
+      </c>
       <c r="D68" s="4" t="n">
-        <v>95</v>
+        <v>138</v>
       </c>
       <c r="E68" s="5" t="n">
         <v>0.98</v>
@@ -4636,7 +4656,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>MURR2-2</t>
+          <t>MURR2-1</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -4644,7 +4664,9 @@
           <t>MURRAY2</t>
         </is>
       </c>
-      <c r="C69" s="3" t="n"/>
+      <c r="C69" s="3" t="n">
+        <v/>
+      </c>
       <c r="D69" s="4" t="n">
         <v>138</v>
       </c>
@@ -4699,17 +4721,19 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>MURR2-3</t>
+          <t>MURR1-9</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>MURRAY2</t>
-        </is>
-      </c>
-      <c r="C70" s="3" t="n"/>
+          <t>MURRAY1</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v/>
+      </c>
       <c r="D70" s="4" t="n">
-        <v>138</v>
+        <v>95</v>
       </c>
       <c r="E70" s="5" t="n">
         <v>0.98</v>
@@ -4762,7 +4786,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>MURR2-4</t>
+          <t>MURR2-3</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -4770,7 +4794,9 @@
           <t>MURRAY2</t>
         </is>
       </c>
-      <c r="C71" s="3" t="n"/>
+      <c r="C71" s="3" t="n">
+        <v/>
+      </c>
       <c r="D71" s="4" t="n">
         <v>138</v>
       </c>
@@ -4825,17 +4851,19 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>MURR1-6</t>
+          <t>MURR2-4</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>MURRAY1</t>
-        </is>
-      </c>
-      <c r="C72" s="3" t="n"/>
+          <t>MURRAY2</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v/>
+      </c>
       <c r="D72" s="4" t="n">
-        <v>95</v>
+        <v>138</v>
       </c>
       <c r="E72" s="5" t="n">
         <v>0.98</v>
@@ -5008,7 +5036,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>GPWFEST3</t>
+          <t>GPWFEST1</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -5057,7 +5085,7 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>GPWFEST1</t>
+          <t>GPWFEST3</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -5112,7 +5140,9 @@
       <c r="B77" s="3" t="n">
         <v/>
       </c>
-      <c r="C77" s="3" t="n"/>
+      <c r="C77" s="3" t="n">
+        <v/>
+      </c>
       <c r="D77" s="4" t="n">
         <v>3</v>
       </c>
@@ -5235,55 +5265,35 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>JLA04</t>
+          <t>GPWFWST2</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Jeeralang "A" Power Station</t>
+          <t>Golden Plains Wind Farm West</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D80" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="E80" s="5" t="n">
-        <v>0.9667</v>
-      </c>
-      <c r="F80" s="5" t="n">
-        <v>0.9641</v>
-      </c>
-      <c r="G80" s="5" t="n">
-        <v>0.983</v>
-      </c>
-      <c r="H80" s="5" t="n">
-        <v>0.9782999999999999</v>
-      </c>
-      <c r="I80" s="5" t="n">
-        <v>0.9731</v>
-      </c>
-      <c r="J80" s="5" t="n">
-        <v>0.9734</v>
-      </c>
-      <c r="K80" s="5" t="n">
-        <v>0.9755</v>
-      </c>
-      <c r="L80" s="5" t="n">
-        <v>0.9727</v>
-      </c>
-      <c r="M80" s="5" t="n">
-        <v>0.9764</v>
-      </c>
-      <c r="N80" s="5" t="n">
-        <v>0.9789</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="E80" s="5" t="inlineStr"/>
+      <c r="F80" s="5" t="inlineStr"/>
+      <c r="G80" s="5" t="inlineStr"/>
+      <c r="H80" s="5" t="inlineStr"/>
+      <c r="I80" s="5" t="inlineStr"/>
+      <c r="J80" s="5" t="inlineStr"/>
+      <c r="K80" s="5" t="inlineStr"/>
+      <c r="L80" s="5" t="inlineStr"/>
+      <c r="M80" s="5" t="inlineStr"/>
+      <c r="N80" s="5" t="inlineStr"/>
       <c r="O80" s="5" t="inlineStr"/>
       <c r="P80" s="5" t="n">
-        <v>0.9768</v>
+        <v>0.9837</v>
       </c>
       <c r="Q80" s="5" t="inlineStr"/>
       <c r="R80" s="5" t="n">
@@ -5291,10 +5301,10 @@
       </c>
       <c r="S80" s="5" t="inlineStr"/>
       <c r="T80" s="5" t="n">
-        <v>0.0055</v>
+        <v>-0.0014</v>
       </c>
       <c r="U80" s="6" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.14</v>
       </c>
       <c r="V80" s="5" t="inlineStr"/>
       <c r="W80" s="6" t="inlineStr"/>
@@ -5302,55 +5312,35 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>JLA03</t>
+          <t>GPWFWST1</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Jeeralang "A" Power Station</t>
+          <t>Golden Plains Wind Farm West</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D81" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="E81" s="5" t="n">
-        <v>0.9667</v>
-      </c>
-      <c r="F81" s="5" t="n">
-        <v>0.9641</v>
-      </c>
-      <c r="G81" s="5" t="n">
-        <v>0.983</v>
-      </c>
-      <c r="H81" s="5" t="n">
-        <v>0.9782999999999999</v>
-      </c>
-      <c r="I81" s="5" t="n">
-        <v>0.9731</v>
-      </c>
-      <c r="J81" s="5" t="n">
-        <v>0.9734</v>
-      </c>
-      <c r="K81" s="5" t="n">
-        <v>0.9755</v>
-      </c>
-      <c r="L81" s="5" t="n">
-        <v>0.9727</v>
-      </c>
-      <c r="M81" s="5" t="n">
-        <v>0.9764</v>
-      </c>
-      <c r="N81" s="5" t="n">
-        <v>0.9789</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="E81" s="5" t="inlineStr"/>
+      <c r="F81" s="5" t="inlineStr"/>
+      <c r="G81" s="5" t="inlineStr"/>
+      <c r="H81" s="5" t="inlineStr"/>
+      <c r="I81" s="5" t="inlineStr"/>
+      <c r="J81" s="5" t="inlineStr"/>
+      <c r="K81" s="5" t="inlineStr"/>
+      <c r="L81" s="5" t="inlineStr"/>
+      <c r="M81" s="5" t="inlineStr"/>
+      <c r="N81" s="5" t="inlineStr"/>
       <c r="O81" s="5" t="inlineStr"/>
       <c r="P81" s="5" t="n">
-        <v>0.9768</v>
+        <v>0.9837</v>
       </c>
       <c r="Q81" s="5" t="inlineStr"/>
       <c r="R81" s="5" t="n">
@@ -5358,10 +5348,10 @@
       </c>
       <c r="S81" s="5" t="inlineStr"/>
       <c r="T81" s="5" t="n">
-        <v>0.0055</v>
+        <v>-0.0014</v>
       </c>
       <c r="U81" s="6" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.14</v>
       </c>
       <c r="V81" s="5" t="inlineStr"/>
       <c r="W81" s="6" t="inlineStr"/>
@@ -5369,42 +5359,74 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>GPWFWL1</t>
-        </is>
-      </c>
-      <c r="B82" s="3" t="n">
-        <v/>
-      </c>
-      <c r="C82" s="3" t="n"/>
+          <t>JLA01</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>Jeeralang "A" Power Station</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
       <c r="D82" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E82" s="5" t="inlineStr"/>
-      <c r="F82" s="5" t="inlineStr"/>
-      <c r="G82" s="5" t="inlineStr"/>
-      <c r="H82" s="5" t="inlineStr"/>
-      <c r="I82" s="5" t="inlineStr"/>
-      <c r="J82" s="5" t="inlineStr"/>
-      <c r="K82" s="5" t="inlineStr"/>
-      <c r="L82" s="5" t="inlineStr"/>
-      <c r="M82" s="5" t="inlineStr"/>
-      <c r="N82" s="5" t="inlineStr"/>
+        <v>51</v>
+      </c>
+      <c r="E82" s="5" t="n">
+        <v>0.9667</v>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>0.9641</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>0.983</v>
+      </c>
+      <c r="H82" s="5" t="n">
+        <v>0.9782999999999999</v>
+      </c>
+      <c r="I82" s="5" t="n">
+        <v>0.9731</v>
+      </c>
+      <c r="J82" s="5" t="n">
+        <v>0.9734</v>
+      </c>
+      <c r="K82" s="5" t="n">
+        <v>0.9755</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>0.9727</v>
+      </c>
+      <c r="M82" s="5" t="n">
+        <v>0.9764</v>
+      </c>
+      <c r="N82" s="5" t="n">
+        <v>0.9789</v>
+      </c>
       <c r="O82" s="5" t="inlineStr"/>
-      <c r="P82" s="5" t="inlineStr"/>
+      <c r="P82" s="5" t="n">
+        <v>0.9768</v>
+      </c>
       <c r="Q82" s="5" t="inlineStr"/>
       <c r="R82" s="5" t="n">
         <v>0.9823</v>
       </c>
       <c r="S82" s="5" t="inlineStr"/>
-      <c r="T82" s="5" t="inlineStr"/>
-      <c r="U82" s="6" t="inlineStr"/>
+      <c r="T82" s="5" t="n">
+        <v>0.0055</v>
+      </c>
+      <c r="U82" s="6" t="n">
+        <v>0.5600000000000001</v>
+      </c>
       <c r="V82" s="5" t="inlineStr"/>
       <c r="W82" s="6" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>JLA01</t>
+          <t>JLA04</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -5471,7 +5493,7 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>JLA02</t>
+          <t>JLA03</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -5538,12 +5560,12 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>JLB01</t>
+          <t>JLA02</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Jeeralang "B" Power Station</t>
+          <t>Jeeralang "A" Power Station</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
@@ -5552,7 +5574,7 @@
         </is>
       </c>
       <c r="D85" s="4" t="n">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E85" s="5" t="n">
         <v>0.9667</v>
@@ -5605,7 +5627,7 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>JLB02</t>
+          <t>JLB03</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -5672,7 +5694,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>JLB03</t>
+          <t>JLB02</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -5739,35 +5761,55 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>GPWFWST1</t>
+          <t>JLB01</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Golden Plains Wind Farm West</t>
+          <t>Jeeralang "B" Power Station</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D88" s="4" t="n">
-        <v>266</v>
-      </c>
-      <c r="E88" s="5" t="inlineStr"/>
-      <c r="F88" s="5" t="inlineStr"/>
-      <c r="G88" s="5" t="inlineStr"/>
-      <c r="H88" s="5" t="inlineStr"/>
-      <c r="I88" s="5" t="inlineStr"/>
-      <c r="J88" s="5" t="inlineStr"/>
-      <c r="K88" s="5" t="inlineStr"/>
-      <c r="L88" s="5" t="inlineStr"/>
-      <c r="M88" s="5" t="inlineStr"/>
-      <c r="N88" s="5" t="inlineStr"/>
+        <v>76</v>
+      </c>
+      <c r="E88" s="5" t="n">
+        <v>0.9667</v>
+      </c>
+      <c r="F88" s="5" t="n">
+        <v>0.9641</v>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>0.983</v>
+      </c>
+      <c r="H88" s="5" t="n">
+        <v>0.9782999999999999</v>
+      </c>
+      <c r="I88" s="5" t="n">
+        <v>0.9731</v>
+      </c>
+      <c r="J88" s="5" t="n">
+        <v>0.9734</v>
+      </c>
+      <c r="K88" s="5" t="n">
+        <v>0.9755</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>0.9727</v>
+      </c>
+      <c r="M88" s="5" t="n">
+        <v>0.9764</v>
+      </c>
+      <c r="N88" s="5" t="n">
+        <v>0.9789</v>
+      </c>
       <c r="O88" s="5" t="inlineStr"/>
       <c r="P88" s="5" t="n">
-        <v>0.9837</v>
+        <v>0.9768</v>
       </c>
       <c r="Q88" s="5" t="inlineStr"/>
       <c r="R88" s="5" t="n">
@@ -5775,10 +5817,10 @@
       </c>
       <c r="S88" s="5" t="inlineStr"/>
       <c r="T88" s="5" t="n">
-        <v>-0.0014</v>
+        <v>0.0055</v>
       </c>
       <c r="U88" s="6" t="n">
-        <v>-0.14</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="V88" s="5" t="inlineStr"/>
       <c r="W88" s="6" t="inlineStr"/>
@@ -5786,21 +5828,17 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>GPWFWST2</t>
-        </is>
-      </c>
-      <c r="B89" s="3" t="inlineStr">
-        <is>
-          <t>Golden Plains Wind Farm West</t>
-        </is>
-      </c>
-      <c r="C89" s="3" t="inlineStr">
-        <is>
-          <t>Wind</t>
-        </is>
+          <t>GPWFWL1</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v/>
       </c>
       <c r="D89" s="4" t="n">
-        <v>310</v>
+        <v>3</v>
       </c>
       <c r="E89" s="5" t="inlineStr"/>
       <c r="F89" s="5" t="inlineStr"/>
@@ -5813,20 +5851,14 @@
       <c r="M89" s="5" t="inlineStr"/>
       <c r="N89" s="5" t="inlineStr"/>
       <c r="O89" s="5" t="inlineStr"/>
-      <c r="P89" s="5" t="n">
-        <v>0.9837</v>
-      </c>
+      <c r="P89" s="5" t="inlineStr"/>
       <c r="Q89" s="5" t="inlineStr"/>
       <c r="R89" s="5" t="n">
         <v>0.9823</v>
       </c>
       <c r="S89" s="5" t="inlineStr"/>
-      <c r="T89" s="5" t="n">
-        <v>-0.0014</v>
-      </c>
-      <c r="U89" s="6" t="n">
-        <v>-0.14</v>
-      </c>
+      <c r="T89" s="5" t="inlineStr"/>
+      <c r="U89" s="6" t="inlineStr"/>
       <c r="V89" s="5" t="inlineStr"/>
       <c r="W89" s="6" t="inlineStr"/>
     </row>
@@ -5900,12 +5932,12 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>STOCKYD1</t>
+          <t>DUNDWF3</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>Stockyard Hill Wind Farm</t>
+          <t>Dundonnell Wind Farm</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -5914,25 +5946,29 @@
         </is>
       </c>
       <c r="D91" s="4" t="n">
-        <v>531</v>
+        <v>121</v>
       </c>
       <c r="E91" s="5" t="inlineStr"/>
       <c r="F91" s="5" t="inlineStr"/>
       <c r="G91" s="5" t="inlineStr"/>
       <c r="H91" s="5" t="inlineStr"/>
-      <c r="I91" s="5" t="inlineStr"/>
-      <c r="J91" s="5" t="inlineStr"/>
+      <c r="I91" s="5" t="n">
+        <v>0.9812</v>
+      </c>
+      <c r="J91" s="5" t="n">
+        <v>0.979</v>
+      </c>
       <c r="K91" s="5" t="n">
-        <v>0.9782</v>
+        <v>0.9789</v>
       </c>
       <c r="L91" s="5" t="n">
-        <v>0.9799</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="M91" s="5" t="n">
-        <v>0.9869</v>
+        <v>0.987</v>
       </c>
       <c r="N91" s="5" t="n">
-        <v>0.9812</v>
+        <v>0.981</v>
       </c>
       <c r="O91" s="5" t="inlineStr"/>
       <c r="P91" s="5" t="n">
@@ -5955,7 +5991,7 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>DUNDWF3</t>
+          <t>DUNDWF2</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -5969,7 +6005,7 @@
         </is>
       </c>
       <c r="D92" s="4" t="n">
-        <v>121</v>
+        <v>46</v>
       </c>
       <c r="E92" s="5" t="inlineStr"/>
       <c r="F92" s="5" t="inlineStr"/>
@@ -6014,7 +6050,7 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>DUNDWF2</t>
+          <t>DUNDWF1</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -6028,7 +6064,7 @@
         </is>
       </c>
       <c r="D93" s="4" t="n">
-        <v>46</v>
+        <v>168</v>
       </c>
       <c r="E93" s="5" t="inlineStr"/>
       <c r="F93" s="5" t="inlineStr"/>
@@ -6073,12 +6109,12 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>DUNDWF1</t>
+          <t>STOCKYD1</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>Dundonnell Wind Farm</t>
+          <t>Stockyard Hill Wind Farm</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -6087,29 +6123,25 @@
         </is>
       </c>
       <c r="D94" s="4" t="n">
-        <v>168</v>
+        <v>531</v>
       </c>
       <c r="E94" s="5" t="inlineStr"/>
       <c r="F94" s="5" t="inlineStr"/>
       <c r="G94" s="5" t="inlineStr"/>
       <c r="H94" s="5" t="inlineStr"/>
-      <c r="I94" s="5" t="n">
+      <c r="I94" s="5" t="inlineStr"/>
+      <c r="J94" s="5" t="inlineStr"/>
+      <c r="K94" s="5" t="n">
+        <v>0.9782</v>
+      </c>
+      <c r="L94" s="5" t="n">
+        <v>0.9799</v>
+      </c>
+      <c r="M94" s="5" t="n">
+        <v>0.9869</v>
+      </c>
+      <c r="N94" s="5" t="n">
         <v>0.9812</v>
-      </c>
-      <c r="J94" s="5" t="n">
-        <v>0.979</v>
-      </c>
-      <c r="K94" s="5" t="n">
-        <v>0.9789</v>
-      </c>
-      <c r="L94" s="5" t="n">
-        <v>0.9824000000000001</v>
-      </c>
-      <c r="M94" s="5" t="n">
-        <v>0.987</v>
-      </c>
-      <c r="N94" s="5" t="n">
-        <v>0.981</v>
       </c>
       <c r="O94" s="5" t="inlineStr"/>
       <c r="P94" s="5" t="n">
@@ -6181,12 +6213,12 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>LYNL1</t>
+          <t>VPGS6</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>LOY YANG A POWER STATION</t>
+          <t>Valley Power Peaking Facility</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
@@ -6195,7 +6227,7 @@
         </is>
       </c>
       <c r="D96" s="4" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E96" s="5" t="n">
         <v>0.9742</v>
@@ -6248,12 +6280,12 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>LYA4</t>
+          <t>VPGS5</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>Loy Yang A Power Station</t>
+          <t>Valley Power Peaking Facility</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
@@ -6262,7 +6294,7 @@
         </is>
       </c>
       <c r="D97" s="4" t="n">
-        <v>560</v>
+        <v>50</v>
       </c>
       <c r="E97" s="5" t="n">
         <v>0.9742</v>
@@ -6315,7 +6347,7 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>VPGS6</t>
+          <t>VPGS4</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -6382,65 +6414,69 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>HBESS1</t>
+          <t>VPGS3</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>Hazelwood Battery Energy Storage System</t>
+          <t>Valley Power Peaking Facility</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D99" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="E99" s="5" t="inlineStr"/>
-      <c r="F99" s="5" t="inlineStr"/>
-      <c r="G99" s="5" t="inlineStr"/>
-      <c r="H99" s="5" t="inlineStr"/>
-      <c r="I99" s="5" t="inlineStr"/>
-      <c r="J99" s="5" t="inlineStr"/>
-      <c r="K99" s="5" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="E99" s="5" t="n">
+        <v>0.9742</v>
+      </c>
+      <c r="F99" s="5" t="n">
+        <v>0.9723000000000001</v>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>0.9801</v>
+      </c>
+      <c r="H99" s="5" t="n">
+        <v>0.9798</v>
+      </c>
+      <c r="I99" s="5" t="n">
+        <v>0.9754</v>
+      </c>
+      <c r="J99" s="5" t="n">
+        <v>0.976</v>
+      </c>
+      <c r="K99" s="5" t="n">
+        <v>0.9759</v>
+      </c>
       <c r="L99" s="5" t="n">
-        <v>0.9785</v>
+        <v>0.9782999999999999</v>
       </c>
       <c r="M99" s="5" t="n">
-        <v>0.9789</v>
+        <v>0.9782</v>
       </c>
       <c r="N99" s="5" t="n">
-        <v>0.9804</v>
-      </c>
-      <c r="O99" s="5" t="n">
-        <v>0.9864000000000001</v>
-      </c>
+        <v>0.9809</v>
+      </c>
+      <c r="O99" s="5" t="inlineStr"/>
       <c r="P99" s="5" t="n">
-        <v>0.9802</v>
-      </c>
-      <c r="Q99" s="5" t="n">
-        <v>0.9873</v>
-      </c>
+        <v>0.9815</v>
+      </c>
+      <c r="Q99" s="5" t="inlineStr"/>
       <c r="R99" s="5" t="n">
         <v>0.9834000000000001</v>
       </c>
-      <c r="S99" s="5" t="n">
-        <v>0.9873</v>
-      </c>
+      <c r="S99" s="5" t="inlineStr"/>
       <c r="T99" s="5" t="n">
-        <v>0.0032</v>
+        <v>0.0019</v>
       </c>
       <c r="U99" s="6" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="V99" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W99" s="6" t="n">
-        <v>0</v>
-      </c>
+        <v>0.19</v>
+      </c>
+      <c r="V99" s="5" t="inlineStr"/>
+      <c r="W99" s="6" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
@@ -6579,79 +6615,75 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>LYA3</t>
+          <t>HBESS1</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>Loy Yang A Power Station</t>
+          <t>Hazelwood Battery Energy Storage System</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D102" s="4" t="n">
-        <v>560</v>
-      </c>
-      <c r="E102" s="5" t="n">
-        <v>0.9742</v>
-      </c>
-      <c r="F102" s="5" t="n">
-        <v>0.9723000000000001</v>
-      </c>
-      <c r="G102" s="5" t="n">
-        <v>0.9801</v>
-      </c>
-      <c r="H102" s="5" t="n">
-        <v>0.9798</v>
-      </c>
-      <c r="I102" s="5" t="n">
-        <v>0.9754</v>
-      </c>
-      <c r="J102" s="5" t="n">
-        <v>0.976</v>
-      </c>
-      <c r="K102" s="5" t="n">
-        <v>0.9759</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="E102" s="5" t="inlineStr"/>
+      <c r="F102" s="5" t="inlineStr"/>
+      <c r="G102" s="5" t="inlineStr"/>
+      <c r="H102" s="5" t="inlineStr"/>
+      <c r="I102" s="5" t="inlineStr"/>
+      <c r="J102" s="5" t="inlineStr"/>
+      <c r="K102" s="5" t="inlineStr"/>
       <c r="L102" s="5" t="n">
-        <v>0.9782999999999999</v>
+        <v>0.9785</v>
       </c>
       <c r="M102" s="5" t="n">
-        <v>0.9782</v>
+        <v>0.9789</v>
       </c>
       <c r="N102" s="5" t="n">
-        <v>0.9809</v>
-      </c>
-      <c r="O102" s="5" t="inlineStr"/>
+        <v>0.9804</v>
+      </c>
+      <c r="O102" s="5" t="n">
+        <v>0.9864000000000001</v>
+      </c>
       <c r="P102" s="5" t="n">
-        <v>0.9815</v>
-      </c>
-      <c r="Q102" s="5" t="inlineStr"/>
+        <v>0.9802</v>
+      </c>
+      <c r="Q102" s="5" t="n">
+        <v>0.9873</v>
+      </c>
       <c r="R102" s="5" t="n">
         <v>0.9834000000000001</v>
       </c>
-      <c r="S102" s="5" t="inlineStr"/>
+      <c r="S102" s="5" t="n">
+        <v>0.9873</v>
+      </c>
       <c r="T102" s="5" t="n">
-        <v>0.0019</v>
+        <v>0.0032</v>
       </c>
       <c r="U102" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="V102" s="5" t="inlineStr"/>
-      <c r="W102" s="6" t="inlineStr"/>
+        <v>0.33</v>
+      </c>
+      <c r="V102" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W102" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>VPGS3</t>
+          <t>LYNL1</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>Valley Power Peaking Facility</t>
+          <t>LOY YANG A POWER STATION</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
@@ -6660,7 +6692,7 @@
         </is>
       </c>
       <c r="D103" s="4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E103" s="5" t="n">
         <v>0.9742</v>
@@ -6713,7 +6745,7 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>LYA2</t>
+          <t>LYA4</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -6727,7 +6759,7 @@
         </is>
       </c>
       <c r="D104" s="4" t="n">
-        <v>530</v>
+        <v>560</v>
       </c>
       <c r="E104" s="5" t="n">
         <v>0.9742</v>
@@ -6780,7 +6812,7 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>LYA1</t>
+          <t>LYA3</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -6847,12 +6879,12 @@
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>LOYYB1</t>
+          <t>LYA2</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>Loy Yang B Power Station</t>
+          <t>Loy Yang A Power Station</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
@@ -6861,7 +6893,7 @@
         </is>
       </c>
       <c r="D106" s="4" t="n">
-        <v>500</v>
+        <v>530</v>
       </c>
       <c r="E106" s="5" t="n">
         <v>0.9742</v>
@@ -6914,12 +6946,12 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>VPGS5</t>
+          <t>LYA1</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>Valley Power Peaking Facility</t>
+          <t>Loy Yang A Power Station</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
@@ -6928,7 +6960,7 @@
         </is>
       </c>
       <c r="D107" s="4" t="n">
-        <v>50</v>
+        <v>560</v>
       </c>
       <c r="E107" s="5" t="n">
         <v>0.9742</v>
@@ -6981,12 +7013,12 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>VPGS4</t>
+          <t>LOYYB2</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>Valley Power Peaking Facility</t>
+          <t>Loy Yang B Power Station</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
@@ -6995,7 +7027,7 @@
         </is>
       </c>
       <c r="D108" s="4" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="E108" s="5" t="n">
         <v>0.9742</v>
@@ -7048,7 +7080,7 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>LOYYB2</t>
+          <t>LOYYB1</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -7123,7 +7155,9 @@
           <t>Basslink HVDC Link</t>
         </is>
       </c>
-      <c r="C110" s="3" t="n"/>
+      <c r="C110" s="3" t="n">
+        <v/>
+      </c>
       <c r="D110" s="4" t="n">
         <v>600</v>
       </c>
@@ -7312,12 +7346,12 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>WKIEWA2</t>
+          <t>WKIEWA1</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>WEST KIEWA POWER STATION</t>
+          <t>West Kiewa Power Station</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
@@ -7326,7 +7360,7 @@
         </is>
       </c>
       <c r="D113" s="4" t="n">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="E113" s="5" t="n">
         <v>1.0247</v>
@@ -7379,12 +7413,12 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>WKIEWA1</t>
+          <t>WKIEWA2</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>West Kiewa Power Station</t>
+          <t>WEST KIEWA POWER STATION</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
@@ -7393,7 +7427,7 @@
         </is>
       </c>
       <c r="D114" s="4" t="n">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="E114" s="5" t="n">
         <v>1.0247</v>
@@ -7633,74 +7667,62 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>BDL02</t>
+          <t>MLB01</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>Bairnsdale Power Station</t>
+          <t>Mortlake Battery Energy Storage System</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D118" s="4" t="n">
-        <v>46</v>
-      </c>
-      <c r="E118" s="5" t="n">
-        <v>0.9771</v>
-      </c>
-      <c r="F118" s="5" t="n">
-        <v>0.9745</v>
-      </c>
-      <c r="G118" s="5" t="n">
-        <v>0.9863</v>
-      </c>
-      <c r="H118" s="5" t="n">
-        <v>0.9866</v>
-      </c>
-      <c r="I118" s="5" t="n">
-        <v>0.9871</v>
-      </c>
-      <c r="J118" s="5" t="n">
-        <v>0.9899</v>
-      </c>
-      <c r="K118" s="5" t="n">
-        <v>0.9874000000000001</v>
-      </c>
-      <c r="L118" s="5" t="n">
-        <v>0.9913</v>
-      </c>
-      <c r="M118" s="5" t="n">
-        <v>0.9804</v>
-      </c>
-      <c r="N118" s="5" t="n">
-        <v>0.9816</v>
-      </c>
+        <v>440</v>
+      </c>
+      <c r="E118" s="5" t="inlineStr"/>
+      <c r="F118" s="5" t="inlineStr"/>
+      <c r="G118" s="5" t="inlineStr"/>
+      <c r="H118" s="5" t="inlineStr"/>
+      <c r="I118" s="5" t="inlineStr"/>
+      <c r="J118" s="5" t="inlineStr"/>
+      <c r="K118" s="5" t="inlineStr"/>
+      <c r="L118" s="5" t="inlineStr"/>
+      <c r="M118" s="5" t="inlineStr"/>
+      <c r="N118" s="5" t="inlineStr"/>
       <c r="O118" s="5" t="inlineStr"/>
       <c r="P118" s="5" t="n">
-        <v>0.9816</v>
-      </c>
-      <c r="Q118" s="5" t="inlineStr"/>
+        <v>0.9945000000000001</v>
+      </c>
+      <c r="Q118" s="5" t="n">
+        <v>0.9945000000000001</v>
+      </c>
       <c r="R118" s="5" t="n">
         <v>0.9893</v>
       </c>
-      <c r="S118" s="5" t="inlineStr"/>
+      <c r="S118" s="5" t="n">
+        <v>0.994</v>
+      </c>
       <c r="T118" s="5" t="n">
-        <v>0.0077</v>
+        <v>-0.0052</v>
       </c>
       <c r="U118" s="6" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="V118" s="5" t="inlineStr"/>
-      <c r="W118" s="6" t="inlineStr"/>
+        <v>-0.52</v>
+      </c>
+      <c r="V118" s="5" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="W118" s="6" t="n">
+        <v>-0.05</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>BDL01</t>
+          <t>BDL02</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -7767,57 +7789,69 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>MLB01</t>
+          <t>BDL01</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>Mortlake Battery Energy Storage System</t>
+          <t>Bairnsdale Power Station</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D120" s="4" t="n">
-        <v>440</v>
-      </c>
-      <c r="E120" s="5" t="inlineStr"/>
-      <c r="F120" s="5" t="inlineStr"/>
-      <c r="G120" s="5" t="inlineStr"/>
-      <c r="H120" s="5" t="inlineStr"/>
-      <c r="I120" s="5" t="inlineStr"/>
-      <c r="J120" s="5" t="inlineStr"/>
-      <c r="K120" s="5" t="inlineStr"/>
-      <c r="L120" s="5" t="inlineStr"/>
-      <c r="M120" s="5" t="inlineStr"/>
-      <c r="N120" s="5" t="inlineStr"/>
+        <v>46</v>
+      </c>
+      <c r="E120" s="5" t="n">
+        <v>0.9771</v>
+      </c>
+      <c r="F120" s="5" t="n">
+        <v>0.9745</v>
+      </c>
+      <c r="G120" s="5" t="n">
+        <v>0.9863</v>
+      </c>
+      <c r="H120" s="5" t="n">
+        <v>0.9866</v>
+      </c>
+      <c r="I120" s="5" t="n">
+        <v>0.9871</v>
+      </c>
+      <c r="J120" s="5" t="n">
+        <v>0.9899</v>
+      </c>
+      <c r="K120" s="5" t="n">
+        <v>0.9874000000000001</v>
+      </c>
+      <c r="L120" s="5" t="n">
+        <v>0.9913</v>
+      </c>
+      <c r="M120" s="5" t="n">
+        <v>0.9804</v>
+      </c>
+      <c r="N120" s="5" t="n">
+        <v>0.9816</v>
+      </c>
       <c r="O120" s="5" t="inlineStr"/>
       <c r="P120" s="5" t="n">
-        <v>0.9945000000000001</v>
-      </c>
-      <c r="Q120" s="5" t="n">
-        <v>0.9945000000000001</v>
-      </c>
+        <v>0.9816</v>
+      </c>
+      <c r="Q120" s="5" t="inlineStr"/>
       <c r="R120" s="5" t="n">
         <v>0.9893</v>
       </c>
-      <c r="S120" s="5" t="n">
-        <v>0.994</v>
-      </c>
+      <c r="S120" s="5" t="inlineStr"/>
       <c r="T120" s="5" t="n">
-        <v>-0.0052</v>
+        <v>0.0077</v>
       </c>
       <c r="U120" s="6" t="n">
-        <v>-0.52</v>
-      </c>
-      <c r="V120" s="5" t="n">
-        <v>-0.0005</v>
-      </c>
-      <c r="W120" s="6" t="n">
-        <v>-0.05</v>
-      </c>
+        <v>0.78</v>
+      </c>
+      <c r="V120" s="5" t="inlineStr"/>
+      <c r="W120" s="6" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
@@ -7877,12 +7911,12 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>MREHA1</t>
+          <t>MREHA2</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>Melbourne Renewable Energy Hub Connection A1</t>
+          <t>Melbourne Renewable Energy Hub Connection A2</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
@@ -7936,12 +7970,12 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>MREHA2</t>
+          <t>MREHA1</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>Melbourne Renewable Energy Hub Connection A2</t>
+          <t>Melbourne Renewable Energy Hub Connection A1</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
@@ -8050,21 +8084,21 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>TOORAWF</t>
+          <t>GLENMAG1</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>Toora Wind Farm</t>
+          <t>Glenmaggie Hydro Power Station</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="D125" s="4" t="n">
-        <v>21</v>
+        <v>3.8</v>
       </c>
       <c r="E125" s="5" t="n">
         <v>0.9799</v>
@@ -8117,21 +8151,21 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>TGNSS1</t>
+          <t>WONWP</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>Traralgon Network Support Station</t>
+          <t>Wonthaggi Wind Farm</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D126" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E126" s="5" t="n">
         <v>0.9799</v>
@@ -8184,43 +8218,29 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>LONGFORD</t>
+          <t>PIBESS1</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>Longford Plant</t>
+          <t>Phillip Island BESS</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D127" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="E127" s="5" t="n">
-        <v>0.9799</v>
-      </c>
-      <c r="F127" s="5" t="n">
-        <v>0.9759</v>
-      </c>
-      <c r="G127" s="5" t="n">
-        <v>0.9886</v>
-      </c>
-      <c r="H127" s="5" t="n">
-        <v>0.9879</v>
-      </c>
-      <c r="I127" s="5" t="n">
-        <v>0.9938</v>
-      </c>
-      <c r="J127" s="5" t="n">
-        <v>0.9955000000000001</v>
-      </c>
-      <c r="K127" s="5" t="n">
-        <v>0.9936</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="E127" s="5" t="inlineStr"/>
+      <c r="F127" s="5" t="inlineStr"/>
+      <c r="G127" s="5" t="inlineStr"/>
+      <c r="H127" s="5" t="inlineStr"/>
+      <c r="I127" s="5" t="inlineStr"/>
+      <c r="J127" s="5" t="inlineStr"/>
+      <c r="K127" s="5" t="inlineStr"/>
       <c r="L127" s="5" t="n">
         <v>0.9977</v>
       </c>
@@ -8230,50 +8250,74 @@
       <c r="N127" s="5" t="n">
         <v>0.9848</v>
       </c>
-      <c r="O127" s="5" t="inlineStr"/>
+      <c r="O127" s="5" t="n">
+        <v>0.9848</v>
+      </c>
       <c r="P127" s="5" t="n">
         <v>0.9862</v>
       </c>
-      <c r="Q127" s="5" t="inlineStr"/>
+      <c r="Q127" s="5" t="n">
+        <v>0.9862</v>
+      </c>
       <c r="R127" s="5" t="n">
         <v>0.992</v>
       </c>
-      <c r="S127" s="5" t="inlineStr"/>
+      <c r="S127" s="5" t="n">
+        <v>0.992</v>
+      </c>
       <c r="T127" s="5" t="n">
         <v>0.0058</v>
       </c>
       <c r="U127" s="6" t="n">
         <v>0.59</v>
       </c>
-      <c r="V127" s="5" t="inlineStr"/>
-      <c r="W127" s="6" t="inlineStr"/>
+      <c r="V127" s="5" t="n">
+        <v>0.0058</v>
+      </c>
+      <c r="W127" s="6" t="n">
+        <v>0.59</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>PIBESS1</t>
+          <t>TGNSS1</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>Phillip Island BESS</t>
+          <t>Traralgon Network Support Station</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D128" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="E128" s="5" t="inlineStr"/>
-      <c r="F128" s="5" t="inlineStr"/>
-      <c r="G128" s="5" t="inlineStr"/>
-      <c r="H128" s="5" t="inlineStr"/>
-      <c r="I128" s="5" t="inlineStr"/>
-      <c r="J128" s="5" t="inlineStr"/>
-      <c r="K128" s="5" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="E128" s="5" t="n">
+        <v>0.9799</v>
+      </c>
+      <c r="F128" s="5" t="n">
+        <v>0.9759</v>
+      </c>
+      <c r="G128" s="5" t="n">
+        <v>0.9886</v>
+      </c>
+      <c r="H128" s="5" t="n">
+        <v>0.9879</v>
+      </c>
+      <c r="I128" s="5" t="n">
+        <v>0.9938</v>
+      </c>
+      <c r="J128" s="5" t="n">
+        <v>0.9955000000000001</v>
+      </c>
+      <c r="K128" s="5" t="n">
+        <v>0.9936</v>
+      </c>
       <c r="L128" s="5" t="n">
         <v>0.9977</v>
       </c>
@@ -8283,43 +8327,33 @@
       <c r="N128" s="5" t="n">
         <v>0.9848</v>
       </c>
-      <c r="O128" s="5" t="n">
-        <v>0.9848</v>
-      </c>
+      <c r="O128" s="5" t="inlineStr"/>
       <c r="P128" s="5" t="n">
         <v>0.9862</v>
       </c>
-      <c r="Q128" s="5" t="n">
-        <v>0.9862</v>
-      </c>
+      <c r="Q128" s="5" t="inlineStr"/>
       <c r="R128" s="5" t="n">
         <v>0.992</v>
       </c>
-      <c r="S128" s="5" t="n">
-        <v>0.992</v>
-      </c>
+      <c r="S128" s="5" t="inlineStr"/>
       <c r="T128" s="5" t="n">
         <v>0.0058</v>
       </c>
       <c r="U128" s="6" t="n">
         <v>0.59</v>
       </c>
-      <c r="V128" s="5" t="n">
-        <v>0.0058</v>
-      </c>
-      <c r="W128" s="6" t="n">
-        <v>0.59</v>
-      </c>
+      <c r="V128" s="5" t="inlineStr"/>
+      <c r="W128" s="6" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>BALDHWF1</t>
+          <t>TOORAWF</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>Bald Hills Wind Farm</t>
+          <t>Toora Wind Farm</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
@@ -8328,7 +8362,7 @@
         </is>
       </c>
       <c r="D129" s="4" t="n">
-        <v>106.6</v>
+        <v>21</v>
       </c>
       <c r="E129" s="5" t="n">
         <v>0.9799</v>
@@ -8381,12 +8415,12 @@
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>WONWP</t>
+          <t>BALDHWF1</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>Wonthaggi Wind Farm</t>
+          <t>Bald Hills Wind Farm</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
@@ -8395,7 +8429,7 @@
         </is>
       </c>
       <c r="D130" s="4" t="n">
-        <v>12</v>
+        <v>106.6</v>
       </c>
       <c r="E130" s="5" t="n">
         <v>0.9799</v>
@@ -8448,21 +8482,21 @@
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>GLENMAG1</t>
+          <t>LONGFORD</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>Glenmaggie Hydro Power Station</t>
+          <t>Longford Plant</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>Hydro</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D131" s="4" t="n">
-        <v>3.8</v>
+        <v>22</v>
       </c>
       <c r="E131" s="5" t="n">
         <v>0.9799</v>
@@ -8641,12 +8675,12 @@
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>YAMBUKWF</t>
+          <t>FSWF1</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>Yambuk Wind Farm</t>
+          <t>Ferguson South Wind Farm</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
@@ -8655,23 +8689,13 @@
         </is>
       </c>
       <c r="D134" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="E134" s="5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="F134" s="5" t="n">
-        <v>1.0339</v>
-      </c>
-      <c r="G134" s="5" t="n">
-        <v>1.0322</v>
-      </c>
-      <c r="H134" s="5" t="n">
-        <v>1.0149</v>
-      </c>
-      <c r="I134" s="5" t="n">
-        <v>1.0019</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="E134" s="5" t="inlineStr"/>
+      <c r="F134" s="5" t="inlineStr"/>
+      <c r="G134" s="5" t="inlineStr"/>
+      <c r="H134" s="5" t="inlineStr"/>
+      <c r="I134" s="5" t="inlineStr"/>
       <c r="J134" s="5" t="n">
         <v>1.0079</v>
       </c>
@@ -8708,12 +8732,12 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>OAKLAND1</t>
+          <t>CODRNGTON</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>Oaklands Hill Wind Farm</t>
+          <t>Codrington Wind Farm</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
@@ -8722,7 +8746,7 @@
         </is>
       </c>
       <c r="D135" s="4" t="n">
-        <v>67</v>
+        <v>18.2</v>
       </c>
       <c r="E135" s="5" t="n">
         <v>1.03</v>
@@ -8775,12 +8799,12 @@
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>FSWF1</t>
+          <t>OAKLAND1</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>Ferguson South Wind Farm</t>
+          <t>Oaklands Hill Wind Farm</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
@@ -8789,13 +8813,23 @@
         </is>
       </c>
       <c r="D136" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="E136" s="5" t="inlineStr"/>
-      <c r="F136" s="5" t="inlineStr"/>
-      <c r="G136" s="5" t="inlineStr"/>
-      <c r="H136" s="5" t="inlineStr"/>
-      <c r="I136" s="5" t="inlineStr"/>
+        <v>67</v>
+      </c>
+      <c r="E136" s="5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="F136" s="5" t="n">
+        <v>1.0339</v>
+      </c>
+      <c r="G136" s="5" t="n">
+        <v>1.0322</v>
+      </c>
+      <c r="H136" s="5" t="n">
+        <v>1.0149</v>
+      </c>
+      <c r="I136" s="5" t="n">
+        <v>1.0019</v>
+      </c>
       <c r="J136" s="5" t="n">
         <v>1.0079</v>
       </c>
@@ -8832,12 +8866,12 @@
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>CODRNGTON</t>
+          <t>MLWF1</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>Codrington Wind Farm</t>
+          <t>Mortons Lane Wind Farm</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
@@ -8846,7 +8880,7 @@
         </is>
       </c>
       <c r="D137" s="4" t="n">
-        <v>18.2</v>
+        <v>20</v>
       </c>
       <c r="E137" s="5" t="n">
         <v>1.03</v>
@@ -8899,12 +8933,12 @@
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>MLWF1</t>
+          <t>YAMBUKWF</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>Mortons Lane Wind Farm</t>
+          <t>Yambuk Wind Farm</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
@@ -8913,7 +8947,7 @@
         </is>
       </c>
       <c r="D138" s="4" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E138" s="5" t="n">
         <v>1.03</v>
@@ -9504,7 +9538,9 @@
           <t>Hastings Generation Site</t>
         </is>
       </c>
-      <c r="C147" s="3" t="n"/>
+      <c r="C147" s="3" t="n">
+        <v/>
+      </c>
       <c r="D147" s="4" t="n">
         <v>14</v>
       </c>
@@ -9602,7 +9638,9 @@
           <t>Hastings Generation Site</t>
         </is>
       </c>
-      <c r="C149" s="3" t="n"/>
+      <c r="C149" s="3" t="n">
+        <v/>
+      </c>
       <c r="D149" s="4" t="n">
         <v>14</v>
       </c>
@@ -9700,30 +9738,30 @@
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>WOLLERT1</t>
+          <t>RUBICON</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>Wollert Renewable Energy Facility</t>
+          <t>Rubicon Mountain Streams Station</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>Other Renewable</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="D151" s="4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>0.9987</v>
+        <v>1</v>
       </c>
       <c r="F151" s="5" t="n">
-        <v>0.9985000000000001</v>
+        <v>1</v>
       </c>
       <c r="G151" s="5" t="n">
-        <v>0.998</v>
+        <v>1</v>
       </c>
       <c r="H151" s="5" t="n">
         <v>0.9979</v>
@@ -9767,12 +9805,12 @@
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>RUBICON</t>
+          <t>EILDON3</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>Rubicon Mountain Streams Station</t>
+          <t>Eildon Power Station</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
@@ -9781,16 +9819,16 @@
         </is>
       </c>
       <c r="D152" s="4" t="n">
-        <v>13</v>
+        <v>4.5</v>
       </c>
       <c r="E152" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F152" s="5" t="n">
-        <v>1</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="G152" s="5" t="n">
-        <v>1</v>
+        <v>0.998</v>
       </c>
       <c r="H152" s="5" t="n">
         <v>0.9979</v>
@@ -9834,24 +9872,24 @@
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>EILDON3</t>
+          <t>WOLLERT1</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>Eildon Power Station</t>
+          <t>Wollert Renewable Energy Facility</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>Hydro</t>
+          <t>Other Renewable</t>
         </is>
       </c>
       <c r="D153" s="4" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>1</v>
+        <v>0.9987</v>
       </c>
       <c r="F153" s="5" t="n">
         <v>0.9985000000000001</v>
@@ -10181,7 +10219,9 @@
           <t>VIC1 Dummy Generator</t>
         </is>
       </c>
-      <c r="C158" s="3" t="n"/>
+      <c r="C158" s="3" t="n">
+        <v/>
+      </c>
       <c r="D158" s="4" t="n">
         <v>3000</v>
       </c>
@@ -10498,12 +10538,12 @@
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>SHEP1</t>
+          <t>TATURA01</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>Shepparton Wastewater Treatment Facility</t>
+          <t>Tatura Biomass Generator</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
@@ -10565,12 +10605,12 @@
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>TATURA01</t>
+          <t>SHEP1</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>Tatura Biomass Generator</t>
+          <t>Shepparton Wastewater Treatment Facility</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
@@ -10766,7 +10806,7 @@
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
         <is>
-          <t>MOR1</t>
+          <t>MOR3</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
@@ -10780,10 +10820,10 @@
         </is>
       </c>
       <c r="D167" s="4" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="E167" s="5" t="n">
-        <v>0.9704</v>
+        <v>0.9732</v>
       </c>
       <c r="F167" s="5" t="inlineStr"/>
       <c r="G167" s="5" t="inlineStr"/>
@@ -10848,7 +10888,7 @@
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
         <is>
-          <t>MOR3</t>
+          <t>MOR1</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
@@ -10862,10 +10902,10 @@
         </is>
       </c>
       <c r="D169" s="4" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="E169" s="5" t="n">
-        <v>0.9732</v>
+        <v>0.9704</v>
       </c>
       <c r="F169" s="5" t="inlineStr"/>
       <c r="G169" s="5" t="inlineStr"/>
@@ -10971,7 +11011,7 @@
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>HWPNL1</t>
+          <t>HWPS6</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -10985,7 +11025,7 @@
         </is>
       </c>
       <c r="D172" s="4" t="n">
-        <v>25</v>
+        <v>200</v>
       </c>
       <c r="E172" s="5" t="n">
         <v>0.9723000000000001</v>
@@ -11014,7 +11054,7 @@
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>HWPS1</t>
+          <t>HWPS7</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -11028,7 +11068,7 @@
         </is>
       </c>
       <c r="D173" s="4" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="E173" s="5" t="n">
         <v>0.9723000000000001</v>
@@ -11057,7 +11097,7 @@
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>HWPS2</t>
+          <t>HWPS8</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -11071,7 +11111,7 @@
         </is>
       </c>
       <c r="D174" s="4" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="E174" s="5" t="n">
         <v>0.9723000000000001</v>
@@ -11100,7 +11140,7 @@
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>HWPS3</t>
+          <t>HWPS4</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
@@ -11143,7 +11183,7 @@
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>HWPS4</t>
+          <t>HWPS5</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -11186,7 +11226,7 @@
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
         <is>
-          <t>HWPS5</t>
+          <t>HWPS3</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
@@ -11229,7 +11269,7 @@
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>HWPS6</t>
+          <t>HWPS2</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -11243,7 +11283,7 @@
         </is>
       </c>
       <c r="D178" s="4" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="E178" s="5" t="n">
         <v>0.9723000000000001</v>
@@ -11272,7 +11312,7 @@
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
         <is>
-          <t>HWPS7</t>
+          <t>HWPS1</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
@@ -11286,7 +11326,7 @@
         </is>
       </c>
       <c r="D179" s="4" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="E179" s="5" t="n">
         <v>0.9723000000000001</v>
@@ -11315,7 +11355,7 @@
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>HWPS8</t>
+          <t>HWPNL1</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -11329,7 +11369,7 @@
         </is>
       </c>
       <c r="D180" s="4" t="n">
-        <v>200</v>
+        <v>25</v>
       </c>
       <c r="E180" s="5" t="n">
         <v>0.9723000000000001</v>
@@ -11358,12 +11398,12 @@
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>MORNW</t>
+          <t>WYNDW</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>Mornington Waste Disposal Facility</t>
+          <t>Wyndham Waste Disposal Facility</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
@@ -11375,13 +11415,13 @@
         <v>1</v>
       </c>
       <c r="E181" s="5" t="n">
-        <v>0.9923999999999999</v>
+        <v>1.0032</v>
       </c>
       <c r="F181" s="5" t="n">
-        <v>0.9925</v>
+        <v>1.0068</v>
       </c>
       <c r="G181" s="5" t="n">
-        <v>0.9963</v>
+        <v>1.0084</v>
       </c>
       <c r="H181" s="5" t="inlineStr"/>
       <c r="I181" s="5" t="inlineStr"/>
@@ -11403,12 +11443,12 @@
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>WYNDW</t>
+          <t>MORNW</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>Wyndham Waste Disposal Facility</t>
+          <t>Mornington Waste Disposal Facility</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
@@ -11420,13 +11460,13 @@
         <v>1</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>1.0032</v>
+        <v>0.9923999999999999</v>
       </c>
       <c r="F182" s="5" t="n">
-        <v>1.0068</v>
+        <v>0.9925</v>
       </c>
       <c r="G182" s="5" t="n">
-        <v>1.0084</v>
+        <v>0.9963</v>
       </c>
       <c r="H182" s="5" t="inlineStr"/>
       <c r="I182" s="5" t="inlineStr"/>
@@ -11448,45 +11488,43 @@
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t>CORIO1</t>
+          <t>BERWICK</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>Corio Landfill Gas Power Station</t>
-        </is>
-      </c>
-      <c r="C183" s="3" t="inlineStr">
-        <is>
-          <t>Other Renewable</t>
-        </is>
+          <t>Berwick Power Plant</t>
+        </is>
+      </c>
+      <c r="C183" s="3" t="n">
+        <v/>
       </c>
       <c r="D183" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E183" s="5" t="n">
-        <v>0.9987</v>
+        <v>0.9923</v>
       </c>
       <c r="F183" s="5" t="n">
-        <v>1.0048</v>
+        <v>0.9923</v>
       </c>
       <c r="G183" s="5" t="n">
-        <v>1.0055</v>
+        <v>0.9923</v>
       </c>
       <c r="H183" s="5" t="n">
-        <v>1.0002</v>
+        <v>0.9923</v>
       </c>
       <c r="I183" s="5" t="n">
-        <v>0.9908</v>
+        <v>0.9923</v>
       </c>
       <c r="J183" s="5" t="n">
-        <v>0.9913999999999999</v>
+        <v>0.9923</v>
       </c>
       <c r="K183" s="5" t="n">
-        <v>0.9918</v>
+        <v>0.9923</v>
       </c>
       <c r="L183" s="5" t="n">
-        <v>0.9933</v>
+        <v>0.9923</v>
       </c>
       <c r="M183" s="5" t="inlineStr"/>
       <c r="N183" s="5" t="inlineStr"/>
@@ -11503,41 +11541,45 @@
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>BERWICK</t>
+          <t>CORIO1</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>Berwick Power Plant</t>
-        </is>
-      </c>
-      <c r="C184" s="3" t="n"/>
+          <t>Corio Landfill Gas Power Station</t>
+        </is>
+      </c>
+      <c r="C184" s="3" t="inlineStr">
+        <is>
+          <t>Other Renewable</t>
+        </is>
+      </c>
       <c r="D184" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E184" s="5" t="n">
-        <v>0.9923</v>
+        <v>0.9987</v>
       </c>
       <c r="F184" s="5" t="n">
-        <v>0.9923</v>
+        <v>1.0048</v>
       </c>
       <c r="G184" s="5" t="n">
-        <v>0.9923</v>
+        <v>1.0055</v>
       </c>
       <c r="H184" s="5" t="n">
-        <v>0.9923</v>
+        <v>1.0002</v>
       </c>
       <c r="I184" s="5" t="n">
-        <v>0.9923</v>
+        <v>0.9908</v>
       </c>
       <c r="J184" s="5" t="n">
-        <v>0.9923</v>
+        <v>0.9913999999999999</v>
       </c>
       <c r="K184" s="5" t="n">
-        <v>0.9923</v>
+        <v>0.9918</v>
       </c>
       <c r="L184" s="5" t="n">
-        <v>0.9923</v>
+        <v>0.9933</v>
       </c>
       <c r="M184" s="5" t="inlineStr"/>
       <c r="N184" s="5" t="inlineStr"/>
@@ -11554,12 +11596,12 @@
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
         <is>
-          <t>BROADMDW</t>
+          <t>SVALE1</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>Broadmeadows Landfill Gas Power Station</t>
+          <t>Springvale Landfill Gas Power Station</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
@@ -11571,31 +11613,31 @@
         <v>5</v>
       </c>
       <c r="E185" s="5" t="n">
-        <v>1</v>
+        <v>0.997</v>
       </c>
       <c r="F185" s="5" t="n">
-        <v>1</v>
+        <v>0.9972</v>
       </c>
       <c r="G185" s="5" t="n">
-        <v>1</v>
+        <v>0.9989</v>
       </c>
       <c r="H185" s="5" t="n">
-        <v>1</v>
+        <v>0.9986</v>
       </c>
       <c r="I185" s="5" t="n">
-        <v>1</v>
+        <v>0.9987</v>
       </c>
       <c r="J185" s="5" t="n">
-        <v>1</v>
+        <v>0.9984</v>
       </c>
       <c r="K185" s="5" t="n">
-        <v>1</v>
+        <v>0.9957</v>
       </c>
       <c r="L185" s="5" t="n">
-        <v>1</v>
+        <v>0.9972</v>
       </c>
       <c r="M185" s="5" t="n">
-        <v>1</v>
+        <v>1.0001</v>
       </c>
       <c r="N185" s="5" t="inlineStr"/>
       <c r="O185" s="5" t="inlineStr"/>
@@ -11611,12 +11653,12 @@
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>SVALE1</t>
+          <t>BROADMDW</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>Springvale Landfill Gas Power Station</t>
+          <t>Broadmeadows Landfill Gas Power Station</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
@@ -11628,31 +11670,31 @@
         <v>5</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>0.997</v>
+        <v>1</v>
       </c>
       <c r="F186" s="5" t="n">
-        <v>0.9972</v>
+        <v>1</v>
       </c>
       <c r="G186" s="5" t="n">
-        <v>0.9989</v>
+        <v>1</v>
       </c>
       <c r="H186" s="5" t="n">
-        <v>0.9986</v>
+        <v>1</v>
       </c>
       <c r="I186" s="5" t="n">
-        <v>0.9987</v>
+        <v>1</v>
       </c>
       <c r="J186" s="5" t="n">
-        <v>0.9984</v>
+        <v>1</v>
       </c>
       <c r="K186" s="5" t="n">
-        <v>0.9957</v>
+        <v>1</v>
       </c>
       <c r="L186" s="5" t="n">
-        <v>0.9972</v>
+        <v>1</v>
       </c>
       <c r="M186" s="5" t="n">
-        <v>1.0001</v>
+        <v>1</v>
       </c>
       <c r="N186" s="5" t="inlineStr"/>
       <c r="O186" s="5" t="inlineStr"/>
@@ -12141,23 +12183,15 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>KIATAWF1</t>
+          <t>DIAPURWF1</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr"/>
       <c r="C7" s="5" t="inlineStr"/>
-      <c r="D7" s="5" t="n">
-        <v>1.0357</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>0.9911</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>0.9066</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>0.8974</v>
-      </c>
+      <c r="D7" s="5" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr"/>
       <c r="H7" s="5" t="n">
         <v>0.9005</v>
       </c>
@@ -12183,15 +12217,23 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>DIAPURWF1</t>
+          <t>KIATAWF1</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr"/>
       <c r="C8" s="5" t="inlineStr"/>
-      <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="5" t="inlineStr"/>
-      <c r="F8" s="5" t="inlineStr"/>
-      <c r="G8" s="5" t="inlineStr"/>
+      <c r="D8" s="5" t="n">
+        <v>1.0357</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.9911</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>0.9066</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>0.8974</v>
+      </c>
       <c r="H8" s="5" t="n">
         <v>0.9005</v>
       </c>
@@ -12329,14 +12371,18 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>YATSF1</t>
+          <t>KARSF1</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr"/>
       <c r="C12" s="5" t="inlineStr"/>
       <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="n">
+        <v>0.9472</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0.8097</v>
+      </c>
       <c r="G12" s="5" t="n">
         <v>0.8045</v>
       </c>
@@ -12365,18 +12411,14 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>KARSF1</t>
+          <t>YATSF1</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr"/>
       <c r="C13" s="5" t="inlineStr"/>
       <c r="D13" s="5" t="inlineStr"/>
-      <c r="E13" s="5" t="n">
-        <v>0.9472</v>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>0.8097</v>
-      </c>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr"/>
       <c r="G13" s="5" t="n">
         <v>0.8045</v>
       </c>
@@ -12405,7 +12447,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>BANN1</t>
+          <t>WEMENSF1</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr"/>
@@ -12445,7 +12487,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>WEMENSF1</t>
+          <t>BANN1</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr"/>
@@ -12485,30 +12527,18 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>NUMURSF1</t>
+          <t>GIRGSF</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr"/>
       <c r="C16" s="5" t="inlineStr"/>
       <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="n">
-        <v>0.982</v>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>0.9896</v>
-      </c>
-      <c r="G16" s="5" t="n">
-        <v>0.9945000000000001</v>
-      </c>
-      <c r="H16" s="5" t="n">
-        <v>0.9963</v>
-      </c>
-      <c r="I16" s="5" t="n">
-        <v>0.9715</v>
-      </c>
-      <c r="J16" s="5" t="n">
-        <v>0.9738</v>
-      </c>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr"/>
       <c r="K16" s="5" t="n">
         <v>0.9477</v>
       </c>
@@ -12525,18 +12555,30 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>WUNUSF1</t>
+          <t>NUMURSF1</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr"/>
       <c r="C17" s="5" t="inlineStr"/>
       <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>0.9896</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0.9945000000000001</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>0.9963</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>0.9715</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>0.9738</v>
+      </c>
       <c r="K17" s="5" t="n">
         <v>0.9477</v>
       </c>
@@ -12553,7 +12595,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>LANCSF1</t>
+          <t>WUNUSF1</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr"/>
@@ -12565,10 +12607,12 @@
       <c r="H18" s="5" t="inlineStr"/>
       <c r="I18" s="5" t="inlineStr"/>
       <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="n">
+        <v>0.9477</v>
+      </c>
       <c r="L18" s="5" t="inlineStr"/>
       <c r="M18" s="5" t="n">
-        <v>0.9441000000000001</v>
+        <v>0.9463</v>
       </c>
       <c r="N18" s="5" t="inlineStr"/>
       <c r="O18" s="5" t="n">
@@ -12579,7 +12623,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>GIRGSF</t>
+          <t>LANCSF1</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr"/>
@@ -12591,12 +12635,10 @@
       <c r="H19" s="5" t="inlineStr"/>
       <c r="I19" s="5" t="inlineStr"/>
       <c r="J19" s="5" t="inlineStr"/>
-      <c r="K19" s="5" t="n">
-        <v>0.9477</v>
-      </c>
+      <c r="K19" s="5" t="inlineStr"/>
       <c r="L19" s="5" t="inlineStr"/>
       <c r="M19" s="5" t="n">
-        <v>0.9463</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="N19" s="5" t="inlineStr"/>
       <c r="O19" s="5" t="n">
@@ -12607,7 +12649,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>WINTSF1</t>
+          <t>GLRWNSF1</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr"/>
@@ -12643,7 +12685,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>GLRWNSF1</t>
+          <t>WINTSF1</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr"/>
@@ -12943,7 +12985,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>BRYB1WF1</t>
+          <t>BRYB2WF2</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr"/>
@@ -12951,12 +12993,8 @@
       <c r="D30" s="5" t="inlineStr"/>
       <c r="E30" s="5" t="inlineStr"/>
       <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="n">
-        <v>0.9482</v>
-      </c>
-      <c r="H30" s="5" t="n">
-        <v>0.9431</v>
-      </c>
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr"/>
       <c r="I30" s="5" t="n">
         <v>0.9496</v>
       </c>
@@ -12979,7 +13017,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>BRYB2WF2</t>
+          <t>BRYB1WF1</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr"/>
@@ -12987,8 +13025,12 @@
       <c r="D31" s="5" t="inlineStr"/>
       <c r="E31" s="5" t="inlineStr"/>
       <c r="F31" s="5" t="inlineStr"/>
-      <c r="G31" s="5" t="inlineStr"/>
-      <c r="H31" s="5" t="inlineStr"/>
+      <c r="G31" s="5" t="n">
+        <v>0.9482</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>0.9431</v>
+      </c>
       <c r="I31" s="5" t="n">
         <v>0.9496</v>
       </c>
@@ -13271,24 +13313,14 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>MERCER01</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="n">
-        <v>1.0033</v>
-      </c>
-      <c r="C39" s="5" t="n">
-        <v>1.0048</v>
-      </c>
-      <c r="D39" s="5" t="n">
-        <v>1.001</v>
-      </c>
-      <c r="E39" s="5" t="n">
-        <v>0.9909</v>
-      </c>
-      <c r="F39" s="5" t="n">
-        <v>0.965</v>
-      </c>
+          <t>MOORAWF1</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr"/>
+      <c r="C39" s="5" t="inlineStr"/>
+      <c r="D39" s="5" t="inlineStr"/>
+      <c r="E39" s="5" t="inlineStr"/>
+      <c r="F39" s="5" t="inlineStr"/>
       <c r="G39" s="5" t="n">
         <v>0.9500999999999999</v>
       </c>
@@ -13347,14 +13379,24 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>MOORAWF1</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="inlineStr"/>
-      <c r="C41" s="5" t="inlineStr"/>
-      <c r="D41" s="5" t="inlineStr"/>
-      <c r="E41" s="5" t="inlineStr"/>
-      <c r="F41" s="5" t="inlineStr"/>
+          <t>MERCER01</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>1.0033</v>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>1.0048</v>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>1.001</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>0.9909</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>0.965</v>
+      </c>
       <c r="G41" s="5" t="n">
         <v>0.9500999999999999</v>
       </c>
@@ -13383,7 +13425,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>MURAYNL2</t>
+          <t>MURAYNL3</t>
         </is>
       </c>
       <c r="B42" s="5" t="n">
@@ -13429,7 +13471,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>MURAYNL3</t>
+          <t>MURAYNL2</t>
         </is>
       </c>
       <c r="B43" s="5" t="n">
@@ -13659,7 +13701,7 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>YWNL1</t>
+          <t>YWPS4</t>
         </is>
       </c>
       <c r="B48" s="5" t="n">
@@ -13751,7 +13793,7 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>YWPS4</t>
+          <t>YWNL1</t>
         </is>
       </c>
       <c r="B50" s="5" t="n">
@@ -13797,7 +13839,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>BAPS</t>
+          <t>DARTM1</t>
         </is>
       </c>
       <c r="B51" s="5" t="n">
@@ -13843,7 +13885,7 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>DARTM1</t>
+          <t>BAPS</t>
         </is>
       </c>
       <c r="B52" s="5" t="n">
@@ -13965,19 +14007,23 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>MAROOWF1</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="inlineStr"/>
-      <c r="C55" s="5" t="inlineStr"/>
+          <t>CHALLHWF</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>1.0988</v>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>1.0988</v>
+      </c>
       <c r="D55" s="5" t="n">
-        <v>1.016</v>
+        <v>1.0988</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>1.0016</v>
+        <v>0.9957</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>0.9716</v>
+        <v>0.9193</v>
       </c>
       <c r="G55" s="5" t="n">
         <v>0.9711</v>
@@ -14053,23 +14099,19 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>CHALLHWF</t>
-        </is>
-      </c>
-      <c r="B57" s="5" t="n">
-        <v>1.0988</v>
-      </c>
-      <c r="C57" s="5" t="n">
-        <v>1.0988</v>
-      </c>
+          <t>MAROOWF1</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr"/>
+      <c r="C57" s="5" t="inlineStr"/>
       <c r="D57" s="5" t="n">
-        <v>1.0988</v>
+        <v>1.016</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>0.9957</v>
+        <v>1.0016</v>
       </c>
       <c r="F57" s="5" t="n">
-        <v>0.9193</v>
+        <v>0.9716</v>
       </c>
       <c r="G57" s="5" t="n">
         <v>0.9711</v>
@@ -14141,7 +14183,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>MURR1-8</t>
+          <t>MURR1-4</t>
         </is>
       </c>
       <c r="B59" s="5" t="n">
@@ -14187,7 +14229,7 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>MURR2-1</t>
+          <t>MURR1-3</t>
         </is>
       </c>
       <c r="B60" s="5" t="n">
@@ -14233,7 +14275,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>MURR1-10</t>
+          <t>MURR1-2</t>
         </is>
       </c>
       <c r="B61" s="5" t="n">
@@ -14279,7 +14321,7 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>MURR1-1</t>
+          <t>MURR1-10</t>
         </is>
       </c>
       <c r="B62" s="5" t="n">
@@ -14325,7 +14367,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>MURR1-2</t>
+          <t>MURR1-1</t>
         </is>
       </c>
       <c r="B63" s="5" t="n">
@@ -14371,7 +14413,7 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>MURR1-9</t>
+          <t>MURR1-7</t>
         </is>
       </c>
       <c r="B64" s="5" t="n">
@@ -14417,7 +14459,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>MURR1-7</t>
+          <t>MURR1-6</t>
         </is>
       </c>
       <c r="B65" s="5" t="n">
@@ -14509,7 +14551,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>MURR1-4</t>
+          <t>MURR1-8</t>
         </is>
       </c>
       <c r="B67" s="5" t="n">
@@ -14555,7 +14597,7 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>MURR1-3</t>
+          <t>MURR2-2</t>
         </is>
       </c>
       <c r="B68" s="5" t="n">
@@ -14601,7 +14643,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>MURR2-2</t>
+          <t>MURR2-1</t>
         </is>
       </c>
       <c r="B69" s="5" t="n">
@@ -14647,7 +14689,7 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>MURR2-3</t>
+          <t>MURR1-9</t>
         </is>
       </c>
       <c r="B70" s="5" t="n">
@@ -14693,7 +14735,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>MURR2-4</t>
+          <t>MURR2-3</t>
         </is>
       </c>
       <c r="B71" s="5" t="n">
@@ -14739,7 +14781,7 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>MURR1-6</t>
+          <t>MURR2-4</t>
         </is>
       </c>
       <c r="B72" s="5" t="n">
@@ -14859,7 +14901,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>GPWFEST3</t>
+          <t>GPWFEST1</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr"/>
@@ -14887,7 +14929,7 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>GPWFEST1</t>
+          <t>GPWFEST3</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr"/>
@@ -14995,42 +15037,22 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>JLA04</t>
-        </is>
-      </c>
-      <c r="B80" s="5" t="n">
-        <v>0.9667</v>
-      </c>
-      <c r="C80" s="5" t="n">
-        <v>0.9641</v>
-      </c>
-      <c r="D80" s="5" t="n">
-        <v>0.983</v>
-      </c>
-      <c r="E80" s="5" t="n">
-        <v>0.9782999999999999</v>
-      </c>
-      <c r="F80" s="5" t="n">
-        <v>0.9731</v>
-      </c>
-      <c r="G80" s="5" t="n">
-        <v>0.9734</v>
-      </c>
-      <c r="H80" s="5" t="n">
-        <v>0.9755</v>
-      </c>
-      <c r="I80" s="5" t="n">
-        <v>0.9727</v>
-      </c>
-      <c r="J80" s="5" t="n">
-        <v>0.9764</v>
-      </c>
-      <c r="K80" s="5" t="n">
-        <v>0.9789</v>
-      </c>
+          <t>GPWFWST2</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr"/>
+      <c r="C80" s="5" t="inlineStr"/>
+      <c r="D80" s="5" t="inlineStr"/>
+      <c r="E80" s="5" t="inlineStr"/>
+      <c r="F80" s="5" t="inlineStr"/>
+      <c r="G80" s="5" t="inlineStr"/>
+      <c r="H80" s="5" t="inlineStr"/>
+      <c r="I80" s="5" t="inlineStr"/>
+      <c r="J80" s="5" t="inlineStr"/>
+      <c r="K80" s="5" t="inlineStr"/>
       <c r="L80" s="5" t="inlineStr"/>
       <c r="M80" s="5" t="n">
-        <v>0.9768</v>
+        <v>0.9837</v>
       </c>
       <c r="N80" s="5" t="inlineStr"/>
       <c r="O80" s="5" t="n">
@@ -15041,42 +15063,22 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>JLA03</t>
-        </is>
-      </c>
-      <c r="B81" s="5" t="n">
-        <v>0.9667</v>
-      </c>
-      <c r="C81" s="5" t="n">
-        <v>0.9641</v>
-      </c>
-      <c r="D81" s="5" t="n">
-        <v>0.983</v>
-      </c>
-      <c r="E81" s="5" t="n">
-        <v>0.9782999999999999</v>
-      </c>
-      <c r="F81" s="5" t="n">
-        <v>0.9731</v>
-      </c>
-      <c r="G81" s="5" t="n">
-        <v>0.9734</v>
-      </c>
-      <c r="H81" s="5" t="n">
-        <v>0.9755</v>
-      </c>
-      <c r="I81" s="5" t="n">
-        <v>0.9727</v>
-      </c>
-      <c r="J81" s="5" t="n">
-        <v>0.9764</v>
-      </c>
-      <c r="K81" s="5" t="n">
-        <v>0.9789</v>
-      </c>
+          <t>GPWFWST1</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr"/>
+      <c r="C81" s="5" t="inlineStr"/>
+      <c r="D81" s="5" t="inlineStr"/>
+      <c r="E81" s="5" t="inlineStr"/>
+      <c r="F81" s="5" t="inlineStr"/>
+      <c r="G81" s="5" t="inlineStr"/>
+      <c r="H81" s="5" t="inlineStr"/>
+      <c r="I81" s="5" t="inlineStr"/>
+      <c r="J81" s="5" t="inlineStr"/>
+      <c r="K81" s="5" t="inlineStr"/>
       <c r="L81" s="5" t="inlineStr"/>
       <c r="M81" s="5" t="n">
-        <v>0.9768</v>
+        <v>0.9837</v>
       </c>
       <c r="N81" s="5" t="inlineStr"/>
       <c r="O81" s="5" t="n">
@@ -15087,21 +15089,43 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>GPWFWL1</t>
-        </is>
-      </c>
-      <c r="B82" s="5" t="inlineStr"/>
-      <c r="C82" s="5" t="inlineStr"/>
-      <c r="D82" s="5" t="inlineStr"/>
-      <c r="E82" s="5" t="inlineStr"/>
-      <c r="F82" s="5" t="inlineStr"/>
-      <c r="G82" s="5" t="inlineStr"/>
-      <c r="H82" s="5" t="inlineStr"/>
-      <c r="I82" s="5" t="inlineStr"/>
-      <c r="J82" s="5" t="inlineStr"/>
-      <c r="K82" s="5" t="inlineStr"/>
+          <t>JLA01</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="n">
+        <v>0.9667</v>
+      </c>
+      <c r="C82" s="5" t="n">
+        <v>0.9641</v>
+      </c>
+      <c r="D82" s="5" t="n">
+        <v>0.983</v>
+      </c>
+      <c r="E82" s="5" t="n">
+        <v>0.9782999999999999</v>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>0.9731</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>0.9734</v>
+      </c>
+      <c r="H82" s="5" t="n">
+        <v>0.9755</v>
+      </c>
+      <c r="I82" s="5" t="n">
+        <v>0.9727</v>
+      </c>
+      <c r="J82" s="5" t="n">
+        <v>0.9764</v>
+      </c>
+      <c r="K82" s="5" t="n">
+        <v>0.9789</v>
+      </c>
       <c r="L82" s="5" t="inlineStr"/>
-      <c r="M82" s="5" t="inlineStr"/>
+      <c r="M82" s="5" t="n">
+        <v>0.9768</v>
+      </c>
       <c r="N82" s="5" t="inlineStr"/>
       <c r="O82" s="5" t="n">
         <v>0.9823</v>
@@ -15111,7 +15135,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>JLA01</t>
+          <t>JLA04</t>
         </is>
       </c>
       <c r="B83" s="5" t="n">
@@ -15157,7 +15181,7 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>JLA02</t>
+          <t>JLA03</t>
         </is>
       </c>
       <c r="B84" s="5" t="n">
@@ -15203,7 +15227,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>JLB01</t>
+          <t>JLA02</t>
         </is>
       </c>
       <c r="B85" s="5" t="n">
@@ -15249,7 +15273,7 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>JLB02</t>
+          <t>JLB03</t>
         </is>
       </c>
       <c r="B86" s="5" t="n">
@@ -15295,7 +15319,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>JLB03</t>
+          <t>JLB02</t>
         </is>
       </c>
       <c r="B87" s="5" t="n">
@@ -15341,22 +15365,42 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>GPWFWST1</t>
-        </is>
-      </c>
-      <c r="B88" s="5" t="inlineStr"/>
-      <c r="C88" s="5" t="inlineStr"/>
-      <c r="D88" s="5" t="inlineStr"/>
-      <c r="E88" s="5" t="inlineStr"/>
-      <c r="F88" s="5" t="inlineStr"/>
-      <c r="G88" s="5" t="inlineStr"/>
-      <c r="H88" s="5" t="inlineStr"/>
-      <c r="I88" s="5" t="inlineStr"/>
-      <c r="J88" s="5" t="inlineStr"/>
-      <c r="K88" s="5" t="inlineStr"/>
+          <t>JLB01</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="n">
+        <v>0.9667</v>
+      </c>
+      <c r="C88" s="5" t="n">
+        <v>0.9641</v>
+      </c>
+      <c r="D88" s="5" t="n">
+        <v>0.983</v>
+      </c>
+      <c r="E88" s="5" t="n">
+        <v>0.9782999999999999</v>
+      </c>
+      <c r="F88" s="5" t="n">
+        <v>0.9731</v>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>0.9734</v>
+      </c>
+      <c r="H88" s="5" t="n">
+        <v>0.9755</v>
+      </c>
+      <c r="I88" s="5" t="n">
+        <v>0.9727</v>
+      </c>
+      <c r="J88" s="5" t="n">
+        <v>0.9764</v>
+      </c>
+      <c r="K88" s="5" t="n">
+        <v>0.9789</v>
+      </c>
       <c r="L88" s="5" t="inlineStr"/>
       <c r="M88" s="5" t="n">
-        <v>0.9837</v>
+        <v>0.9768</v>
       </c>
       <c r="N88" s="5" t="inlineStr"/>
       <c r="O88" s="5" t="n">
@@ -15367,7 +15411,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>GPWFWST2</t>
+          <t>GPWFWL1</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr"/>
@@ -15381,9 +15425,7 @@
       <c r="J89" s="5" t="inlineStr"/>
       <c r="K89" s="5" t="inlineStr"/>
       <c r="L89" s="5" t="inlineStr"/>
-      <c r="M89" s="5" t="n">
-        <v>0.9837</v>
-      </c>
+      <c r="M89" s="5" t="inlineStr"/>
       <c r="N89" s="5" t="inlineStr"/>
       <c r="O89" s="5" t="n">
         <v>0.9823</v>
@@ -15439,26 +15481,30 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>STOCKYD1</t>
+          <t>DUNDWF3</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr"/>
       <c r="C91" s="5" t="inlineStr"/>
       <c r="D91" s="5" t="inlineStr"/>
       <c r="E91" s="5" t="inlineStr"/>
-      <c r="F91" s="5" t="inlineStr"/>
-      <c r="G91" s="5" t="inlineStr"/>
+      <c r="F91" s="5" t="n">
+        <v>0.9812</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>0.979</v>
+      </c>
       <c r="H91" s="5" t="n">
-        <v>0.9782</v>
+        <v>0.9789</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>0.9799</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="J91" s="5" t="n">
-        <v>0.9869</v>
+        <v>0.987</v>
       </c>
       <c r="K91" s="5" t="n">
-        <v>0.9812</v>
+        <v>0.981</v>
       </c>
       <c r="L91" s="5" t="inlineStr"/>
       <c r="M91" s="5" t="n">
@@ -15473,7 +15519,7 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>DUNDWF3</t>
+          <t>DUNDWF2</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr"/>
@@ -15511,7 +15557,7 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>DUNDWF2</t>
+          <t>DUNDWF1</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr"/>
@@ -15549,30 +15595,26 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>DUNDWF1</t>
+          <t>STOCKYD1</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr"/>
       <c r="C94" s="5" t="inlineStr"/>
       <c r="D94" s="5" t="inlineStr"/>
       <c r="E94" s="5" t="inlineStr"/>
-      <c r="F94" s="5" t="n">
+      <c r="F94" s="5" t="inlineStr"/>
+      <c r="G94" s="5" t="inlineStr"/>
+      <c r="H94" s="5" t="n">
+        <v>0.9782</v>
+      </c>
+      <c r="I94" s="5" t="n">
+        <v>0.9799</v>
+      </c>
+      <c r="J94" s="5" t="n">
+        <v>0.9869</v>
+      </c>
+      <c r="K94" s="5" t="n">
         <v>0.9812</v>
-      </c>
-      <c r="G94" s="5" t="n">
-        <v>0.979</v>
-      </c>
-      <c r="H94" s="5" t="n">
-        <v>0.9789</v>
-      </c>
-      <c r="I94" s="5" t="n">
-        <v>0.9824000000000001</v>
-      </c>
-      <c r="J94" s="5" t="n">
-        <v>0.987</v>
-      </c>
-      <c r="K94" s="5" t="n">
-        <v>0.981</v>
       </c>
       <c r="L94" s="5" t="inlineStr"/>
       <c r="M94" s="5" t="n">
@@ -15615,7 +15657,7 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>LYNL1</t>
+          <t>VPGS6</t>
         </is>
       </c>
       <c r="B96" s="5" t="n">
@@ -15661,7 +15703,7 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>LYA4</t>
+          <t>VPGS5</t>
         </is>
       </c>
       <c r="B97" s="5" t="n">
@@ -15707,7 +15749,7 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>VPGS6</t>
+          <t>VPGS4</t>
         </is>
       </c>
       <c r="B98" s="5" t="n">
@@ -15753,40 +15795,48 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>HBESS1</t>
-        </is>
-      </c>
-      <c r="B99" s="5" t="inlineStr"/>
-      <c r="C99" s="5" t="inlineStr"/>
-      <c r="D99" s="5" t="inlineStr"/>
-      <c r="E99" s="5" t="inlineStr"/>
-      <c r="F99" s="5" t="inlineStr"/>
-      <c r="G99" s="5" t="inlineStr"/>
-      <c r="H99" s="5" t="inlineStr"/>
+          <t>VPGS3</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="n">
+        <v>0.9742</v>
+      </c>
+      <c r="C99" s="5" t="n">
+        <v>0.9723000000000001</v>
+      </c>
+      <c r="D99" s="5" t="n">
+        <v>0.9801</v>
+      </c>
+      <c r="E99" s="5" t="n">
+        <v>0.9798</v>
+      </c>
+      <c r="F99" s="5" t="n">
+        <v>0.9754</v>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>0.976</v>
+      </c>
+      <c r="H99" s="5" t="n">
+        <v>0.9759</v>
+      </c>
       <c r="I99" s="5" t="n">
-        <v>0.9785</v>
+        <v>0.9782999999999999</v>
       </c>
       <c r="J99" s="5" t="n">
-        <v>0.9789</v>
+        <v>0.9782</v>
       </c>
       <c r="K99" s="5" t="n">
-        <v>0.9804</v>
-      </c>
-      <c r="L99" s="5" t="n">
-        <v>0.9864000000000001</v>
-      </c>
+        <v>0.9809</v>
+      </c>
+      <c r="L99" s="5" t="inlineStr"/>
       <c r="M99" s="5" t="n">
-        <v>0.9802</v>
-      </c>
-      <c r="N99" s="5" t="n">
-        <v>0.9873</v>
-      </c>
+        <v>0.9815</v>
+      </c>
+      <c r="N99" s="5" t="inlineStr"/>
       <c r="O99" s="5" t="n">
         <v>0.9834000000000001</v>
       </c>
-      <c r="P99" s="5" t="n">
-        <v>0.9873</v>
-      </c>
+      <c r="P99" s="5" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
@@ -15883,53 +15933,45 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>LYA3</t>
-        </is>
-      </c>
-      <c r="B102" s="5" t="n">
-        <v>0.9742</v>
-      </c>
-      <c r="C102" s="5" t="n">
-        <v>0.9723000000000001</v>
-      </c>
-      <c r="D102" s="5" t="n">
-        <v>0.9801</v>
-      </c>
-      <c r="E102" s="5" t="n">
-        <v>0.9798</v>
-      </c>
-      <c r="F102" s="5" t="n">
-        <v>0.9754</v>
-      </c>
-      <c r="G102" s="5" t="n">
-        <v>0.976</v>
-      </c>
-      <c r="H102" s="5" t="n">
-        <v>0.9759</v>
-      </c>
+          <t>HBESS1</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="inlineStr"/>
+      <c r="C102" s="5" t="inlineStr"/>
+      <c r="D102" s="5" t="inlineStr"/>
+      <c r="E102" s="5" t="inlineStr"/>
+      <c r="F102" s="5" t="inlineStr"/>
+      <c r="G102" s="5" t="inlineStr"/>
+      <c r="H102" s="5" t="inlineStr"/>
       <c r="I102" s="5" t="n">
-        <v>0.9782999999999999</v>
+        <v>0.9785</v>
       </c>
       <c r="J102" s="5" t="n">
-        <v>0.9782</v>
+        <v>0.9789</v>
       </c>
       <c r="K102" s="5" t="n">
-        <v>0.9809</v>
-      </c>
-      <c r="L102" s="5" t="inlineStr"/>
+        <v>0.9804</v>
+      </c>
+      <c r="L102" s="5" t="n">
+        <v>0.9864000000000001</v>
+      </c>
       <c r="M102" s="5" t="n">
-        <v>0.9815</v>
-      </c>
-      <c r="N102" s="5" t="inlineStr"/>
+        <v>0.9802</v>
+      </c>
+      <c r="N102" s="5" t="n">
+        <v>0.9873</v>
+      </c>
       <c r="O102" s="5" t="n">
         <v>0.9834000000000001</v>
       </c>
-      <c r="P102" s="5" t="inlineStr"/>
+      <c r="P102" s="5" t="n">
+        <v>0.9873</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>VPGS3</t>
+          <t>LYNL1</t>
         </is>
       </c>
       <c r="B103" s="5" t="n">
@@ -15975,7 +16017,7 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>LYA2</t>
+          <t>LYA4</t>
         </is>
       </c>
       <c r="B104" s="5" t="n">
@@ -16021,7 +16063,7 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>LYA1</t>
+          <t>LYA3</t>
         </is>
       </c>
       <c r="B105" s="5" t="n">
@@ -16067,7 +16109,7 @@
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>LOYYB1</t>
+          <t>LYA2</t>
         </is>
       </c>
       <c r="B106" s="5" t="n">
@@ -16113,7 +16155,7 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>VPGS5</t>
+          <t>LYA1</t>
         </is>
       </c>
       <c r="B107" s="5" t="n">
@@ -16159,7 +16201,7 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>VPGS4</t>
+          <t>LOYYB2</t>
         </is>
       </c>
       <c r="B108" s="5" t="n">
@@ -16205,7 +16247,7 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>LOYYB2</t>
+          <t>LOYYB1</t>
         </is>
       </c>
       <c r="B109" s="5" t="n">
@@ -16389,7 +16431,7 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>WKIEWA2</t>
+          <t>WKIEWA1</t>
         </is>
       </c>
       <c r="B113" s="5" t="n">
@@ -16435,7 +16477,7 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>WKIEWA1</t>
+          <t>WKIEWA2</t>
         </is>
       </c>
       <c r="B114" s="5" t="n">
@@ -16597,53 +16639,37 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>BDL02</t>
-        </is>
-      </c>
-      <c r="B118" s="5" t="n">
-        <v>0.9771</v>
-      </c>
-      <c r="C118" s="5" t="n">
-        <v>0.9745</v>
-      </c>
-      <c r="D118" s="5" t="n">
-        <v>0.9863</v>
-      </c>
-      <c r="E118" s="5" t="n">
-        <v>0.9866</v>
-      </c>
-      <c r="F118" s="5" t="n">
-        <v>0.9871</v>
-      </c>
-      <c r="G118" s="5" t="n">
-        <v>0.9899</v>
-      </c>
-      <c r="H118" s="5" t="n">
-        <v>0.9874000000000001</v>
-      </c>
-      <c r="I118" s="5" t="n">
-        <v>0.9913</v>
-      </c>
-      <c r="J118" s="5" t="n">
-        <v>0.9804</v>
-      </c>
-      <c r="K118" s="5" t="n">
-        <v>0.9816</v>
-      </c>
+          <t>MLB01</t>
+        </is>
+      </c>
+      <c r="B118" s="5" t="inlineStr"/>
+      <c r="C118" s="5" t="inlineStr"/>
+      <c r="D118" s="5" t="inlineStr"/>
+      <c r="E118" s="5" t="inlineStr"/>
+      <c r="F118" s="5" t="inlineStr"/>
+      <c r="G118" s="5" t="inlineStr"/>
+      <c r="H118" s="5" t="inlineStr"/>
+      <c r="I118" s="5" t="inlineStr"/>
+      <c r="J118" s="5" t="inlineStr"/>
+      <c r="K118" s="5" t="inlineStr"/>
       <c r="L118" s="5" t="inlineStr"/>
       <c r="M118" s="5" t="n">
-        <v>0.9816</v>
-      </c>
-      <c r="N118" s="5" t="inlineStr"/>
+        <v>0.9945000000000001</v>
+      </c>
+      <c r="N118" s="5" t="n">
+        <v>0.9945000000000001</v>
+      </c>
       <c r="O118" s="5" t="n">
         <v>0.9893</v>
       </c>
-      <c r="P118" s="5" t="inlineStr"/>
+      <c r="P118" s="5" t="n">
+        <v>0.994</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>BDL01</t>
+          <t>BDL02</t>
         </is>
       </c>
       <c r="B119" s="5" t="n">
@@ -16689,32 +16715,48 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>MLB01</t>
-        </is>
-      </c>
-      <c r="B120" s="5" t="inlineStr"/>
-      <c r="C120" s="5" t="inlineStr"/>
-      <c r="D120" s="5" t="inlineStr"/>
-      <c r="E120" s="5" t="inlineStr"/>
-      <c r="F120" s="5" t="inlineStr"/>
-      <c r="G120" s="5" t="inlineStr"/>
-      <c r="H120" s="5" t="inlineStr"/>
-      <c r="I120" s="5" t="inlineStr"/>
-      <c r="J120" s="5" t="inlineStr"/>
-      <c r="K120" s="5" t="inlineStr"/>
+          <t>BDL01</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="n">
+        <v>0.9771</v>
+      </c>
+      <c r="C120" s="5" t="n">
+        <v>0.9745</v>
+      </c>
+      <c r="D120" s="5" t="n">
+        <v>0.9863</v>
+      </c>
+      <c r="E120" s="5" t="n">
+        <v>0.9866</v>
+      </c>
+      <c r="F120" s="5" t="n">
+        <v>0.9871</v>
+      </c>
+      <c r="G120" s="5" t="n">
+        <v>0.9899</v>
+      </c>
+      <c r="H120" s="5" t="n">
+        <v>0.9874000000000001</v>
+      </c>
+      <c r="I120" s="5" t="n">
+        <v>0.9913</v>
+      </c>
+      <c r="J120" s="5" t="n">
+        <v>0.9804</v>
+      </c>
+      <c r="K120" s="5" t="n">
+        <v>0.9816</v>
+      </c>
       <c r="L120" s="5" t="inlineStr"/>
       <c r="M120" s="5" t="n">
-        <v>0.9945000000000001</v>
-      </c>
-      <c r="N120" s="5" t="n">
-        <v>0.9945000000000001</v>
-      </c>
+        <v>0.9816</v>
+      </c>
+      <c r="N120" s="5" t="inlineStr"/>
       <c r="O120" s="5" t="n">
         <v>0.9893</v>
       </c>
-      <c r="P120" s="5" t="n">
-        <v>0.994</v>
-      </c>
+      <c r="P120" s="5" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
@@ -16749,7 +16791,7 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>MREHA1</t>
+          <t>MREHA2</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr"/>
@@ -16783,7 +16825,7 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>MREHA2</t>
+          <t>MREHA1</t>
         </is>
       </c>
       <c r="B123" s="5" t="inlineStr"/>
@@ -16847,7 +16889,7 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>TOORAWF</t>
+          <t>GLENMAG1</t>
         </is>
       </c>
       <c r="B125" s="5" t="n">
@@ -16893,7 +16935,7 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>TGNSS1</t>
+          <t>WONWP</t>
         </is>
       </c>
       <c r="B126" s="5" t="n">
@@ -16939,30 +16981,16 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>LONGFORD</t>
-        </is>
-      </c>
-      <c r="B127" s="5" t="n">
-        <v>0.9799</v>
-      </c>
-      <c r="C127" s="5" t="n">
-        <v>0.9759</v>
-      </c>
-      <c r="D127" s="5" t="n">
-        <v>0.9886</v>
-      </c>
-      <c r="E127" s="5" t="n">
-        <v>0.9879</v>
-      </c>
-      <c r="F127" s="5" t="n">
-        <v>0.9938</v>
-      </c>
-      <c r="G127" s="5" t="n">
-        <v>0.9955000000000001</v>
-      </c>
-      <c r="H127" s="5" t="n">
-        <v>0.9936</v>
-      </c>
+          <t>PIBESS1</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="inlineStr"/>
+      <c r="C127" s="5" t="inlineStr"/>
+      <c r="D127" s="5" t="inlineStr"/>
+      <c r="E127" s="5" t="inlineStr"/>
+      <c r="F127" s="5" t="inlineStr"/>
+      <c r="G127" s="5" t="inlineStr"/>
+      <c r="H127" s="5" t="inlineStr"/>
       <c r="I127" s="5" t="n">
         <v>0.9977</v>
       </c>
@@ -16972,29 +17000,49 @@
       <c r="K127" s="5" t="n">
         <v>0.9848</v>
       </c>
-      <c r="L127" s="5" t="inlineStr"/>
+      <c r="L127" s="5" t="n">
+        <v>0.9848</v>
+      </c>
       <c r="M127" s="5" t="n">
         <v>0.9862</v>
       </c>
-      <c r="N127" s="5" t="inlineStr"/>
+      <c r="N127" s="5" t="n">
+        <v>0.9862</v>
+      </c>
       <c r="O127" s="5" t="n">
         <v>0.992</v>
       </c>
-      <c r="P127" s="5" t="inlineStr"/>
+      <c r="P127" s="5" t="n">
+        <v>0.992</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>PIBESS1</t>
-        </is>
-      </c>
-      <c r="B128" s="5" t="inlineStr"/>
-      <c r="C128" s="5" t="inlineStr"/>
-      <c r="D128" s="5" t="inlineStr"/>
-      <c r="E128" s="5" t="inlineStr"/>
-      <c r="F128" s="5" t="inlineStr"/>
-      <c r="G128" s="5" t="inlineStr"/>
-      <c r="H128" s="5" t="inlineStr"/>
+          <t>TGNSS1</t>
+        </is>
+      </c>
+      <c r="B128" s="5" t="n">
+        <v>0.9799</v>
+      </c>
+      <c r="C128" s="5" t="n">
+        <v>0.9759</v>
+      </c>
+      <c r="D128" s="5" t="n">
+        <v>0.9886</v>
+      </c>
+      <c r="E128" s="5" t="n">
+        <v>0.9879</v>
+      </c>
+      <c r="F128" s="5" t="n">
+        <v>0.9938</v>
+      </c>
+      <c r="G128" s="5" t="n">
+        <v>0.9955000000000001</v>
+      </c>
+      <c r="H128" s="5" t="n">
+        <v>0.9936</v>
+      </c>
       <c r="I128" s="5" t="n">
         <v>0.9977</v>
       </c>
@@ -17004,26 +17052,20 @@
       <c r="K128" s="5" t="n">
         <v>0.9848</v>
       </c>
-      <c r="L128" s="5" t="n">
-        <v>0.9848</v>
-      </c>
+      <c r="L128" s="5" t="inlineStr"/>
       <c r="M128" s="5" t="n">
         <v>0.9862</v>
       </c>
-      <c r="N128" s="5" t="n">
-        <v>0.9862</v>
-      </c>
+      <c r="N128" s="5" t="inlineStr"/>
       <c r="O128" s="5" t="n">
         <v>0.992</v>
       </c>
-      <c r="P128" s="5" t="n">
-        <v>0.992</v>
-      </c>
+      <c r="P128" s="5" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>BALDHWF1</t>
+          <t>TOORAWF</t>
         </is>
       </c>
       <c r="B129" s="5" t="n">
@@ -17069,7 +17111,7 @@
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>WONWP</t>
+          <t>BALDHWF1</t>
         </is>
       </c>
       <c r="B130" s="5" t="n">
@@ -17115,7 +17157,7 @@
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>GLENMAG1</t>
+          <t>LONGFORD</t>
         </is>
       </c>
       <c r="B131" s="5" t="n">
@@ -17241,24 +17283,14 @@
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>YAMBUKWF</t>
-        </is>
-      </c>
-      <c r="B134" s="5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="C134" s="5" t="n">
-        <v>1.0339</v>
-      </c>
-      <c r="D134" s="5" t="n">
-        <v>1.0322</v>
-      </c>
-      <c r="E134" s="5" t="n">
-        <v>1.0149</v>
-      </c>
-      <c r="F134" s="5" t="n">
-        <v>1.0019</v>
-      </c>
+          <t>FSWF1</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="inlineStr"/>
+      <c r="C134" s="5" t="inlineStr"/>
+      <c r="D134" s="5" t="inlineStr"/>
+      <c r="E134" s="5" t="inlineStr"/>
+      <c r="F134" s="5" t="inlineStr"/>
       <c r="G134" s="5" t="n">
         <v>1.0079</v>
       </c>
@@ -17287,7 +17319,7 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>OAKLAND1</t>
+          <t>CODRNGTON</t>
         </is>
       </c>
       <c r="B135" s="5" t="n">
@@ -17333,14 +17365,24 @@
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>FSWF1</t>
-        </is>
-      </c>
-      <c r="B136" s="5" t="inlineStr"/>
-      <c r="C136" s="5" t="inlineStr"/>
-      <c r="D136" s="5" t="inlineStr"/>
-      <c r="E136" s="5" t="inlineStr"/>
-      <c r="F136" s="5" t="inlineStr"/>
+          <t>OAKLAND1</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="C136" s="5" t="n">
+        <v>1.0339</v>
+      </c>
+      <c r="D136" s="5" t="n">
+        <v>1.0322</v>
+      </c>
+      <c r="E136" s="5" t="n">
+        <v>1.0149</v>
+      </c>
+      <c r="F136" s="5" t="n">
+        <v>1.0019</v>
+      </c>
       <c r="G136" s="5" t="n">
         <v>1.0079</v>
       </c>
@@ -17369,7 +17411,7 @@
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>CODRNGTON</t>
+          <t>MLWF1</t>
         </is>
       </c>
       <c r="B137" s="5" t="n">
@@ -17415,7 +17457,7 @@
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>MLWF1</t>
+          <t>YAMBUKWF</t>
         </is>
       </c>
       <c r="B138" s="5" t="n">
@@ -17951,17 +17993,17 @@
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>WOLLERT1</t>
+          <t>RUBICON</t>
         </is>
       </c>
       <c r="B151" s="5" t="n">
-        <v>0.9987</v>
+        <v>1</v>
       </c>
       <c r="C151" s="5" t="n">
-        <v>0.9985000000000001</v>
+        <v>1</v>
       </c>
       <c r="D151" s="5" t="n">
-        <v>0.998</v>
+        <v>1</v>
       </c>
       <c r="E151" s="5" t="n">
         <v>0.9979</v>
@@ -17997,17 +18039,17 @@
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>RUBICON</t>
+          <t>EILDON3</t>
         </is>
       </c>
       <c r="B152" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C152" s="5" t="n">
-        <v>1</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="D152" s="5" t="n">
-        <v>1</v>
+        <v>0.998</v>
       </c>
       <c r="E152" s="5" t="n">
         <v>0.9979</v>
@@ -18043,11 +18085,11 @@
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>EILDON3</t>
+          <t>WOLLERT1</t>
         </is>
       </c>
       <c r="B153" s="5" t="n">
-        <v>1</v>
+        <v>0.9987</v>
       </c>
       <c r="C153" s="5" t="n">
         <v>0.9985000000000001</v>
@@ -18497,7 +18539,7 @@
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>SHEP1</t>
+          <t>TATURA01</t>
         </is>
       </c>
       <c r="B163" s="5" t="n">
@@ -18543,7 +18585,7 @@
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>TATURA01</t>
+          <t>SHEP1</t>
         </is>
       </c>
       <c r="B164" s="5" t="n">
@@ -18681,11 +18723,11 @@
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
         <is>
-          <t>MOR1</t>
+          <t>MOR3</t>
         </is>
       </c>
       <c r="B167" s="5" t="n">
-        <v>0.9704</v>
+        <v>0.9732</v>
       </c>
       <c r="C167" s="5" t="inlineStr"/>
       <c r="D167" s="5" t="inlineStr"/>
@@ -18729,11 +18771,11 @@
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
         <is>
-          <t>MOR3</t>
+          <t>MOR1</t>
         </is>
       </c>
       <c r="B169" s="5" t="n">
-        <v>0.9732</v>
+        <v>0.9704</v>
       </c>
       <c r="C169" s="5" t="inlineStr"/>
       <c r="D169" s="5" t="inlineStr"/>
@@ -18801,7 +18843,7 @@
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>HWPNL1</t>
+          <t>HWPS6</t>
         </is>
       </c>
       <c r="B172" s="5" t="n">
@@ -18827,7 +18869,7 @@
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>HWPS1</t>
+          <t>HWPS7</t>
         </is>
       </c>
       <c r="B173" s="5" t="n">
@@ -18853,7 +18895,7 @@
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>HWPS2</t>
+          <t>HWPS8</t>
         </is>
       </c>
       <c r="B174" s="5" t="n">
@@ -18879,7 +18921,7 @@
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>HWPS3</t>
+          <t>HWPS4</t>
         </is>
       </c>
       <c r="B175" s="5" t="n">
@@ -18905,7 +18947,7 @@
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>HWPS4</t>
+          <t>HWPS5</t>
         </is>
       </c>
       <c r="B176" s="5" t="n">
@@ -18931,7 +18973,7 @@
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
         <is>
-          <t>HWPS5</t>
+          <t>HWPS3</t>
         </is>
       </c>
       <c r="B177" s="5" t="n">
@@ -18957,7 +18999,7 @@
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>HWPS6</t>
+          <t>HWPS2</t>
         </is>
       </c>
       <c r="B178" s="5" t="n">
@@ -18983,7 +19025,7 @@
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
         <is>
-          <t>HWPS7</t>
+          <t>HWPS1</t>
         </is>
       </c>
       <c r="B179" s="5" t="n">
@@ -19009,7 +19051,7 @@
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>HWPS8</t>
+          <t>HWPNL1</t>
         </is>
       </c>
       <c r="B180" s="5" t="n">
@@ -19035,17 +19077,17 @@
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>MORNW</t>
+          <t>WYNDW</t>
         </is>
       </c>
       <c r="B181" s="5" t="n">
-        <v>0.9923999999999999</v>
+        <v>1.0032</v>
       </c>
       <c r="C181" s="5" t="n">
-        <v>0.9925</v>
+        <v>1.0068</v>
       </c>
       <c r="D181" s="5" t="n">
-        <v>0.9963</v>
+        <v>1.0084</v>
       </c>
       <c r="E181" s="5" t="inlineStr"/>
       <c r="F181" s="5" t="inlineStr"/>
@@ -19063,17 +19105,17 @@
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>WYNDW</t>
+          <t>MORNW</t>
         </is>
       </c>
       <c r="B182" s="5" t="n">
-        <v>1.0032</v>
+        <v>0.9923999999999999</v>
       </c>
       <c r="C182" s="5" t="n">
-        <v>1.0068</v>
+        <v>0.9925</v>
       </c>
       <c r="D182" s="5" t="n">
-        <v>1.0084</v>
+        <v>0.9963</v>
       </c>
       <c r="E182" s="5" t="inlineStr"/>
       <c r="F182" s="5" t="inlineStr"/>
@@ -19091,32 +19133,32 @@
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t>CORIO1</t>
+          <t>BERWICK</t>
         </is>
       </c>
       <c r="B183" s="5" t="n">
-        <v>0.9987</v>
+        <v>0.9923</v>
       </c>
       <c r="C183" s="5" t="n">
-        <v>1.0048</v>
+        <v>0.9923</v>
       </c>
       <c r="D183" s="5" t="n">
-        <v>1.0055</v>
+        <v>0.9923</v>
       </c>
       <c r="E183" s="5" t="n">
-        <v>1.0002</v>
+        <v>0.9923</v>
       </c>
       <c r="F183" s="5" t="n">
-        <v>0.9908</v>
+        <v>0.9923</v>
       </c>
       <c r="G183" s="5" t="n">
-        <v>0.9913999999999999</v>
+        <v>0.9923</v>
       </c>
       <c r="H183" s="5" t="n">
-        <v>0.9918</v>
+        <v>0.9923</v>
       </c>
       <c r="I183" s="5" t="n">
-        <v>0.9933</v>
+        <v>0.9923</v>
       </c>
       <c r="J183" s="5" t="inlineStr"/>
       <c r="K183" s="5" t="inlineStr"/>
@@ -19129,32 +19171,32 @@
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>BERWICK</t>
+          <t>CORIO1</t>
         </is>
       </c>
       <c r="B184" s="5" t="n">
-        <v>0.9923</v>
+        <v>0.9987</v>
       </c>
       <c r="C184" s="5" t="n">
-        <v>0.9923</v>
+        <v>1.0048</v>
       </c>
       <c r="D184" s="5" t="n">
-        <v>0.9923</v>
+        <v>1.0055</v>
       </c>
       <c r="E184" s="5" t="n">
-        <v>0.9923</v>
+        <v>1.0002</v>
       </c>
       <c r="F184" s="5" t="n">
-        <v>0.9923</v>
+        <v>0.9908</v>
       </c>
       <c r="G184" s="5" t="n">
-        <v>0.9923</v>
+        <v>0.9913999999999999</v>
       </c>
       <c r="H184" s="5" t="n">
-        <v>0.9923</v>
+        <v>0.9918</v>
       </c>
       <c r="I184" s="5" t="n">
-        <v>0.9923</v>
+        <v>0.9933</v>
       </c>
       <c r="J184" s="5" t="inlineStr"/>
       <c r="K184" s="5" t="inlineStr"/>
@@ -19167,35 +19209,35 @@
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
         <is>
-          <t>BROADMDW</t>
+          <t>SVALE1</t>
         </is>
       </c>
       <c r="B185" s="5" t="n">
-        <v>1</v>
+        <v>0.997</v>
       </c>
       <c r="C185" s="5" t="n">
-        <v>1</v>
+        <v>0.9972</v>
       </c>
       <c r="D185" s="5" t="n">
-        <v>1</v>
+        <v>0.9989</v>
       </c>
       <c r="E185" s="5" t="n">
-        <v>1</v>
+        <v>0.9986</v>
       </c>
       <c r="F185" s="5" t="n">
-        <v>1</v>
+        <v>0.9987</v>
       </c>
       <c r="G185" s="5" t="n">
-        <v>1</v>
+        <v>0.9984</v>
       </c>
       <c r="H185" s="5" t="n">
-        <v>1</v>
+        <v>0.9957</v>
       </c>
       <c r="I185" s="5" t="n">
-        <v>1</v>
+        <v>0.9972</v>
       </c>
       <c r="J185" s="5" t="n">
-        <v>1</v>
+        <v>1.0001</v>
       </c>
       <c r="K185" s="5" t="inlineStr"/>
       <c r="L185" s="5" t="inlineStr"/>
@@ -19207,35 +19249,35 @@
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>SVALE1</t>
+          <t>BROADMDW</t>
         </is>
       </c>
       <c r="B186" s="5" t="n">
-        <v>0.997</v>
+        <v>1</v>
       </c>
       <c r="C186" s="5" t="n">
-        <v>0.9972</v>
+        <v>1</v>
       </c>
       <c r="D186" s="5" t="n">
-        <v>0.9989</v>
+        <v>1</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>0.9986</v>
+        <v>1</v>
       </c>
       <c r="F186" s="5" t="n">
-        <v>0.9987</v>
+        <v>1</v>
       </c>
       <c r="G186" s="5" t="n">
-        <v>0.9984</v>
+        <v>1</v>
       </c>
       <c r="H186" s="5" t="n">
-        <v>0.9957</v>
+        <v>1</v>
       </c>
       <c r="I186" s="5" t="n">
-        <v>0.9972</v>
+        <v>1</v>
       </c>
       <c r="J186" s="5" t="n">
-        <v>1.0001</v>
+        <v>1</v>
       </c>
       <c r="K186" s="5" t="inlineStr"/>
       <c r="L186" s="5" t="inlineStr"/>
@@ -19636,7 +19678,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>MURRAY</t>
+          <t>MURAYNL3</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -19665,7 +19707,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>MURAYNL1</t>
+          <t>MURAYNL2</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -19694,7 +19736,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>MURAYNL3</t>
+          <t>MURAYNL1</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -19723,7 +19765,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>MURAYNL2</t>
+          <t>MURRAY</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -19752,12 +19794,12 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>NUMURSF1</t>
+          <t>GIRGSF</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Numurkah Solar Farm</t>
+          <t>Girgarre Solar Farm</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -19781,12 +19823,12 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>WUNUSF1</t>
+          <t>NUMURSF1</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Wunghnu Solar Farm</t>
+          <t>Numurkah Solar Farm</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -19810,12 +19852,12 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>GIRGSF</t>
+          <t>WUNUSF1</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Girgarre Solar Farm</t>
+          <t>Wunghnu Solar Farm</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -19955,12 +19997,12 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>WINTSF1</t>
+          <t>GLRWNSF1</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Winton Solar Farm</t>
+          <t>Glenrowan West Solar Farm</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -19984,12 +20026,12 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>GLRWNSF1</t>
+          <t>WINTSF1</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Glenrowan West Solar Farm</t>
+          <t>Winton Solar Farm</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -20071,12 +20113,12 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>WKIEWA2</t>
+          <t>WKIEWA1</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>WEST KIEWA POWER STATION</t>
+          <t>West Kiewa Power Station</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -20100,12 +20142,12 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>WKIEWA1</t>
+          <t>WKIEWA2</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>West Kiewa Power Station</t>
+          <t>WEST KIEWA POWER STATION</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -20129,17 +20171,17 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>YWNGAHYD</t>
+          <t>TATURA01</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Yarrawonga Hydro Power Station</t>
+          <t>Tatura Biomass Generator</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Hydro</t>
+          <t>Other Renewable</t>
         </is>
       </c>
       <c r="D22" s="5" t="n">
@@ -20202,12 +20244,12 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>YATSF1</t>
+          <t>KARSF1</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Yatpool Solar Farm</t>
+          <t>Karadoc Solar Farm</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -20231,12 +20273,12 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>KARSF1</t>
+          <t>YATSF1</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Karadoc Solar Farm</t>
+          <t>Yatpool Solar Farm</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -20260,12 +20302,12 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>BANN1</t>
+          <t>WEMENSF1</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Bannerton Solar Park</t>
+          <t>Wemen Solar Farm</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -20289,12 +20331,12 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>WEMENSF1</t>
+          <t>BANN1</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Wemen Solar Farm</t>
+          <t>Bannerton Solar Park</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -20434,17 +20476,17 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>WONWP</t>
+          <t>GLENMAG1</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Wonthaggi Wind Farm</t>
+          <t>Glenmaggie Hydro Power Station</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
@@ -20463,17 +20505,17 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>PIBESS1</t>
+          <t>WONWP</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Phillip Island BESS</t>
+          <t>Wonthaggi Wind Farm</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D36" s="5" t="n">
@@ -20492,17 +20534,17 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>BALDHWF1</t>
+          <t>PIBESS1</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Bald Hills Wind Farm</t>
+          <t>Phillip Island BESS</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D37" s="5" t="n">
@@ -20521,17 +20563,17 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>GLENMAG1</t>
+          <t>TGNSS1</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Glenmaggie Hydro Power Station</t>
+          <t>Traralgon Network Support Station</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Hydro</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D38" s="5" t="n">
@@ -20550,17 +20592,17 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>LONGFORD</t>
+          <t>TOORAWF</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Longford Plant</t>
+          <t>Toora Wind Farm</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
@@ -20579,17 +20621,17 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TGNSS1</t>
+          <t>BALDHWF1</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Traralgon Network Support Station</t>
+          <t>Bald Hills Wind Farm</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D40" s="5" t="n">
@@ -20608,17 +20650,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>TOORAWF</t>
+          <t>LONGFORD</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Toora Wind Farm</t>
+          <t>Longford Plant</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">
@@ -20637,12 +20679,12 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>JLB03</t>
+          <t>JLA01</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Jeeralang "B" Power Station</t>
+          <t>Jeeralang "A" Power Station</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -20666,12 +20708,12 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>JLB02</t>
+          <t>JLA04</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Jeeralang "B" Power Station</t>
+          <t>Jeeralang "A" Power Station</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -20695,12 +20737,12 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>JLB01</t>
+          <t>JLA03</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Jeeralang "B" Power Station</t>
+          <t>Jeeralang "A" Power Station</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -20753,12 +20795,12 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>JLA03</t>
+          <t>JLB03</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Jeeralang "A" Power Station</t>
+          <t>Jeeralang "B" Power Station</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
